--- a/results/enrichment_OR_by_protein_class.xlsx
+++ b/results/enrichment_OR_by_protein_class.xlsx
@@ -932,67 +932,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.223424315461856</v>
+        <v>2.112536034121807</v>
       </c>
       <c r="C2" t="n">
-        <v>1.546626557799742</v>
+        <v>1.338396702635113</v>
       </c>
       <c r="D2" t="n">
-        <v>3.128401360544218</v>
+        <v>3.108973658323314</v>
       </c>
       <c r="E2" t="n">
-        <v>1.236879432624113</v>
+        <v>1.04950495049505</v>
       </c>
       <c r="F2" t="n">
-        <v>1.024192688905467</v>
+        <v>1.146177283355771</v>
       </c>
       <c r="G2" t="n">
-        <v>2.629950301628481</v>
+        <v>1.774182300020922</v>
       </c>
       <c r="H2" t="n">
-        <v>11.02334152334152</v>
+        <v>10.83538083538084</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5187665689967909</v>
+        <v>0.4759341637010676</v>
       </c>
       <c r="J2" t="n">
-        <v>2.626402602776403</v>
+        <v>2.555551043942212</v>
       </c>
       <c r="K2" t="n">
-        <v>1.161273209549072</v>
+        <v>1.117830828175656</v>
       </c>
       <c r="L2" t="n">
-        <v>1.100808368996671</v>
+        <v>1.088989441930618</v>
       </c>
       <c r="M2" t="n">
-        <v>1.664479225014601</v>
+        <v>1.656136872607017</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9784543885727954</v>
+        <v>1.086305777031753</v>
       </c>
       <c r="O2" t="n">
-        <v>2.398105360443623</v>
+        <v>2.347225799575455</v>
       </c>
       <c r="P2" t="n">
-        <v>3.974262734584451</v>
+        <v>3.988910696761531</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.37047353760446</v>
+        <v>15.85413744740533</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63275039745628</v>
+        <v>1.039344262295082</v>
       </c>
       <c r="S2" t="n">
         <v>0.599883063730267</v>
       </c>
       <c r="T2" t="n">
-        <v>4.256150635047518</v>
+        <v>4.175084175084175</v>
       </c>
       <c r="U2" t="n">
-        <v>1.415355703801545</v>
+        <v>1.384869475143268</v>
       </c>
       <c r="V2" t="n">
-        <v>2.446018307494473</v>
+        <v>2.368248240598305</v>
       </c>
     </row>
     <row r="3">
@@ -1002,67 +1002,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.028672963681318</v>
+        <v>1.93446411135532</v>
       </c>
       <c r="C3" t="n">
-        <v>2.761294109559341</v>
+        <v>2.384897522000927</v>
       </c>
       <c r="D3" t="n">
-        <v>3.277765223856662</v>
+        <v>3.267285305936452</v>
       </c>
       <c r="E3" t="n">
-        <v>1.051921757546832</v>
+        <v>0.8395150078628895</v>
       </c>
       <c r="F3" t="n">
-        <v>5.294158025940243</v>
+        <v>6.101659586294517</v>
       </c>
       <c r="G3" t="n">
-        <v>2.892843946211785</v>
+        <v>1.927744024369508</v>
       </c>
       <c r="H3" t="n">
-        <v>1.078453871877254</v>
+        <v>1.053373549275457</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4440889223497919</v>
+        <v>0.3898251980093412</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2474124214138</v>
+        <v>4.129908806494402</v>
       </c>
       <c r="K3" t="n">
-        <v>2.826234931136486</v>
+        <v>2.700499379751264</v>
       </c>
       <c r="L3" t="n">
-        <v>1.673067915690867</v>
+        <v>1.659287141429999</v>
       </c>
       <c r="M3" t="n">
-        <v>1.882501507757528</v>
+        <v>1.873470699694842</v>
       </c>
       <c r="N3" t="n">
-        <v>1.993950579873833</v>
+        <v>2.276027830487033</v>
       </c>
       <c r="O3" t="n">
-        <v>2.374540614710726</v>
+        <v>2.340227322501972</v>
       </c>
       <c r="P3" t="n">
-        <v>1.818317240301445</v>
+        <v>1.836054965551368</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.012651454343921</v>
+        <v>3.878442435015586</v>
       </c>
       <c r="R3" t="n">
-        <v>2.90549298215214</v>
+        <v>1.760566425251324</v>
       </c>
       <c r="S3" t="n">
         <v>1.833935857046945</v>
       </c>
       <c r="T3" t="n">
-        <v>2.135095353058027</v>
+        <v>2.108881310272687</v>
       </c>
       <c r="U3" t="n">
-        <v>1.179138546612376</v>
+        <v>1.152297864083466</v>
       </c>
       <c r="V3" t="n">
-        <v>2.624495772018861</v>
+        <v>2.579385929227274</v>
       </c>
     </row>
     <row r="4">
@@ -1072,67 +1072,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.447313289358832</v>
+        <v>1.374428285180315</v>
       </c>
       <c r="C4" t="n">
-        <v>1.082765892017748</v>
+        <v>0.9335103860381295</v>
       </c>
       <c r="D4" t="n">
-        <v>1.52897216506011</v>
+        <v>1.519463635688285</v>
       </c>
       <c r="E4" t="n">
-        <v>1.620565260094914</v>
+        <v>1.373712472802495</v>
       </c>
       <c r="F4" t="n">
-        <v>2.756253615232969</v>
+        <v>3.10741550254997</v>
       </c>
       <c r="G4" t="n">
-        <v>2.608732626165863</v>
+        <v>1.754638708071198</v>
       </c>
       <c r="H4" t="n">
-        <v>1.047477959242665</v>
+        <v>1.029050440815147</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1032392142368507</v>
+        <v>0.09418026148328126</v>
       </c>
       <c r="J4" t="n">
-        <v>2.772130890872084</v>
+        <v>2.696956589876195</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6778210116731518</v>
+        <v>0.6517509727626459</v>
       </c>
       <c r="L4" t="n">
-        <v>1.177777777777778</v>
+        <v>1.165128205128205</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8564265726588599</v>
+        <v>0.8519302285323599</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8754918278807061</v>
+        <v>0.9739814441306979</v>
       </c>
       <c r="O4" t="n">
-        <v>1.607843948604117</v>
+        <v>1.573675604970569</v>
       </c>
       <c r="P4" t="n">
-        <v>1.509300682834942</v>
+        <v>1.515092628578832</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.231939895973801</v>
+        <v>1.19210436975605</v>
       </c>
       <c r="R4" t="n">
-        <v>3.398319327731092</v>
+        <v>2.145833333333333</v>
       </c>
       <c r="S4" t="n">
         <v>1.310100536542168</v>
       </c>
       <c r="T4" t="n">
-        <v>1.731897975468092</v>
+        <v>1.698879838082514</v>
       </c>
       <c r="U4" t="n">
-        <v>1.587059875608853</v>
+        <v>1.5522666784464</v>
       </c>
       <c r="V4" t="n">
-        <v>1.428787642432422</v>
+        <v>1.383296678754339</v>
       </c>
     </row>
     <row r="5">
@@ -1142,67 +1142,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.74952940107106</v>
+        <v>1.669380145956096</v>
       </c>
       <c r="C5" t="n">
-        <v>2.197734348553692</v>
+        <v>1.865687171002352</v>
       </c>
       <c r="D5" t="n">
-        <v>1.712525039014963</v>
+        <v>1.707192627666815</v>
       </c>
       <c r="E5" t="n">
-        <v>1.160493019073042</v>
+        <v>0.9740323649729845</v>
       </c>
       <c r="F5" t="n">
-        <v>2.672107073667478</v>
+        <v>3.249656929340044</v>
       </c>
       <c r="G5" t="n">
-        <v>3.291403311318982</v>
+        <v>2.025690453357245</v>
       </c>
       <c r="H5" t="n">
-        <v>1.203470609800807</v>
+        <v>1.178540877428816</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1694725541680253</v>
+        <v>0.1499651973543474</v>
       </c>
       <c r="J5" t="n">
-        <v>4.765820238901616</v>
+        <v>4.619325542972987</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7068435754189945</v>
+        <v>0.6740921787709497</v>
       </c>
       <c r="L5" t="n">
-        <v>1.784311145708845</v>
+        <v>1.789974979754149</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8907812453973805</v>
+        <v>0.8839337294348726</v>
       </c>
       <c r="N5" t="n">
-        <v>1.373098736401416</v>
+        <v>1.621404307923363</v>
       </c>
       <c r="O5" t="n">
-        <v>1.498882021994915</v>
+        <v>1.469760272516198</v>
       </c>
       <c r="P5" t="n">
-        <v>1.923930374701036</v>
+        <v>1.980502171909964</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.639373100911562</v>
+        <v>1.580758646411903</v>
       </c>
       <c r="R5" t="n">
-        <v>1.263238690911856</v>
+        <v>0.672437542736525</v>
       </c>
       <c r="S5" t="n">
         <v>1.146038305129214</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8388350256300182</v>
+        <v>0.8072527459241841</v>
       </c>
       <c r="U5" t="n">
-        <v>2.314684257244527</v>
+        <v>2.242179181666075</v>
       </c>
       <c r="V5" t="n">
-        <v>1.664636219981775</v>
+        <v>1.643233088353199</v>
       </c>
     </row>
     <row r="6">
@@ -1212,22 +1212,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.460788130293835</v>
+        <v>3.288912247949833</v>
       </c>
       <c r="C6" t="n">
-        <v>1.507537688442211</v>
+        <v>1.304602888086643</v>
       </c>
       <c r="D6" t="n">
-        <v>2.235033259423503</v>
+        <v>2.220871327254306</v>
       </c>
       <c r="E6" t="n">
-        <v>0.77184637068358</v>
+        <v>0.6554054054054054</v>
       </c>
       <c r="F6" t="n">
-        <v>2.82063305978898</v>
+        <v>3.157443491816056</v>
       </c>
       <c r="G6" t="n">
-        <v>33.92832275240631</v>
+        <v>22.92720481744036</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1236,43 +1236,43 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>10.16026234567901</v>
+        <v>9.886546184738956</v>
       </c>
       <c r="K6" t="n">
-        <v>1.371102661596958</v>
+        <v>1.320152091254753</v>
       </c>
       <c r="L6" t="n">
-        <v>4.769452449567724</v>
+        <v>4.721254355400696</v>
       </c>
       <c r="M6" t="n">
-        <v>1.348560900870415</v>
+        <v>1.341783791575003</v>
       </c>
       <c r="N6" t="n">
-        <v>1.099248881762174</v>
+        <v>1.220390840900119</v>
       </c>
       <c r="O6" t="n">
-        <v>5.021464646464646</v>
+        <v>4.914817232375979</v>
       </c>
       <c r="P6" t="n">
-        <v>3.865310934276451</v>
+        <v>3.876495311994827</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>13.20064205457464</v>
+        <v>8.410596026490067</v>
       </c>
       <c r="S6" t="n">
         <v>1.405737704918033</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9910770693709008</v>
+        <v>0.9714319640699323</v>
       </c>
       <c r="U6" t="n">
-        <v>3.295747088370039</v>
+        <v>3.224810133599423</v>
       </c>
       <c r="V6" t="n">
-        <v>5.163652136196053</v>
+        <v>5.001746798948528</v>
       </c>
     </row>
     <row r="7">
@@ -1282,67 +1282,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.028509982874862</v>
+        <v>0.9748486497710402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6997099255896078</v>
+        <v>0.6022204077929736</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7884617001774347</v>
+        <v>0.783029112604213</v>
       </c>
       <c r="E7" t="n">
-        <v>1.310759027266028</v>
+        <v>1.107075064710958</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8281921549426038</v>
+        <v>0.9287405303030303</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6105702648314304</v>
+        <v>0.4065481626192651</v>
       </c>
       <c r="H7" t="n">
-        <v>1.16416958356505</v>
+        <v>1.14331512316399</v>
       </c>
       <c r="I7" t="n">
-        <v>3.069109651724291</v>
+        <v>3.134762929206474</v>
       </c>
       <c r="J7" t="n">
-        <v>1.048938566301453</v>
+        <v>1.019352894822231</v>
       </c>
       <c r="K7" t="n">
-        <v>1.161818181818182</v>
+        <v>1.116136363636364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8610341989074309</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4043967427894126</v>
+        <v>0.4021834487057284</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2818156143833739</v>
+        <v>0.3126445693819487</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6264690634106227</v>
+        <v>0.611562486877584</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7283870502559665</v>
+        <v>0.7295791956551901</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4760979401476875</v>
+        <v>0.4598904090940031</v>
       </c>
       <c r="R7" t="n">
-        <v>1.339082139725227</v>
+        <v>0.8480325644504749</v>
       </c>
       <c r="S7" t="n">
         <v>0.3182978723404256</v>
       </c>
       <c r="T7" t="n">
-        <v>1.056767496799968</v>
+        <v>1.035422036240335</v>
       </c>
       <c r="U7" t="n">
-        <v>0.449239532053549</v>
+        <v>0.4392458463468074</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9629919676733151</v>
+        <v>0.9302956419792184</v>
       </c>
     </row>
     <row r="8">
@@ -1352,67 +1352,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.400269246288489</v>
+        <v>0.3510447631131994</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3872526173398051</v>
+        <v>0.2935132518113121</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3264897674405091</v>
+        <v>0.3145295915647153</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9219421781373777</v>
+        <v>0.7238698227789453</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1954298676186226</v>
+        <v>0.1693440428380187</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4207610627039687</v>
+        <v>0.225575975766199</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5708247978436658</v>
+        <v>0.5576280323450135</v>
       </c>
       <c r="I8" t="n">
-        <v>1.52397860416998</v>
+        <v>1.570431430159304</v>
       </c>
       <c r="J8" t="n">
-        <v>0.174694334528351</v>
+        <v>0.1607919212371887</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5958966033801218</v>
+        <v>0.5628460467356945</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4052432819690843</v>
+        <v>0.3898000624804748</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7416456366047339</v>
+        <v>0.7361024703163445</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3272131671362087</v>
+        <v>0.3636436673805056</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3758246570389798</v>
+        <v>0.3507943347984717</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3298962484655871</v>
+        <v>0.3143315603363742</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2506675954951817</v>
+        <v>0.2350435926594867</v>
       </c>
       <c r="R8" t="n">
-        <v>1.041692307692308</v>
+        <v>0.5836441402908469</v>
       </c>
       <c r="S8" t="n">
         <v>0.655735949853597</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6457668696791861</v>
+        <v>0.6223136835664762</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2527503851132071</v>
+        <v>0.2440093253718458</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3674216061746824</v>
+        <v>0.3165821038956151</v>
       </c>
     </row>
     <row r="9">
@@ -1422,67 +1422,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.382386029296322</v>
+        <v>1.311763453887925</v>
       </c>
       <c r="C9" t="n">
-        <v>1.786696689386563</v>
+        <v>1.539273491939142</v>
       </c>
       <c r="D9" t="n">
-        <v>1.734726688102894</v>
+        <v>1.724937862468931</v>
       </c>
       <c r="E9" t="n">
-        <v>2.264498299319728</v>
+        <v>1.923127637130802</v>
       </c>
       <c r="F9" t="n">
-        <v>2.042475850695029</v>
+        <v>2.320760320760321</v>
       </c>
       <c r="G9" t="n">
-        <v>2.085286967864342</v>
+        <v>1.39215457972943</v>
       </c>
       <c r="H9" t="n">
-        <v>1.33409495688039</v>
+        <v>1.309594113235846</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2007613758032355</v>
+        <v>0.1798228999675741</v>
       </c>
       <c r="J9" t="n">
-        <v>1.264661615164872</v>
+        <v>1.229199416538461</v>
       </c>
       <c r="K9" t="n">
-        <v>1.401130442462245</v>
+        <v>1.344917424710766</v>
       </c>
       <c r="L9" t="n">
-        <v>1.227109921512342</v>
+        <v>1.21405934889081</v>
       </c>
       <c r="M9" t="n">
-        <v>1.243973856345972</v>
+        <v>1.237419173116489</v>
       </c>
       <c r="N9" t="n">
-        <v>1.135669763784114</v>
+        <v>1.269507582270211</v>
       </c>
       <c r="O9" t="n">
-        <v>1.370601895046754</v>
+        <v>1.341016388194117</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66985388415852</v>
+        <v>1.679243004760246</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7054118901626233</v>
+        <v>0.6804082180743923</v>
       </c>
       <c r="R9" t="n">
-        <v>3.194886531093428</v>
+        <v>1.997560231777981</v>
       </c>
       <c r="S9" t="n">
         <v>1.146130986398445</v>
       </c>
       <c r="T9" t="n">
-        <v>1.10423160920613</v>
+        <v>1.081598280918779</v>
       </c>
       <c r="U9" t="n">
-        <v>1.185440383026651</v>
+        <v>1.158720436268795</v>
       </c>
       <c r="V9" t="n">
-        <v>1.625376804968202</v>
+        <v>1.577439351702761</v>
       </c>
     </row>
     <row r="10">
@@ -1492,67 +1492,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.245214443975655</v>
+        <v>1.180034009197559</v>
       </c>
       <c r="C10" t="n">
-        <v>1.363074538065111</v>
+        <v>1.168748437251381</v>
       </c>
       <c r="D10" t="n">
-        <v>1.45840357185366</v>
+        <v>1.449735751709338</v>
       </c>
       <c r="E10" t="n">
-        <v>1.496417305257303</v>
+        <v>1.257995045283335</v>
       </c>
       <c r="F10" t="n">
-        <v>2.502341763682591</v>
+        <v>2.85438203066601</v>
       </c>
       <c r="G10" t="n">
-        <v>2.462570676075941</v>
+        <v>1.641056233797847</v>
       </c>
       <c r="H10" t="n">
-        <v>1.085368840985442</v>
+        <v>1.064844624860022</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1041146904026434</v>
+        <v>0.09238103969927569</v>
       </c>
       <c r="J10" t="n">
-        <v>1.370136245905807</v>
+        <v>1.331195233669676</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6751938526021656</v>
+        <v>0.6474234485970427</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8333908125258657</v>
+        <v>0.8230401844532279</v>
       </c>
       <c r="M10" t="n">
-        <v>1.000059760289527</v>
+        <v>0.9944578663287431</v>
       </c>
       <c r="N10" t="n">
-        <v>1.379063660817215</v>
+        <v>1.551689189189189</v>
       </c>
       <c r="O10" t="n">
-        <v>1.177547160793899</v>
+        <v>1.150835540156737</v>
       </c>
       <c r="P10" t="n">
-        <v>1.032526194208399</v>
+        <v>1.035650806672136</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.650173337535455</v>
+        <v>1.595141700404858</v>
       </c>
       <c r="R10" t="n">
-        <v>1.759406278434941</v>
+        <v>1.067719132893497</v>
       </c>
       <c r="S10" t="n">
         <v>0.8131269349845202</v>
       </c>
       <c r="T10" t="n">
-        <v>1.050446280348462</v>
+        <v>1.028201945558987</v>
       </c>
       <c r="U10" t="n">
-        <v>1.198618643452721</v>
+        <v>1.171025250184015</v>
       </c>
       <c r="V10" t="n">
-        <v>1.357436725834333</v>
+        <v>1.315176337018864</v>
       </c>
     </row>
     <row r="11">
@@ -1562,22 +1562,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.753927076420059</v>
+        <v>6.752889714375429</v>
       </c>
       <c r="C11" t="n">
         <v>7.559470345466425</v>
       </c>
       <c r="D11" t="n">
-        <v>6.333641689793401</v>
+        <v>6.310947859634532</v>
       </c>
       <c r="E11" t="n">
-        <v>6.954047736220472</v>
+        <v>6.929835968217562</v>
       </c>
       <c r="F11" t="n">
-        <v>16.80084809934878</v>
+        <v>16.73655913978495</v>
       </c>
       <c r="G11" t="n">
-        <v>5.072092192424143</v>
+        <v>5.059505002632965</v>
       </c>
       <c r="H11" t="n">
         <v>5.208173486786019</v>
@@ -1589,19 +1589,19 @@
         <v>23.94938945962841</v>
       </c>
       <c r="K11" t="n">
-        <v>5.757510101841186</v>
+        <v>5.736521040327294</v>
       </c>
       <c r="L11" t="n">
         <v>5.713194133452754</v>
       </c>
       <c r="M11" t="n">
-        <v>5.429132900754983</v>
+        <v>5.428926280978457</v>
       </c>
       <c r="N11" t="n">
         <v>6.832401712407987</v>
       </c>
       <c r="O11" t="n">
-        <v>7.454612281146545</v>
+        <v>7.433442791986572</v>
       </c>
       <c r="P11" t="n">
         <v>6.603116816759277</v>
@@ -1610,19 +1610,19 @@
         <v>9.119144602851323</v>
       </c>
       <c r="R11" t="n">
-        <v>4.454412837345004</v>
+        <v>4.543666169895678</v>
       </c>
       <c r="S11" t="n">
         <v>4.966803545291917</v>
       </c>
       <c r="T11" t="n">
-        <v>5.322181610981106</v>
+        <v>5.317377102919573</v>
       </c>
       <c r="U11" t="n">
-        <v>5.966646661374944</v>
+        <v>5.970579574241676</v>
       </c>
       <c r="V11" t="n">
-        <v>7.720167087494267</v>
+        <v>7.73705299352471</v>
       </c>
     </row>
     <row r="12">
@@ -1632,67 +1632,67 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.710559152739006</v>
+        <v>2.724575957532719</v>
       </c>
       <c r="C12" t="n">
-        <v>2.652207870495652</v>
+        <v>2.637387268021659</v>
       </c>
       <c r="D12" t="n">
-        <v>3.152486935599083</v>
+        <v>3.178877187665732</v>
       </c>
       <c r="E12" t="n">
-        <v>2.712067331600627</v>
+        <v>2.732717117832889</v>
       </c>
       <c r="F12" t="n">
-        <v>7.209523095220238</v>
+        <v>7.286493565529856</v>
       </c>
       <c r="G12" t="n">
-        <v>2.71265391273633</v>
+        <v>2.725447557180591</v>
       </c>
       <c r="H12" t="n">
-        <v>1.554577369700243</v>
+        <v>1.572652368835575</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4576249650580672</v>
+        <v>0.4660990640072777</v>
       </c>
       <c r="J12" t="n">
-        <v>7.460976708582728</v>
+        <v>7.457465794170137</v>
       </c>
       <c r="K12" t="n">
-        <v>2.295448968502971</v>
+        <v>2.302482191053493</v>
       </c>
       <c r="L12" t="n">
-        <v>3.442153557017301</v>
+        <v>3.417016777752241</v>
       </c>
       <c r="M12" t="n">
-        <v>1.698394775046996</v>
+        <v>1.710295611561314</v>
       </c>
       <c r="N12" t="n">
-        <v>2.278586314099279</v>
+        <v>2.302949419458161</v>
       </c>
       <c r="O12" t="n">
-        <v>2.815409007193526</v>
+        <v>2.832021641566937</v>
       </c>
       <c r="P12" t="n">
-        <v>2.887323943661972</v>
+        <v>2.903209242618742</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.122023379997113</v>
+        <v>4.136849569106578</v>
       </c>
       <c r="R12" t="n">
-        <v>2.475897218093013</v>
+        <v>2.485187810063785</v>
       </c>
       <c r="S12" t="n">
-        <v>2.213923013923014</v>
+        <v>2.215482400488745</v>
       </c>
       <c r="T12" t="n">
-        <v>2.035079771485898</v>
+        <v>2.03541648847509</v>
       </c>
       <c r="U12" t="n">
-        <v>2.656760493051031</v>
+        <v>2.683777706455361</v>
       </c>
       <c r="V12" t="n">
-        <v>2.967812428321631</v>
+        <v>2.971610616028402</v>
       </c>
     </row>
     <row r="13">
@@ -1702,67 +1702,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8127375120088284</v>
+        <v>0.8170569055511515</v>
       </c>
       <c r="C13" t="n">
-        <v>0.687808146994135</v>
+        <v>0.7062766563558902</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8419610176520438</v>
+        <v>0.841370716793732</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4169166878549029</v>
+        <v>0.4141080538220555</v>
       </c>
       <c r="F13" t="n">
-        <v>1.35458279094988</v>
+        <v>1.37629241827355</v>
       </c>
       <c r="G13" t="n">
-        <v>1.247585149741632</v>
+        <v>1.261497344553964</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5706056747502019</v>
+        <v>0.5596775480884348</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3047080175082738</v>
+        <v>0.2735738162001172</v>
       </c>
       <c r="J13" t="n">
-        <v>2.025558171486651</v>
+        <v>2.079487316194112</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6635200499297862</v>
+        <v>0.6791815007531151</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7707827192833915</v>
+        <v>0.7841314849821466</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4164562086532019</v>
+        <v>0.4168806609961837</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8002977784721602</v>
+        <v>0.8103680989634522</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7196932041119001</v>
+        <v>0.725792751222571</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9893952890844195</v>
+        <v>0.9977190380079274</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.262645970632443</v>
+        <v>1.285107500985243</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9344386906741413</v>
+        <v>0.9484447004608295</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7219940326268067</v>
+        <v>0.7169477234401349</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5946433482685864</v>
+        <v>0.5975323850521742</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8265399354236623</v>
+        <v>0.8237590305659253</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9550869182152313</v>
+        <v>0.9673721308073796</v>
       </c>
     </row>
     <row r="14">
@@ -1772,67 +1772,67 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.306789510285301</v>
+        <v>0.3088813624976937</v>
       </c>
       <c r="C14" t="n">
-        <v>0.177423855945045</v>
+        <v>0.1787583109171192</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3197634753379644</v>
+        <v>0.3248990713339182</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2015372221133538</v>
+        <v>0.211115520457161</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2117599371510714</v>
+        <v>0.2135493689049653</v>
       </c>
       <c r="G14" t="n">
-        <v>0.433902218089413</v>
+        <v>0.4385477754923176</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3843351548269581</v>
+        <v>0.3975964793500338</v>
       </c>
       <c r="I14" t="n">
-        <v>6.718542912037054</v>
+        <v>6.455491870394198</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2422755373054542</v>
+        <v>0.2462733143025904</v>
       </c>
       <c r="K14" t="n">
-        <v>0.399498735089327</v>
+        <v>0.4039447731755424</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2700120756742251</v>
+        <v>0.2730744449515423</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1759341608883145</v>
+        <v>0.179402732455005</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1994682833503118</v>
+        <v>0.2018050408165778</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1570636814560269</v>
+        <v>0.1604695439375023</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2663802051200163</v>
+        <v>0.2689301908295143</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1816867930387836</v>
+        <v>0.1828853728873514</v>
       </c>
       <c r="R14" t="n">
         <v>0.2516399612861598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2069308799245105</v>
+        <v>0.215334513812076</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2632437247557817</v>
+        <v>0.2694694834046799</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1996646210931925</v>
+        <v>0.2044445442956661</v>
       </c>
       <c r="V14" t="n">
-        <v>0.318918023702527</v>
+        <v>0.3187097786846649</v>
       </c>
     </row>
     <row r="15">
@@ -1842,67 +1842,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.199513300359945</v>
+        <v>0.2013329143516641</v>
       </c>
       <c r="C15" t="n">
-        <v>0.214714674473261</v>
+        <v>0.2103507383966245</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4002018561993988</v>
+        <v>0.3956266318537859</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2198226071319301</v>
+        <v>0.2160073480992794</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2562321503204235</v>
+        <v>0.2521736958716725</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1548051325348927</v>
+        <v>0.1537109153387723</v>
       </c>
       <c r="H15" t="n">
-        <v>0.423093729517151</v>
+        <v>0.414070351758794</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1950447933377796</v>
+        <v>0.2296006329198273</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1792583198864139</v>
+        <v>0.177115100165232</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3653268760631722</v>
+        <v>0.3565017208761653</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2849947684795766</v>
+        <v>0.2804396272285251</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2774106098087721</v>
+        <v>0.2740739846752543</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2454944291891551</v>
+        <v>0.2400483818444027</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1894311247142398</v>
+        <v>0.1878250747658531</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3102307197352698</v>
+        <v>0.3063123985182268</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1567648438814083</v>
+        <v>0.1535684858947699</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1762955295335447</v>
+        <v>0.169729613657105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3205813125212921</v>
+        <v>0.3192571671525753</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2038865325681373</v>
+        <v>0.2007264482793026</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1174670296075076</v>
+        <v>0.1172680858223841</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2403575424288283</v>
+        <v>0.2431226809356208</v>
       </c>
     </row>
     <row r="16">
@@ -1912,67 +1912,67 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1639640107553314</v>
+        <v>0.1639099942460459</v>
       </c>
       <c r="C16" t="n">
         <v>0.08976468677825367</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1478945318514895</v>
+        <v>0.1481656075206919</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1895704877985512</v>
+        <v>0.1902208512231003</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05718317571979191</v>
+        <v>0.0574038645725032</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05404523081779959</v>
+        <v>0.05408907289462681</v>
       </c>
       <c r="H16" t="n">
         <v>0.3662265386294195</v>
       </c>
       <c r="I16" t="n">
-        <v>3.922600563036917</v>
+        <v>3.911923672854702</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0563427803447412</v>
+        <v>0.05641938654075736</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3108494026146287</v>
+        <v>0.3079357429718875</v>
       </c>
       <c r="L16" t="n">
         <v>0.1249331193151418</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1728837526155034</v>
+        <v>0.1729999868338794</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1139296451715107</v>
+        <v>0.1142177769752328</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09981176365391151</v>
+        <v>0.09988735165422256</v>
       </c>
       <c r="P16" t="n">
-        <v>0.127292131561075</v>
+        <v>0.127828138191573</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.06352498093058734</v>
+        <v>0.06188590143956128</v>
       </c>
       <c r="R16" t="n">
         <v>0.09338446788111218</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1671957671957672</v>
+        <v>0.168099173553719</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1797240535252961</v>
+        <v>0.1802271701492213</v>
       </c>
       <c r="U16" t="n">
-        <v>0.06313797480714774</v>
+        <v>0.06316805313624302</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1591634704385511</v>
+        <v>0.1583864343176073</v>
       </c>
     </row>
     <row r="17">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5522841354565341</v>
+        <v>0.5510794800300389</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8594750320102432</v>
+        <v>0.876844328502878</v>
       </c>
       <c r="D17" t="n">
         <v>1.130091989822403</v>
@@ -1994,55 +1994,55 @@
         <v>0.2685811343110501</v>
       </c>
       <c r="F17" t="n">
-        <v>1.133621294304685</v>
+        <v>1.125232190953841</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6486955770892119</v>
+        <v>0.6420305107093071</v>
       </c>
       <c r="H17" t="n">
-        <v>1.087686582356821</v>
+        <v>1.091399166870865</v>
       </c>
       <c r="I17" t="n">
-        <v>0.799404394301112</v>
+        <v>0.8058080841168677</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4174103521012494</v>
+        <v>0.4165512189027206</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5694048077481023</v>
+        <v>0.5779785809906292</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5222860267979218</v>
+        <v>0.5098586422374568</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2796756732969548</v>
+        <v>0.2790730885086781</v>
       </c>
       <c r="N17" t="n">
-        <v>0.409702509736045</v>
+        <v>0.3984008849471651</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7287380283392247</v>
+        <v>0.7274458490768142</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7135652729013725</v>
+        <v>0.7049972938841782</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3347560975609756</v>
+        <v>0.3450969827586207</v>
       </c>
       <c r="R17" t="n">
         <v>0.4973591549295774</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4586606035551881</v>
+        <v>0.4526580899870669</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5949912629367297</v>
+        <v>0.5882613527478923</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5571023173934672</v>
+        <v>0.5554577988526441</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6260637087711448</v>
+        <v>0.6272149596611497</v>
       </c>
     </row>
     <row r="18">
@@ -2052,67 +2052,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1931132407791</v>
+        <v>1.190135610799196</v>
       </c>
       <c r="C18" t="n">
-        <v>1.286777386490442</v>
+        <v>1.266797348813031</v>
       </c>
       <c r="D18" t="n">
-        <v>2.148546591384962</v>
+        <v>2.114911237845816</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7013295087812533</v>
+        <v>0.6965164425281456</v>
       </c>
       <c r="F18" t="n">
-        <v>4.45375379488233</v>
+        <v>4.434726776190191</v>
       </c>
       <c r="G18" t="n">
-        <v>1.486059632736724</v>
+        <v>1.495276338066095</v>
       </c>
       <c r="H18" t="n">
-        <v>4.054266645479104</v>
+        <v>4.040693424857787</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09472465671541266</v>
+        <v>0.09413218706921724</v>
       </c>
       <c r="J18" t="n">
-        <v>1.288483391608392</v>
+        <v>1.28557916418947</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6620953792933036</v>
+        <v>0.6517651025860504</v>
       </c>
       <c r="L18" t="n">
-        <v>2.324386624455876</v>
+        <v>2.333348246241947</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5977590379798587</v>
+        <v>0.5885532115694661</v>
       </c>
       <c r="N18" t="n">
-        <v>1.178239338123072</v>
+        <v>1.18542911648081</v>
       </c>
       <c r="O18" t="n">
-        <v>1.108864798124539</v>
+        <v>1.106068206336881</v>
       </c>
       <c r="P18" t="n">
-        <v>1.155825969385291</v>
+        <v>1.172786324786325</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.199014171287739</v>
+        <v>1.212413494241704</v>
       </c>
       <c r="R18" t="n">
-        <v>2.193943677394308</v>
+        <v>2.207792207792208</v>
       </c>
       <c r="S18" t="n">
-        <v>1.084466459466459</v>
+        <v>1.082300418036446</v>
       </c>
       <c r="T18" t="n">
-        <v>0.884186970732432</v>
+        <v>0.8833445843711446</v>
       </c>
       <c r="U18" t="n">
-        <v>1.939846858410305</v>
+        <v>1.932541671916411</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35127865737777</v>
+        <v>1.348348139229096</v>
       </c>
     </row>
     <row r="19">
@@ -2122,67 +2122,67 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.906764785823372</v>
+        <v>3.910655871981331</v>
       </c>
       <c r="C19" t="n">
-        <v>3.992642687277051</v>
+        <v>4.016085238013404</v>
       </c>
       <c r="D19" t="n">
-        <v>3.156662665066027</v>
+        <v>3.191116572762333</v>
       </c>
       <c r="E19" t="n">
-        <v>3.644012670030237</v>
+        <v>3.652983330056149</v>
       </c>
       <c r="F19" t="n">
-        <v>8.469339847853073</v>
+        <v>8.470144812537194</v>
       </c>
       <c r="G19" t="n">
-        <v>4.243347127867771</v>
+        <v>4.218167069006764</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3879731078428147</v>
+        <v>0.3902718507981666</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4668331361522663</v>
+        <v>0.4614023752882923</v>
       </c>
       <c r="J19" t="n">
-        <v>25.15300629581454</v>
+        <v>24.82973146487514</v>
       </c>
       <c r="K19" t="n">
-        <v>3.309166056293816</v>
+        <v>3.323916083916084</v>
       </c>
       <c r="L19" t="n">
-        <v>2.030722102206325</v>
+        <v>2.036900466893039</v>
       </c>
       <c r="M19" t="n">
-        <v>3.615571545441024</v>
+        <v>3.654824534642397</v>
       </c>
       <c r="N19" t="n">
-        <v>4.21087279794173</v>
+        <v>4.19727248971828</v>
       </c>
       <c r="O19" t="n">
-        <v>4.177055818484079</v>
+        <v>4.184106194056247</v>
       </c>
       <c r="P19" t="n">
-        <v>4.760540228353103</v>
+        <v>4.694194172197073</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.03263690750115</v>
+        <v>8.878552269102508</v>
       </c>
       <c r="R19" t="n">
-        <v>1.525925878372739</v>
+        <v>1.521317779771824</v>
       </c>
       <c r="S19" t="n">
-        <v>2.449971473398945</v>
+        <v>2.456058832465084</v>
       </c>
       <c r="T19" t="n">
-        <v>2.641701339257585</v>
+        <v>2.645868693041422</v>
       </c>
       <c r="U19" t="n">
-        <v>2.560158428267381</v>
+        <v>2.56797033457745</v>
       </c>
       <c r="V19" t="n">
-        <v>4.496159127577437</v>
+        <v>4.501790105841895</v>
       </c>
     </row>
     <row r="20">
@@ -5136,67 +5136,67 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3575939589389174</v>
+        <v>0.3424434885314094</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4791530706963434</v>
+        <v>0.4703638054147143</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4615113882555318</v>
+        <v>0.4377461530210976</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3092785767481709</v>
+        <v>0.3056966643263261</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4979480164158687</v>
+        <v>0.4865648606936886</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4468896861665321</v>
+        <v>0.4338944544991736</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4248624960430516</v>
+        <v>0.4297360850531582</v>
       </c>
       <c r="I62" t="n">
-        <v>0.06815479121245503</v>
+        <v>0.06671877014990146</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5152891684341464</v>
+        <v>0.4943265010352824</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2429473252811173</v>
+        <v>0.2335924557155601</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4105652301516844</v>
+        <v>0.3951448980777049</v>
       </c>
       <c r="M62" t="n">
-        <v>0.3234560739275036</v>
+        <v>0.3092344775092752</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3570998130361169</v>
+        <v>0.3391471431986612</v>
       </c>
       <c r="O62" t="n">
-        <v>0.381025147387234</v>
+        <v>0.3550331224335221</v>
       </c>
       <c r="P62" t="n">
-        <v>0.4550944365925735</v>
+        <v>0.4455386432647925</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.414993810145889</v>
+        <v>0.3686746987951807</v>
       </c>
       <c r="R62" t="n">
-        <v>0.3230948713717293</v>
+        <v>0.315820203892493</v>
       </c>
       <c r="S62" t="n">
-        <v>0.3974047734296459</v>
+        <v>0.3750399882333474</v>
       </c>
       <c r="T62" t="n">
-        <v>0.299735436315463</v>
+        <v>0.2870097488525183</v>
       </c>
       <c r="U62" t="n">
-        <v>0.3782884108050644</v>
+        <v>0.3597286310059517</v>
       </c>
       <c r="V62" t="n">
-        <v>0.3726570396499945</v>
+        <v>0.3571554245350142</v>
       </c>
     </row>
     <row r="63">
@@ -5206,67 +5206,67 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8923749809678833</v>
+        <v>0.9157828875681306</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8944652738429637</v>
+        <v>0.9022374700951894</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8813895547688864</v>
+        <v>0.9184022479581651</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7876903222513666</v>
+        <v>0.7896265736129791</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7671315475852676</v>
+        <v>0.7798855090358064</v>
       </c>
       <c r="G63" t="n">
-        <v>1.109594469658766</v>
+        <v>1.132130483232643</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8169102154975912</v>
+        <v>0.8050359274144441</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7527588394125924</v>
+        <v>0.7472933061214885</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6818797622497005</v>
+        <v>0.7032498877058463</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7349111682107132</v>
+        <v>0.7510630220197418</v>
       </c>
       <c r="L63" t="n">
-        <v>1.0714930115189</v>
+        <v>1.098216544396661</v>
       </c>
       <c r="M63" t="n">
-        <v>1.109617796301962</v>
+        <v>1.140352270101583</v>
       </c>
       <c r="N63" t="n">
-        <v>0.9964302089102349</v>
+        <v>1.028633456534247</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8594295832244547</v>
+        <v>0.9018821051237175</v>
       </c>
       <c r="P63" t="n">
-        <v>0.8358474220543186</v>
+        <v>0.8472657711980704</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9678106388134318</v>
+        <v>1.043833359622833</v>
       </c>
       <c r="R63" t="n">
-        <v>0.6315345255050905</v>
+        <v>0.6340128963317218</v>
       </c>
       <c r="S63" t="n">
-        <v>1.203517447805313</v>
+        <v>1.257518796992481</v>
       </c>
       <c r="T63" t="n">
-        <v>0.9165059772128948</v>
+        <v>0.9382793056026121</v>
       </c>
       <c r="U63" t="n">
-        <v>0.9943892434667567</v>
+        <v>1.027598646155347</v>
       </c>
       <c r="V63" t="n">
-        <v>0.857757693708515</v>
+        <v>0.8805632063978807</v>
       </c>
     </row>
     <row r="64">
@@ -5898,7 +5898,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Function:DNA binding region</t>
+          <t>Function:DNA binding</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -8062,67 +8062,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.757243999393996e-45</v>
+        <v>4.191969646706985e-40</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3745805455268862</v>
+        <v>0.5185277327409404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004414585252032601</v>
+        <v>0.004546356068459695</v>
       </c>
       <c r="E2" t="n">
-        <v>0.556771481308913</v>
+        <v>0.8514991206571452</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.766904029686704</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006342134211382476</v>
+        <v>0.1168108799507465</v>
       </c>
       <c r="H2" t="n">
-        <v>1.848848159780188e-08</v>
+        <v>2.272949210511958e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08646222680701865</v>
+        <v>0.05302296528822824</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007936895858577936</v>
+        <v>0.001357105787820545</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8361822190174308</v>
+        <v>0.8376276527469002</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>7.374137961855478e-05</v>
+        <v>9.374938066556774e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.8508107823450293</v>
       </c>
       <c r="O2" t="n">
-        <v>1.829857489523866e-08</v>
+        <v>3.474392909643704e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.955434420734545e-05</v>
+        <v>6.72909431172493e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.592375148333037e-07</v>
+        <v>1.07511282637105e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6967162507427893</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0.5360417276206617</v>
       </c>
       <c r="T2" t="n">
-        <v>3.145850972917629e-11</v>
+        <v>7.58544911091926e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07011722618867192</v>
+        <v>0.08545416280158095</v>
       </c>
       <c r="V2" t="n">
-        <v>1.170754550545135e-10</v>
+        <v>4.958340549277004e-10</v>
       </c>
     </row>
     <row r="3">
@@ -8135,64 +8135,64 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2.661017150548194e-29</v>
+        <v>1.035602825645741e-21</v>
       </c>
       <c r="D3" t="n">
-        <v>2.084630140815822e-30</v>
+        <v>2.554969654547301e-30</v>
       </c>
       <c r="E3" t="n">
-        <v>0.488773726443141</v>
+        <v>0.02052497316837013</v>
       </c>
       <c r="F3" t="n">
-        <v>9.024871409348593e-36</v>
+        <v>4.890506434331884e-41</v>
       </c>
       <c r="G3" t="n">
-        <v>2.672610274569942e-48</v>
+        <v>5.624141621717207e-19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5202406697744942</v>
+        <v>0.6416537623602919</v>
       </c>
       <c r="I3" t="n">
-        <v>1.159808325070342e-21</v>
+        <v>1.580077177103016e-27</v>
       </c>
       <c r="J3" t="n">
-        <v>1.089248212404656e-105</v>
+        <v>1.234225454910767e-101</v>
       </c>
       <c r="K3" t="n">
-        <v>7.556202558220776e-35</v>
+        <v>1.00605423686742e-31</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001812663052685287</v>
+        <v>0.0002409261961242379</v>
       </c>
       <c r="M3" t="n">
-        <v>4.250467436616579e-79</v>
+        <v>9.839957997650561e-78</v>
       </c>
       <c r="N3" t="n">
-        <v>3.037986261549061e-22</v>
+        <v>2.798643544010737e-30</v>
       </c>
       <c r="O3" t="n">
-        <v>4.174143357892801e-88</v>
+        <v>3.112523422092046e-84</v>
       </c>
       <c r="P3" t="n">
-        <v>1.086723312693925e-08</v>
+        <v>8.933040444013477e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.200889989391229e-36</v>
+        <v>1.188237661450377e-34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.439799189680534e-17</v>
+        <v>1.680063398835725e-05</v>
       </c>
       <c r="S3" t="n">
         <v>2.683273748982049e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>4.314200943619076e-55</v>
+        <v>1.282203312082789e-52</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003318044117249621</v>
+        <v>0.01155333880208861</v>
       </c>
       <c r="V3" t="n">
-        <v>3.302249314824401e-196</v>
+        <v>4.683558401620638e-186</v>
       </c>
     </row>
     <row r="4">
@@ -8202,67 +8202,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.26834861652306e-39</v>
+        <v>1.758559730205594e-29</v>
       </c>
       <c r="C4" t="n">
-        <v>0.650540456482983</v>
+        <v>0.7224829886992253</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03825763060264405</v>
+        <v>0.03884121418155316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01768138687353673</v>
+        <v>0.1198472678818925</v>
       </c>
       <c r="F4" t="n">
-        <v>8.879487758747344e-07</v>
+        <v>4.737417604955002e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.163206412676161e-11</v>
+        <v>7.701844972243951e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8859689526676715</v>
+        <v>0.8870385052571319</v>
       </c>
       <c r="I4" t="n">
-        <v>8.309755456665329e-12</v>
+        <v>9.895497929618756e-13</v>
       </c>
       <c r="J4" t="n">
-        <v>7.617124395983438e-13</v>
+        <v>2.846050733162781e-12</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08811636903139256</v>
+        <v>0.05593758967615536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5436506085771795</v>
+        <v>0.6464805263007115</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02448782285184908</v>
+        <v>0.0203197587606409</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4060336535448427</v>
+        <v>0.9385806395966618</v>
       </c>
       <c r="O4" t="n">
-        <v>1.385382701913e-07</v>
+        <v>5.099353545287833e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02952764658753481</v>
+        <v>0.02905980438037751</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5470807375732231</v>
+        <v>0.5515061830114534</v>
       </c>
       <c r="R4" t="n">
-        <v>6.926345150522622e-07</v>
+        <v>0.002988954734416357</v>
       </c>
       <c r="S4" t="n">
         <v>0.3918283821816115</v>
       </c>
       <c r="T4" t="n">
-        <v>6.731284823940791e-07</v>
+        <v>1.688390175527495e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>8.492220977453399e-09</v>
+        <v>4.855208781828905e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.26439980640345e-07</v>
+        <v>3.640104307539046e-06</v>
       </c>
     </row>
     <row r="5">
@@ -8275,64 +8275,64 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5.788358542159777e-34</v>
+        <v>5.444574518089138e-21</v>
       </c>
       <c r="D5" t="n">
-        <v>6.922103023687759e-14</v>
+        <v>1.076231914087329e-13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2320118615886032</v>
+        <v>0.8547259394305244</v>
       </c>
       <c r="F5" t="n">
-        <v>2.900470414805668e-38</v>
+        <v>1.290430298388434e-50</v>
       </c>
       <c r="G5" t="n">
-        <v>1.819515153419369e-213</v>
+        <v>1.012764536806835e-64</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1580657586867743</v>
+        <v>0.2040653964686536</v>
       </c>
       <c r="I5" t="n">
-        <v>3.743650614419144e-42</v>
+        <v>1.813737590455678e-47</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003687811403119404</v>
+        <v>4.508889865849906e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.204223533223549e-10</v>
+        <v>2.345806775308717e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>2.903402506559681e-05</v>
+        <v>8.395340183366821e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.12992475306162e-09</v>
+        <v>1.993955161398049e-19</v>
       </c>
       <c r="O5" t="n">
-        <v>1.718105390906469e-28</v>
+        <v>1.83438404171309e-25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.730431705170788e-19</v>
+        <v>2.180430130199354e-20</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.054246670171234e-05</v>
+        <v>0.0002663889438395741</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01877879668245643</v>
+        <v>0.0001844046544003223</v>
       </c>
       <c r="S5" t="n">
         <v>0.1928286471979087</v>
       </c>
       <c r="T5" t="n">
-        <v>2.761743523283051e-06</v>
+        <v>2.199385337281299e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.367760781602109e-202</v>
+        <v>1.035549544376239e-184</v>
       </c>
       <c r="V5" t="n">
-        <v>7.256252642558808e-115</v>
+        <v>7.09724990062492e-103</v>
       </c>
     </row>
     <row r="6">
@@ -8342,55 +8342,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.604488973188667e-90</v>
+        <v>7.357646490089537e-83</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3592998218649747</v>
+        <v>0.6504347193503508</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2523801812477685</v>
+        <v>0.2537237070731225</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.218827860250994</v>
+        <v>0.1014695145259603</v>
       </c>
       <c r="G6" t="n">
-        <v>2.511439751695145e-22</v>
+        <v>1.308668882158366e-16</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2413296029296017</v>
+        <v>0.2404628852615699</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1521407521661606</v>
+        <v>0.1369964740287422</v>
       </c>
       <c r="J6" t="n">
-        <v>5.613434514865097e-11</v>
+        <v>1.006091035867065e-10</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001673400437658945</v>
+        <v>0.001787188671006453</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06144299018419851</v>
+        <v>0.06152278112408031</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8408768577954671</v>
+        <v>0.681348702368207</v>
       </c>
       <c r="O6" t="n">
-        <v>3.118789910464237e-11</v>
+        <v>8.366247606382718e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03169059405518054</v>
+        <v>0.03141233934812499</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5389306045271286</v>
+        <v>0.534867323599718</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008337075779988178</v>
+        <v>0.0100986957717226</v>
       </c>
       <c r="S6" t="n">
         <v>0.7255889000242497</v>
@@ -8399,10 +8399,10 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>6.262771466439645e-20</v>
+        <v>3.105654176438006e-19</v>
       </c>
       <c r="V6" t="n">
-        <v>2.056094539394635e-27</v>
+        <v>1.893741669499892e-26</v>
       </c>
     </row>
     <row r="7">
@@ -8412,67 +8412,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2052963164516556</v>
+        <v>0.2541518267742127</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06175618537427757</v>
+        <v>0.006760120381444927</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1949704945735254</v>
+        <v>0.169424121478666</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08771727595320657</v>
+        <v>0.5297585476356532</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3330549499270012</v>
+        <v>0.7850987592867189</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003498785487311266</v>
+        <v>3.063023920095421e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4836505780285707</v>
+        <v>0.5611090888478545</v>
       </c>
       <c r="I7" t="n">
-        <v>2.90480143515585e-75</v>
+        <v>9.443883837176634e-70</v>
       </c>
       <c r="J7" t="n">
-        <v>0.544807270126469</v>
+        <v>0.820795964682921</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3558734835576975</v>
+        <v>0.4899735272299223</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6389209433542642</v>
+        <v>0.6386732060337188</v>
       </c>
       <c r="M7" t="n">
-        <v>2.993275823214826e-35</v>
+        <v>1.049350087071605e-35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.506843342696906e-17</v>
+        <v>1.339167731378841e-14</v>
       </c>
       <c r="O7" t="n">
-        <v>3.731231855135291e-08</v>
+        <v>6.110125814184202e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>0.115616631609806</v>
+        <v>0.1148222119799016</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001694345355368476</v>
+        <v>0.0008501118436730979</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5738021377736604</v>
+        <v>0.6951358389100561</v>
       </c>
       <c r="S7" t="n">
         <v>0.0003429768303310374</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6087319995922147</v>
+        <v>0.7590733706925342</v>
       </c>
       <c r="U7" t="n">
-        <v>6.086423351262588e-18</v>
+        <v>6.530606367648674e-19</v>
       </c>
       <c r="V7" t="n">
-        <v>0.503464122660688</v>
+        <v>0.1919149097534489</v>
       </c>
     </row>
     <row r="8">
@@ -8485,58 +8485,58 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.459585815549565e-45</v>
+        <v>9.64617789952892e-72</v>
       </c>
       <c r="D8" t="n">
-        <v>6.339548951708668e-67</v>
+        <v>7.047537934885951e-70</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2702425591707001</v>
+        <v>1.265692889061023e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.677592088871187e-164</v>
+        <v>5.363678752126694e-156</v>
       </c>
       <c r="G8" t="n">
-        <v>1.009789801895276e-73</v>
+        <v>4.706984905854929e-205</v>
       </c>
       <c r="H8" t="n">
-        <v>2.049848901976436e-05</v>
+        <v>7.536981799478024e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>2.686101381588081e-24</v>
+        <v>6.85837382781236e-19</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.884026854469364e-10</v>
+        <v>2.546200776793356e-12</v>
       </c>
       <c r="L8" t="n">
-        <v>6.485964575681954e-20</v>
+        <v>4.728403893413827e-21</v>
       </c>
       <c r="M8" t="n">
-        <v>1.668648437408357e-23</v>
+        <v>1.586163437577447e-24</v>
       </c>
       <c r="N8" t="n">
-        <v>4.380027887267618e-97</v>
+        <v>1.688334498926553e-75</v>
       </c>
       <c r="O8" t="n">
-        <v>4.048241622775022e-180</v>
+        <v>9.625765134639792e-200</v>
       </c>
       <c r="P8" t="n">
-        <v>1.072591204814154e-51</v>
+        <v>7.486069350970354e-54</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.184727818447142e-39</v>
+        <v>6.935581598407682e-43</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7393032268242699</v>
+        <v>4.123690956810886e-06</v>
       </c>
       <c r="S8" t="n">
         <v>9.975392196592845e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>9.971580524929335e-25</v>
+        <v>3.492012373174714e-28</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -8552,67 +8552,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.950268026347924e-69</v>
+        <v>6.684515466714857e-49</v>
       </c>
       <c r="C9" t="n">
-        <v>2.171047380189384e-06</v>
+        <v>0.0004401426644932568</v>
       </c>
       <c r="D9" t="n">
-        <v>7.61889738024218e-06</v>
+        <v>1.041079890069595e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>7.320453847712897e-16</v>
+        <v>1.463203081010157e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>1.107533361451398e-07</v>
+        <v>8.718263038371795e-10</v>
       </c>
       <c r="G9" t="n">
-        <v>6.642654296786557e-15</v>
+        <v>0.0005449248902375969</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1188486174850317</v>
+        <v>0.1460802278389632</v>
       </c>
       <c r="I9" t="n">
-        <v>2.455965123863621e-27</v>
+        <v>1.209277365886346e-30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002191383953872451</v>
+        <v>0.007608280073143157</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009458009997906025</v>
+        <v>0.0234455513403862</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2898029825045461</v>
+        <v>0.291440766147806</v>
       </c>
       <c r="M9" t="n">
-        <v>3.007828081889928e-06</v>
+        <v>5.14498625505862e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2250500766014755</v>
+        <v>0.02377175007184356</v>
       </c>
       <c r="O9" t="n">
-        <v>2.171244394451004e-07</v>
+        <v>1.515702681428881e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002806315182810638</v>
+        <v>0.0002059861901767449</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.037540912181058</v>
+        <v>0.02509097176687934</v>
       </c>
       <c r="R9" t="n">
-        <v>8.73069331691877e-11</v>
+        <v>0.0002255236475986306</v>
       </c>
       <c r="S9" t="n">
         <v>0.4763790470116894</v>
       </c>
       <c r="T9" t="n">
-        <v>0.189486352298185</v>
+        <v>0.2940817337641032</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005265232633515906</v>
+        <v>0.01618862299502569</v>
       </c>
       <c r="V9" t="n">
-        <v>6.689751574803184e-30</v>
+        <v>2.262921165025529e-26</v>
       </c>
     </row>
     <row r="10">
@@ -8622,67 +8622,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.367047155670271e-40</v>
+        <v>1.459026011588602e-23</v>
       </c>
       <c r="C10" t="n">
-        <v>0.005005321815200137</v>
+        <v>0.1514464229715926</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001084655614289636</v>
+        <v>0.001112796775504409</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001444019651900547</v>
+        <v>0.02971062979105461</v>
       </c>
       <c r="F10" t="n">
-        <v>2.263226767619685e-12</v>
+        <v>2.49338369402239e-15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.879315985276103e-29</v>
+        <v>1.154014138180329e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6072017412610681</v>
+        <v>0.7327416796988482</v>
       </c>
       <c r="I10" t="n">
-        <v>1.491975390925808e-48</v>
+        <v>2.066612229377462e-53</v>
       </c>
       <c r="J10" t="n">
-        <v>1.761564958903769e-06</v>
+        <v>1.467205703173138e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004086567790743428</v>
+        <v>0.001405240101816539</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3212558482150654</v>
+        <v>0.2829185371591024</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.9010907594795871</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0001582818446692124</v>
+        <v>3.260147688240101e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002498010078993849</v>
+        <v>0.009614806581678117</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7982084217690029</v>
+        <v>0.7972462363830242</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.005081389439598149</v>
+        <v>0.009038357883663492</v>
       </c>
       <c r="R10" t="n">
-        <v>7.158308297468307e-05</v>
+        <v>0.7169425022389075</v>
       </c>
       <c r="S10" t="n">
         <v>0.2620620168451334</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4561078512225853</v>
+        <v>0.6733212093911558</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0004735110743644679</v>
+        <v>0.002350699149614941</v>
       </c>
       <c r="V10" t="n">
-        <v>9.69405332727219e-15</v>
+        <v>4.543150274965865e-12</v>
       </c>
     </row>
     <row r="11">
@@ -8698,16 +8698,16 @@
         <v>5.599741945454359e-150</v>
       </c>
       <c r="D11" t="n">
-        <v>6.296426563481265e-103</v>
+        <v>2.017818887671931e-102</v>
       </c>
       <c r="E11" t="n">
-        <v>7.855850324605132e-114</v>
+        <v>2.456826398166339e-113</v>
       </c>
       <c r="F11" t="n">
-        <v>2.204835661371868e-154</v>
+        <v>9.288545836272427e-154</v>
       </c>
       <c r="G11" t="n">
-        <v>6.765924461677651e-145</v>
+        <v>2.356924729376516e-144</v>
       </c>
       <c r="H11" t="n">
         <v>1.931982162414275e-38</v>
@@ -8719,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>9.328948400417216e-64</v>
+        <v>1.90907185301215e-63</v>
       </c>
       <c r="L11" t="n">
         <v>1.596702111388078e-48</v>
@@ -8740,13 +8740,13 @@
         <v>2.125525105091828e-60</v>
       </c>
       <c r="R11" t="n">
-        <v>6.617694826241752e-24</v>
+        <v>2.743126111522419e-24</v>
       </c>
       <c r="S11" t="n">
         <v>3.845809083361065e-39</v>
       </c>
       <c r="T11" t="n">
-        <v>1.288335978148269e-296</v>
+        <v>4.788242333671328e-296</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -8765,64 +8765,64 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>7.015332206842697e-37</v>
+        <v>3.039282139684679e-36</v>
       </c>
       <c r="D12" t="n">
-        <v>5.210853095814576e-41</v>
+        <v>1.768503166875887e-41</v>
       </c>
       <c r="E12" t="n">
-        <v>2.38694610174849e-38</v>
+        <v>9.047896626832589e-39</v>
       </c>
       <c r="F12" t="n">
-        <v>6.852968440172627e-98</v>
+        <v>1.389797295779309e-98</v>
       </c>
       <c r="G12" t="n">
-        <v>2.178293799155756e-64</v>
+        <v>9.901815020465242e-65</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0004089261188246691</v>
+        <v>0.000301471468622297</v>
       </c>
       <c r="I12" t="n">
-        <v>9.04227476204544e-15</v>
+        <v>6.932004076047425e-14</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4.087942231899916e-19</v>
+        <v>4.445221060468488e-19</v>
       </c>
       <c r="L12" t="n">
-        <v>6.555955341992521e-28</v>
+        <v>2.011693273962493e-27</v>
       </c>
       <c r="M12" t="n">
-        <v>1.948757461517763e-67</v>
+        <v>4.702131331118735e-69</v>
       </c>
       <c r="N12" t="n">
-        <v>9.371037315529356e-39</v>
+        <v>1.710887344688802e-39</v>
       </c>
       <c r="O12" t="n">
-        <v>9.057516150230405e-150</v>
+        <v>6.80949353406275e-151</v>
       </c>
       <c r="P12" t="n">
-        <v>3.491838841699617e-32</v>
+        <v>3.007212873164577e-32</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.109762095681639e-28</v>
+        <v>2.615424544914415e-28</v>
       </c>
       <c r="R12" t="n">
-        <v>2.462553482915798e-14</v>
+        <v>1.725495141146475e-14</v>
       </c>
       <c r="S12" t="n">
-        <v>1.212347656286374e-11</v>
+        <v>1.122168734545049e-11</v>
       </c>
       <c r="T12" t="n">
-        <v>1.140514671530009e-61</v>
+        <v>1.748366805019206e-61</v>
       </c>
       <c r="U12" t="n">
-        <v>4.389517976272448e-182</v>
+        <v>3.922336874852418e-185</v>
       </c>
       <c r="V12" t="n">
-        <v>1.641932807415027e-317</v>
+        <v>2.67004557098219e-316</v>
       </c>
     </row>
     <row r="13">
@@ -8832,67 +8832,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.425403939384171e-75</v>
+        <v>1.642165467596558e-71</v>
       </c>
       <c r="C13" t="n">
-        <v>2.972159892342417e-06</v>
+        <v>1.33158311049945e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04354528349143453</v>
+        <v>0.04285216972043782</v>
       </c>
       <c r="E13" t="n">
-        <v>1.544870177020155e-25</v>
+        <v>8.448640292831059e-26</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0005556024997196593</v>
+        <v>0.000271146911626429</v>
       </c>
       <c r="G13" t="n">
-        <v>1.62322708971639e-06</v>
+        <v>5.123398603770666e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>4.377897567902572e-06</v>
+        <v>2.37940404714896e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>4.928538774112528e-52</v>
+        <v>2.018514132062511e-59</v>
       </c>
       <c r="J13" t="n">
-        <v>2.264736063711078e-66</v>
+        <v>5.064783522184432e-71</v>
       </c>
       <c r="K13" t="n">
-        <v>4.181948428027256e-06</v>
+        <v>1.638153342992587e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01712413516054833</v>
+        <v>0.02536802915858643</v>
       </c>
       <c r="M13" t="n">
-        <v>8.930326567124662e-167</v>
+        <v>9.279180978662121e-166</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0003556770009264105</v>
+        <v>0.0007774460268515824</v>
       </c>
       <c r="O13" t="n">
-        <v>5.50696180054287e-16</v>
+        <v>3.340281131998489e-15</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9328617706844342</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04041867157460474</v>
+        <v>0.02635451366944013</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5558076001155128</v>
+        <v>0.6296677941350401</v>
       </c>
       <c r="S13" t="n">
-        <v>0.005907851265676477</v>
+        <v>0.004815610510949953</v>
       </c>
       <c r="T13" t="n">
-        <v>2.522151701024197e-32</v>
+        <v>1.023547863150496e-31</v>
       </c>
       <c r="U13" t="n">
-        <v>5.149103329182366e-09</v>
+        <v>3.123583736232033e-09</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0873024295896794</v>
+        <v>0.2163041005077395</v>
       </c>
     </row>
     <row r="14">
@@ -8905,58 +8905,58 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>9.640045110386117e-99</v>
+        <v>1.081078831891298e-97</v>
       </c>
       <c r="D14" t="n">
-        <v>3.547159717297005e-54</v>
+        <v>5.523693906920479e-53</v>
       </c>
       <c r="E14" t="n">
-        <v>2.121096767282932e-57</v>
+        <v>2.240739151934056e-55</v>
       </c>
       <c r="F14" t="n">
-        <v>1.14727717831999e-101</v>
+        <v>2.845857618812853e-100</v>
       </c>
       <c r="G14" t="n">
-        <v>1.884182194267125e-73</v>
+        <v>7.323583405678515e-72</v>
       </c>
       <c r="H14" t="n">
-        <v>3.358858047450973e-12</v>
+        <v>1.329632426670114e-11</v>
       </c>
       <c r="I14" t="n">
-        <v>1.171216525480822e-279</v>
+        <v>4.590179652730707e-269</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.215277152137581e-26</v>
+        <v>1.285595674791742e-25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27050944283547e-31</v>
+        <v>2.61652767128609e-31</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.510374057470518e-128</v>
+        <v>1.289194593847704e-126</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09687251613622e-56</v>
+        <v>7.373938733086351e-56</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.558850613661604e-48</v>
+        <v>3.152147095724329e-48</v>
       </c>
       <c r="R14" t="n">
         <v>1.066136992865749e-28</v>
       </c>
       <c r="S14" t="n">
-        <v>1.368995474682914e-31</v>
+        <v>1.581231105434952e-30</v>
       </c>
       <c r="T14" t="n">
-        <v>6.981221608235595e-161</v>
+        <v>1.263486894830976e-156</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -8975,58 +8975,58 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.059396275582396e-51</v>
+        <v>2.988550577425385e-53</v>
       </c>
       <c r="D15" t="n">
-        <v>1.782430889854577e-28</v>
+        <v>2.986613403817365e-29</v>
       </c>
       <c r="E15" t="n">
-        <v>7.667694986043884e-34</v>
+        <v>8.082986419723743e-35</v>
       </c>
       <c r="F15" t="n">
-        <v>6.456308324745657e-53</v>
+        <v>1.201648293723896e-54</v>
       </c>
       <c r="G15" t="n">
-        <v>1.918350576216578e-156</v>
+        <v>4.021888529721535e-160</v>
       </c>
       <c r="H15" t="n">
-        <v>1.492610181504186e-05</v>
+        <v>8.215652666210536e-06</v>
       </c>
       <c r="I15" t="n">
-        <v>1.111082620805024e-141</v>
+        <v>3.335842925933615e-122</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.216508292087764e-20</v>
+        <v>1.977914885732203e-21</v>
       </c>
       <c r="L15" t="n">
-        <v>1.561451638378471e-19</v>
+        <v>4.423996779695064e-20</v>
       </c>
       <c r="M15" t="n">
-        <v>1.050761099465787e-149</v>
+        <v>6.733893430718413e-154</v>
       </c>
       <c r="N15" t="n">
-        <v>1.042708370933512e-69</v>
+        <v>2.31954089572619e-72</v>
       </c>
       <c r="O15" t="n">
-        <v>2.49573821813027e-209</v>
+        <v>1.128517434774377e-213</v>
       </c>
       <c r="P15" t="n">
-        <v>2.311958566503305e-30</v>
+        <v>4.727008397243953e-31</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.513852988197977e-35</v>
+        <v>3.481688670157317e-36</v>
       </c>
       <c r="R15" t="n">
-        <v>2.66207351005627e-19</v>
+        <v>1.578321660506026e-20</v>
       </c>
       <c r="S15" t="n">
-        <v>4.204875580649081e-13</v>
+        <v>2.275064085178829e-13</v>
       </c>
       <c r="T15" t="n">
-        <v>3.285260578595471e-105</v>
+        <v>1.446692221413486e-108</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -9048,10 +9048,10 @@
         <v>1.019960655391571e-173</v>
       </c>
       <c r="D16" t="n">
-        <v>4.414543321080424e-151</v>
+        <v>5.60306108946358e-151</v>
       </c>
       <c r="E16" t="n">
-        <v>2.140126879500343e-52</v>
+        <v>3.635597396550692e-52</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -9063,40 +9063,40 @@
         <v>5.265901927156961e-08</v>
       </c>
       <c r="I16" t="n">
-        <v>1.335221338100289e-143</v>
+        <v>5.673165960477917e-143</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>8.396554048220097e-29</v>
+        <v>4.185253330024328e-29</v>
       </c>
       <c r="L16" t="n">
         <v>8.186340812235679e-58</v>
       </c>
       <c r="M16" t="n">
-        <v>3.619871759715911e-313</v>
+        <v>7.327196242367296e-313</v>
       </c>
       <c r="N16" t="n">
-        <v>2.515053863341106e-216</v>
+        <v>1.035232379203682e-215</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.293463126360595e-119</v>
+        <v>1.85257913834642e-118</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.694535109559707e-100</v>
+        <v>4.142887182788078e-101</v>
       </c>
       <c r="R16" t="n">
         <v>1.200636934605185e-43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.544105943100225e-29</v>
+        <v>4.443766023554749e-29</v>
       </c>
       <c r="T16" t="n">
-        <v>4.996668037353943e-174</v>
+        <v>2.527638677523179e-173</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.692801939137449e-265</v>
+        <v>1.059541236970832e-266</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2332769089966231</v>
+        <v>0.3082602865690932</v>
       </c>
       <c r="D17" t="n">
         <v>0.2555628375777011</v>
@@ -9124,55 +9124,55 @@
         <v>1.521479066045183e-14</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2971709245803351</v>
+        <v>0.3275875446234507</v>
       </c>
       <c r="G17" t="n">
-        <v>1.278541943137124e-09</v>
+        <v>6.903495133823645e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6220897792979492</v>
+        <v>0.5657339680782331</v>
       </c>
       <c r="I17" t="n">
-        <v>0.003176947007433193</v>
+        <v>0.004596249646805873</v>
       </c>
       <c r="J17" t="n">
-        <v>1.17516147769067e-48</v>
+        <v>7.113877058422333e-49</v>
       </c>
       <c r="K17" t="n">
-        <v>6.849559762495441e-08</v>
+        <v>1.542126471782377e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>4.840342975050775e-05</v>
+        <v>3.362932635859754e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.10112201537423e-71</v>
+        <v>2.261904849277267e-71</v>
       </c>
       <c r="N17" t="n">
-        <v>5.547499105552634e-15</v>
+        <v>1.0191666038646e-15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.410688043300336e-06</v>
+        <v>1.376698467006425e-06</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0100546466917296</v>
+        <v>0.00731657499499608</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.012956623006787e-09</v>
+        <v>2.80330948515535e-09</v>
       </c>
       <c r="R17" t="n">
         <v>7.388777894240771e-05</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0003073504004046423</v>
+        <v>0.0003059908203407788</v>
       </c>
       <c r="T17" t="n">
-        <v>4.310567255990313e-14</v>
+        <v>1.233905186668237e-14</v>
       </c>
       <c r="U17" t="n">
-        <v>2.277645594098038e-32</v>
+        <v>1.415406877222674e-32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.121024423610828e-37</v>
+        <v>1.854641739878523e-37</v>
       </c>
     </row>
     <row r="18">
@@ -9182,67 +9182,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.821481875777727e-60</v>
+        <v>5.981941732621525e-58</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000299498059007494</v>
+        <v>0.0007335943610479371</v>
       </c>
       <c r="D18" t="n">
-        <v>1.27151234261612e-25</v>
+        <v>1.956574469005278e-24</v>
       </c>
       <c r="E18" t="n">
-        <v>5.512166518682746e-06</v>
+        <v>4.24400842218515e-06</v>
       </c>
       <c r="F18" t="n">
-        <v>3.70362431762855e-78</v>
+        <v>1.540219800306667e-77</v>
       </c>
       <c r="G18" t="n">
-        <v>2.456831911406854e-18</v>
+        <v>7.28449405015806e-19</v>
       </c>
       <c r="H18" t="n">
-        <v>9.162738354548374e-38</v>
+        <v>1.598142187330369e-37</v>
       </c>
       <c r="I18" t="n">
-        <v>7.443710119750519e-154</v>
+        <v>5.663336808096593e-153</v>
       </c>
       <c r="J18" t="n">
-        <v>5.289982519449891e-09</v>
+        <v>8.00676021749555e-09</v>
       </c>
       <c r="K18" t="n">
-        <v>5.708772978226516e-06</v>
+        <v>2.359512650161752e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>2.783868314340535e-19</v>
+        <v>2.329714287922412e-19</v>
       </c>
       <c r="M18" t="n">
-        <v>1.156138123101682e-37</v>
+        <v>1.513563429224884e-39</v>
       </c>
       <c r="N18" t="n">
-        <v>0.00509463187484591</v>
+        <v>0.003776983605790517</v>
       </c>
       <c r="O18" t="n">
-        <v>0.008621677405893206</v>
+        <v>0.01063250949094481</v>
       </c>
       <c r="P18" t="n">
-        <v>0.07152424580291758</v>
+        <v>0.04850552504333704</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1017309313303593</v>
+        <v>0.07985340144510664</v>
       </c>
       <c r="R18" t="n">
-        <v>3.400863476670947e-12</v>
+        <v>2.219392945794207e-12</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5183297945510639</v>
+        <v>0.517665879309534</v>
       </c>
       <c r="T18" t="n">
-        <v>0.002149799519960722</v>
+        <v>0.002112151178687176</v>
       </c>
       <c r="U18" t="n">
-        <v>7.952125188511654e-115</v>
+        <v>2.888668082507345e-113</v>
       </c>
       <c r="V18" t="n">
-        <v>3.086198435793996e-33</v>
+        <v>1.032776892515858e-32</v>
       </c>
     </row>
     <row r="19">
@@ -9255,61 +9255,61 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3.56728668291104e-104</v>
+        <v>3.797301616689484e-105</v>
       </c>
       <c r="D19" t="n">
-        <v>1.298493242880392e-64</v>
+        <v>6.925315758693883e-66</v>
       </c>
       <c r="E19" t="n">
-        <v>3.373212383477977e-77</v>
+        <v>2.218455052937989e-77</v>
       </c>
       <c r="F19" t="n">
-        <v>2.051446331116703e-168</v>
+        <v>6.736832573379928e-169</v>
       </c>
       <c r="G19" t="n">
-        <v>2.949164568002915e-241</v>
+        <v>1.006445249641973e-239</v>
       </c>
       <c r="H19" t="n">
-        <v>3.680215967824598e-18</v>
+        <v>5.896747291611299e-18</v>
       </c>
       <c r="I19" t="n">
-        <v>6.244590734153231e-22</v>
+        <v>8.815290050111328e-23</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.730897700249037e-57</v>
+        <v>5.957765373088456e-58</v>
       </c>
       <c r="L19" t="n">
-        <v>1.807835200147612e-14</v>
+        <v>1.357955606788631e-14</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.732437242443759e-173</v>
+        <v>4.05601896231534e-172</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.079747296327335e-106</v>
+        <v>5.891924786640639e-105</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.282836315644825e-103</v>
+        <v>2.891986322179522e-102</v>
       </c>
       <c r="R19" t="n">
-        <v>1.660501948837555e-05</v>
+        <v>2.038463094416017e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>2.478306576383011e-19</v>
+        <v>2.358402669336906e-19</v>
       </c>
       <c r="T19" t="n">
-        <v>8.759374684480924e-152</v>
+        <v>2.653379348786619e-152</v>
       </c>
       <c r="U19" t="n">
-        <v>2.741450247283822e-227</v>
+        <v>2.452699753888816e-229</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -12265,61 +12265,61 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1.741590066868345e-31</v>
+        <v>1.478329673992079e-32</v>
       </c>
       <c r="D62" t="n">
-        <v>3.192508293677326e-31</v>
+        <v>6.937506441063417e-35</v>
       </c>
       <c r="E62" t="n">
-        <v>8.748801200571167e-65</v>
+        <v>2.426272426818676e-65</v>
       </c>
       <c r="F62" t="n">
-        <v>1.230793482259451e-29</v>
+        <v>3.013092848500385e-31</v>
       </c>
       <c r="G62" t="n">
-        <v>1.784344783412957e-96</v>
+        <v>1.487770096008188e-102</v>
       </c>
       <c r="H62" t="n">
-        <v>1.274138544764497e-13</v>
+        <v>2.649553239266038e-13</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>2.99500245157638e-81</v>
+        <v>2.950486849951683e-90</v>
       </c>
       <c r="K62" t="n">
-        <v>6.744519154023336e-63</v>
+        <v>1.375552495509151e-65</v>
       </c>
       <c r="L62" t="n">
-        <v>1.289058119042588e-21</v>
+        <v>4.677189644108584e-23</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.923307937419345e-88</v>
+        <v>1.027931805745641e-95</v>
       </c>
       <c r="O62" t="n">
-        <v>7.734069431749949e-181</v>
+        <v>1.612039747576548e-203</v>
       </c>
       <c r="P62" t="n">
-        <v>5.019116549381676e-28</v>
+        <v>3.933594805891133e-29</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.029349368421288e-17</v>
+        <v>6.426927179066018e-21</v>
       </c>
       <c r="R62" t="n">
-        <v>5.543257751626145e-33</v>
+        <v>1.30081471514798e-33</v>
       </c>
       <c r="S62" t="n">
-        <v>1.251584876243875e-19</v>
+        <v>8.594982324488484e-22</v>
       </c>
       <c r="T62" t="n">
-        <v>3.338141338382873e-207</v>
+        <v>2.49203980092903e-218</v>
       </c>
       <c r="U62" t="n">
-        <v>1.878749188264556e-241</v>
+        <v>6.637975330385617e-263</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -12332,67 +12332,67 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>8.508645382669255e-39</v>
+        <v>5.867744726005447e-24</v>
       </c>
       <c r="C63" t="n">
-        <v>0.06071723024267245</v>
+        <v>0.08449513252567661</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0471735873428983</v>
+        <v>0.1862860735827002</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0001758928238202873</v>
+        <v>0.0001816972849667775</v>
       </c>
       <c r="F63" t="n">
-        <v>4.365124942882688e-06</v>
+        <v>1.678516750586253e-05</v>
       </c>
       <c r="G63" t="n">
-        <v>0.004613366439678355</v>
+        <v>0.0006885622001664537</v>
       </c>
       <c r="H63" t="n">
-        <v>0.06919777810795517</v>
+        <v>0.04863075704784307</v>
       </c>
       <c r="I63" t="n">
-        <v>1.717195380317091e-13</v>
+        <v>3.611090408076691e-14</v>
       </c>
       <c r="J63" t="n">
-        <v>3.703838079972796e-32</v>
+        <v>1.383127613066377e-27</v>
       </c>
       <c r="K63" t="n">
-        <v>4.93102484736739e-05</v>
+        <v>0.0001513749054726081</v>
       </c>
       <c r="L63" t="n">
-        <v>0.430824799802027</v>
+        <v>0.2941942487788105</v>
       </c>
       <c r="M63" t="n">
-        <v>6.608240500568851e-05</v>
+        <v>4.352100807820039e-07</v>
       </c>
       <c r="N63" t="n">
-        <v>0.9429070612984808</v>
+        <v>0.5674075796556248</v>
       </c>
       <c r="O63" t="n">
-        <v>1.523248018387874e-06</v>
+        <v>0.0009806529194518062</v>
       </c>
       <c r="P63" t="n">
-        <v>0.007935314808855443</v>
+        <v>0.01417812534093546</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.7424496867655377</v>
+        <v>0.6734003301000562</v>
       </c>
       <c r="R63" t="n">
-        <v>1.436764623618464e-07</v>
+        <v>1.636780227390457e-07</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0643843211595113</v>
+        <v>0.02195927105921613</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01788104674279171</v>
+        <v>0.08129395987399302</v>
       </c>
       <c r="U63" t="n">
-        <v>0.844915962620854</v>
+        <v>0.3296636316596163</v>
       </c>
       <c r="V63" t="n">
-        <v>1.051704470769406e-14</v>
+        <v>1.352684473076227e-10</v>
       </c>
     </row>
     <row r="64">
@@ -13028,7 +13028,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Function:DNA binding region</t>
+          <t>Function:DNA binding</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -15398,67 +15398,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.742365635417903e-45</v>
+        <v>6.081308079025627e-40</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4883771669527758</v>
+        <v>0.6513214203941081</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008420412610358479</v>
+        <v>0.008556554805556522</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6827078877954529</v>
+        <v>0.9891772108016181</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.8875406186261855</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008595260839110462</v>
+        <v>0.1522977295560366</v>
       </c>
       <c r="H2" t="n">
-        <v>1.190196002858496e-07</v>
+        <v>1.463211054267073e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1127292324192775</v>
+        <v>0.06913120790743682</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00115140883582187</v>
+        <v>0.00194141522424328</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9569640950977264</v>
+        <v>0.9586183136992302</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001029451349190659</v>
+        <v>0.0001287491494473797</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.9224580061214528</v>
       </c>
       <c r="O2" t="n">
-        <v>3.089759367556693e-08</v>
+        <v>5.771975317633896e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001666069175199205</v>
+        <v>0.0001611852823506204</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.522627871865493e-06</v>
+        <v>3.572149068265102e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8344392305407825</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0.7435403751624357</v>
       </c>
       <c r="T2" t="n">
-        <v>7.043970656750344e-11</v>
+        <v>1.6984809965754e-10</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08597707496944296</v>
+        <v>0.1035503384536804</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7998166971067e-10</v>
+        <v>7.401580819935238e-10</v>
       </c>
     </row>
     <row r="3">
@@ -15471,64 +15471,64 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7130297906654e-28</v>
+        <v>5.925949502306187e-21</v>
       </c>
       <c r="D3" t="n">
-        <v>1.341980653150185e-29</v>
+        <v>1.644761715114825e-29</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6065505279957051</v>
+        <v>0.03583173281935802</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1970783677527e-35</v>
+        <v>3.35814775157456e-40</v>
       </c>
       <c r="G3" t="n">
-        <v>1.251267537639564e-47</v>
+        <v>2.145505877914342e-18</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7834111585425378</v>
+        <v>0.8812045003081342</v>
       </c>
       <c r="I3" t="n">
-        <v>2.778145522842913e-21</v>
+        <v>4.398593222746233e-27</v>
       </c>
       <c r="J3" t="n">
-        <v>6.599562698687033e-105</v>
+        <v>7.477954226812297e-101</v>
       </c>
       <c r="K3" t="n">
-        <v>7.782888634967401e-34</v>
+        <v>8.949897516761774e-31</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000444534034349011</v>
+        <v>0.0005908428143046787</v>
       </c>
       <c r="M3" t="n">
-        <v>1.90347019987612e-78</v>
+        <v>4.406589885904382e-77</v>
       </c>
       <c r="N3" t="n">
-        <v>1.422329931543424e-21</v>
+        <v>1.310274022877754e-29</v>
       </c>
       <c r="O3" t="n">
-        <v>2.047317932680755e-87</v>
+        <v>1.526618630835623e-83</v>
       </c>
       <c r="P3" t="n">
-        <v>3.292132388455125e-08</v>
+        <v>2.788191411313297e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.12446971733906e-35</v>
+        <v>1.019903992744907e-33</v>
       </c>
       <c r="R3" t="n">
-        <v>7.414965826854752e-17</v>
+        <v>4.80684805777999e-05</v>
       </c>
       <c r="S3" t="n">
         <v>1.625748212618536e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.116012843775071e-54</v>
+        <v>6.288901959263202e-52</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004681623891461793</v>
+        <v>0.01586658528820169</v>
       </c>
       <c r="V3" t="n">
-        <v>1.79016673382586e-195</v>
+        <v>2.538981659825925e-185</v>
       </c>
     </row>
     <row r="4">
@@ -15538,67 +15538,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.611505582217468e-39</v>
+        <v>2.415088696149015e-29</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7791356629970609</v>
+        <v>0.8652993934420954</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05970509018291419</v>
+        <v>0.06061583425302993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0308675058978692</v>
+        <v>0.1815333616446312</v>
       </c>
       <c r="F4" t="n">
-        <v>2.286468097877441e-06</v>
+        <v>1.318794630568555e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.072057961683196e-11</v>
+        <v>0.0001259190527208138</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.585008911178757e-11</v>
+        <v>1.923087333491947e-12</v>
       </c>
       <c r="J4" t="n">
-        <v>1.743475139525098e-12</v>
+        <v>6.514293900350365e-12</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1315360291338179</v>
+        <v>0.08599360800961198</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7166788283376772</v>
+        <v>0.7927082643925392</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03152807192175569</v>
+        <v>0.02616168940432517</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5038730881339615</v>
+        <v>0.9966371740047028</v>
       </c>
       <c r="O4" t="n">
-        <v>2.229600285891235e-07</v>
+        <v>8.206772111947607e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04905399352445299</v>
+        <v>0.0482767717932078</v>
       </c>
       <c r="Q4" t="n">
         <v>0.7175658996576265</v>
       </c>
       <c r="R4" t="n">
-        <v>2.098275148540677e-06</v>
+        <v>0.005497541743658656</v>
       </c>
       <c r="S4" t="n">
         <v>0.6208972825339383</v>
       </c>
       <c r="T4" t="n">
-        <v>1.35945556248216e-06</v>
+        <v>3.344311309217923e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.391239841674815e-08</v>
+        <v>7.693638531205803e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>4.605933973418566e-07</v>
+        <v>4.999076582353623e-06</v>
       </c>
     </row>
     <row r="5">
@@ -15611,64 +15611,64 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4.586160998788131e-33</v>
+        <v>2.803955876815906e-20</v>
       </c>
       <c r="D5" t="n">
-        <v>2.742217736307074e-13</v>
+        <v>4.26353412119211e-13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3268954701706438</v>
+        <v>0.9891772108016181</v>
       </c>
       <c r="F5" t="n">
-        <v>2.13391751946417e-37</v>
+        <v>9.493880052429189e-50</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6772865828885e-212</v>
+        <v>5.215737364555202e-64</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2960140571770501</v>
+        <v>0.368749751513532</v>
       </c>
       <c r="I5" t="n">
-        <v>1.329641425121282e-41</v>
+        <v>6.671963279176242e-47</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0007913428635860389</v>
+        <v>0.0001080036409726838</v>
       </c>
       <c r="L5" t="n">
-        <v>5.637955632819342e-10</v>
+        <v>1.098264081167263e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>4.211978284164044e-05</v>
+        <v>1.217915547727863e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.062690778035445e-09</v>
+        <v>8.929451374956482e-19</v>
       </c>
       <c r="O5" t="n">
-        <v>5.056138721810466e-28</v>
+        <v>5.106528548552656e-25</v>
       </c>
       <c r="P5" t="n">
-        <v>9.901914757366173e-19</v>
+        <v>1.247690574502963e-19</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002391249761609326</v>
+        <v>0.0006859515303869033</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03170845997201659</v>
+        <v>0.000395701654234025</v>
       </c>
       <c r="S5" t="n">
         <v>0.3484447484453437</v>
       </c>
       <c r="T5" t="n">
-        <v>5.367161941474609e-06</v>
+        <v>4.719514369582787e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.46061046542321e-201</v>
+        <v>7.618685933625189e-184</v>
       </c>
       <c r="V5" t="n">
-        <v>2.491313407278524e-114</v>
+        <v>2.358118515368925e-102</v>
       </c>
     </row>
     <row r="6">
@@ -15678,55 +15678,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.75022480433514e-90</v>
+        <v>1.329539628910916e-82</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4806218396375635</v>
+        <v>0.7881738363892485</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3170141301039043</v>
+        <v>0.3171442442229303</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2927177870889919</v>
+        <v>0.1412345945428907</v>
       </c>
       <c r="G6" t="n">
-        <v>9.238510515164281e-22</v>
+        <v>4.348157898784248e-16</v>
       </c>
       <c r="H6" t="n">
-        <v>0.421304222063542</v>
+        <v>0.4197911386769779</v>
       </c>
       <c r="I6" t="n">
-        <v>0.188801174374874</v>
+        <v>0.1720809368897615</v>
       </c>
       <c r="J6" t="n">
-        <v>1.111891836598279e-10</v>
+        <v>1.992834167198226e-10</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003667239256997262</v>
+        <v>0.003916604959865204</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07445444692908759</v>
+        <v>0.07455113477388556</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9213863441801394</v>
+        <v>0.7628143080861448</v>
       </c>
       <c r="O6" t="n">
-        <v>6.177603091881085e-11</v>
+        <v>1.625893402749849e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05175543422412406</v>
+        <v>0.05135668179137896</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7175658996576265</v>
+        <v>0.7154718744255968</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00162022416101657</v>
+        <v>0.01793389076702463</v>
       </c>
       <c r="S6" t="n">
         <v>0.9460209709176927</v>
@@ -15735,10 +15735,10 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.466057866007462e-19</v>
+        <v>7.108497337180325e-19</v>
       </c>
       <c r="V6" t="n">
-        <v>4.152504657993086e-27</v>
+        <v>3.824615528597822e-26</v>
       </c>
     </row>
     <row r="7">
@@ -15748,67 +15748,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2093615900447577</v>
+        <v>0.2591845362152862</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1009664618023903</v>
+        <v>0.01313759243941184</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2642363281720147</v>
+        <v>0.2358200609770622</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1401469381090643</v>
+        <v>0.6654284195911254</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4160720418656768</v>
+        <v>0.8985019134059116</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005299630958721476</v>
+        <v>7.88728659424571e-11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7435225304021311</v>
+        <v>0.8324371244579716</v>
       </c>
       <c r="I7" t="n">
-        <v>1.246643949254386e-74</v>
+        <v>4.053000146788306e-69</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6235016535891812</v>
+        <v>0.9090535952939878</v>
       </c>
       <c r="K7" t="n">
-        <v>0.488732917419238</v>
+        <v>0.6230527568479259</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7834387757796335</v>
+        <v>0.7925703641141331</v>
       </c>
       <c r="M7" t="n">
-        <v>9.06786499385668e-35</v>
+        <v>3.178913499069862e-35</v>
       </c>
       <c r="N7" t="n">
-        <v>9.930956319145437e-17</v>
+        <v>4.756354356276574e-14</v>
       </c>
       <c r="O7" t="n">
-        <v>6.198659372240886e-08</v>
+        <v>1.066682981120293e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>0.165396014664028</v>
+        <v>0.1642595532490258</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003635782741728188</v>
+        <v>0.001945811553296202</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7120677131408075</v>
+        <v>0.8423410753851268</v>
       </c>
       <c r="S7" t="n">
         <v>0.001177553784136561</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6966599550888679</v>
+        <v>0.8591709580366047</v>
       </c>
       <c r="U7" t="n">
-        <v>1.306045010791764e-17</v>
+        <v>1.462287947538725e-18</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5238061074146552</v>
+        <v>0.203785935099023</v>
       </c>
     </row>
     <row r="8">
@@ -15821,58 +15821,58 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.533373390016052e-44</v>
+        <v>1.241945404564348e-70</v>
       </c>
       <c r="D8" t="n">
-        <v>9.328193457514182e-66</v>
+        <v>1.03699486756179e-68</v>
       </c>
       <c r="E8" t="n">
-        <v>0.371133114594428</v>
+        <v>2.897030390517453e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.468456930767603e-163</v>
+        <v>7.892270163843563e-155</v>
       </c>
       <c r="G8" t="n">
-        <v>6.500521849700841e-73</v>
+        <v>6.060243066288221e-204</v>
       </c>
       <c r="H8" t="n">
-        <v>7.819793959391589e-05</v>
+        <v>3.234621355609319e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>6.91671105758931e-24</v>
+        <v>1.471692717218069e-18</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9.901825533678148e-10</v>
+        <v>1.049034720038863e-11</v>
       </c>
       <c r="L8" t="n">
-        <v>6.073221375411284e-19</v>
+        <v>4.427505463832947e-20</v>
       </c>
       <c r="M8" t="n">
-        <v>4.191970464708798e-23</v>
+        <v>4.084370851761926e-24</v>
       </c>
       <c r="N8" t="n">
-        <v>5.639285904857058e-96</v>
+        <v>1.73898453389435e-74</v>
       </c>
       <c r="O8" t="n">
-        <v>3.790626246780248e-179</v>
+        <v>9.013216444253623e-199</v>
       </c>
       <c r="P8" t="n">
-        <v>1.380961176198224e-50</v>
+        <v>9.638314289374332e-53</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.220269653000556e-38</v>
+        <v>7.143649046359913e-42</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8558582033164943</v>
+        <v>1.287091419853095e-05</v>
       </c>
       <c r="S8" t="n">
         <v>0.000428110581770443</v>
       </c>
       <c r="T8" t="n">
-        <v>3.20960248146163e-24</v>
+        <v>1.123991482615611e-27</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -15888,67 +15888,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.781293445230602e-69</v>
+        <v>1.059238604725585e-48</v>
       </c>
       <c r="C9" t="n">
-        <v>6.576996475279604e-06</v>
+        <v>0.000985536835713162</v>
       </c>
       <c r="D9" t="n">
-        <v>2.065122184644591e-05</v>
+        <v>2.821874438872851e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.900025947363186e-15</v>
+        <v>4.305997638401319e-10</v>
       </c>
       <c r="F9" t="n">
-        <v>3.168776006374834e-07</v>
+        <v>2.641120861624397e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.954838264482901e-14</v>
+        <v>0.0008254009366834188</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2309699547350617</v>
+        <v>0.2786345086558001</v>
       </c>
       <c r="I9" t="n">
-        <v>7.026789104387583e-27</v>
+        <v>3.4598769079526e-30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003009500629984833</v>
+        <v>0.01044870463378327</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01804027832933927</v>
+        <v>0.03894986754935127</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4455180178801231</v>
+        <v>0.4391595307857605</v>
       </c>
       <c r="M9" t="n">
-        <v>4.555974888745038e-06</v>
+        <v>7.680196873493303e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2897519736243998</v>
+        <v>0.03354096243013543</v>
       </c>
       <c r="O9" t="n">
-        <v>3.440587271206975e-07</v>
+        <v>2.295843767458452e-06</v>
       </c>
       <c r="P9" t="n">
-        <v>0.000628370573542382</v>
+        <v>0.0004612299475696679</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06553752465506735</v>
+        <v>0.04455810503428572</v>
       </c>
       <c r="R9" t="n">
-        <v>3.330597820898642e-10</v>
+        <v>0.000464578714053179</v>
       </c>
       <c r="S9" t="n">
         <v>0.7009577406029145</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2409517813174451</v>
+        <v>0.3606002211631266</v>
       </c>
       <c r="U9" t="n">
-        <v>0.007230919483361844</v>
+        <v>0.02193984432220588</v>
       </c>
       <c r="V9" t="n">
-        <v>1.406213086132098e-29</v>
+        <v>4.482324615339028e-26</v>
       </c>
     </row>
     <row r="10">
@@ -15958,67 +15958,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.386192458806083e-40</v>
+        <v>1.902274420172481e-23</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009727323527653096</v>
+        <v>0.2293967877363828</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002279990372894542</v>
+        <v>0.002339144242386819</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002916353414622673</v>
+        <v>0.05052364269732661</v>
       </c>
       <c r="F10" t="n">
-        <v>7.284761158275863e-12</v>
+        <v>8.855811051182971e-15</v>
       </c>
       <c r="G10" t="n">
-        <v>1.479887209197921e-28</v>
+        <v>2.47632200484529e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8433915866925387</v>
+        <v>0.9434049126122671</v>
       </c>
       <c r="I10" t="n">
-        <v>5.691609824642897e-48</v>
+        <v>8.18696383176456e-53</v>
       </c>
       <c r="J10" t="n">
-        <v>2.708077474135645e-06</v>
+        <v>2.222385109218136e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008253264361697512</v>
+        <v>0.002894794609742071</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4866081230316431</v>
+        <v>0.4349344675729485</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.9189341408554205</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002810867241539461</v>
+        <v>6.852963507933273e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>0.003216187976704581</v>
+        <v>0.01237906347391058</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9135051938023032</v>
+        <v>0.9124040260827943</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01006505985151172</v>
+        <v>0.01790290119264115</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001675694896907354</v>
+        <v>0.8487939969035342</v>
       </c>
       <c r="S10" t="n">
         <v>0.4424981595909629</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5462687055340266</v>
+        <v>0.7705787174143227</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0006773838980491694</v>
+        <v>0.003362805727921373</v>
       </c>
       <c r="V10" t="n">
-        <v>1.610463697917799e-14</v>
+        <v>7.427690132087048e-12</v>
       </c>
     </row>
     <row r="11">
@@ -16034,16 +16034,16 @@
         <v>1.441933550954497e-148</v>
       </c>
       <c r="D11" t="n">
-        <v>1.621329840096426e-101</v>
+        <v>5.195883635755222e-101</v>
       </c>
       <c r="E11" t="n">
-        <v>8.091525834343286e-112</v>
+        <v>2.530531190111329e-111</v>
       </c>
       <c r="F11" t="n">
-        <v>2.83872591401628e-153</v>
+        <v>1.195900276420075e-152</v>
       </c>
       <c r="G11" t="n">
-        <v>6.968902195527981e-144</v>
+        <v>2.427632471257812e-143</v>
       </c>
       <c r="H11" t="n">
         <v>1.989941627286703e-36</v>
@@ -16055,7 +16055,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.202938950809911e-62</v>
+        <v>4.915860021506286e-62</v>
       </c>
       <c r="L11" t="n">
         <v>4.1115079368243e-47</v>
@@ -16076,13 +16076,13 @@
         <v>2.736613572805729e-59</v>
       </c>
       <c r="R11" t="n">
-        <v>4.868732622163575e-23</v>
+        <v>2.084588555953028e-23</v>
       </c>
       <c r="S11" t="n">
         <v>1.980591677930948e-37</v>
       </c>
       <c r="T11" t="n">
-        <v>1.326986057492717e-294</v>
+        <v>4.931889603681468e-294</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -16101,64 +16101,64 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6.568901975498161e-36</v>
+        <v>2.845873276250199e-35</v>
       </c>
       <c r="D12" t="n">
-        <v>4.128598991299241e-40</v>
+        <v>1.40119866298628e-40</v>
       </c>
       <c r="E12" t="n">
-        <v>1.536596553000591e-37</v>
+        <v>5.824583453523479e-38</v>
       </c>
       <c r="F12" t="n">
-        <v>7.058557493377806e-97</v>
+        <v>1.431491214652689e-97</v>
       </c>
       <c r="G12" t="n">
-        <v>1.121821306565215e-63</v>
+        <v>5.215737364555202e-64</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001276345158755785</v>
+        <v>0.0009703612896280186</v>
       </c>
       <c r="I12" t="n">
-        <v>1.862708600981361e-14</v>
+        <v>1.373070038140163e-13</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.216094999398376e-18</v>
+        <v>2.409777732780286e-18</v>
       </c>
       <c r="L12" t="n">
-        <v>9.646620003217565e-27</v>
+        <v>2.960062960259097e-26</v>
       </c>
       <c r="M12" t="n">
-        <v>7.434148834678874e-67</v>
+        <v>1.793776026315666e-68</v>
       </c>
       <c r="N12" t="n">
-        <v>5.080088649997493e-38</v>
+        <v>9.274810342260348e-39</v>
       </c>
       <c r="O12" t="n">
-        <v>7.176339719028706e-149</v>
+        <v>5.395214107757409e-150</v>
       </c>
       <c r="P12" t="n">
-        <v>3.596594006950606e-31</v>
+        <v>3.097429259359515e-31</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67158073734776e-27</v>
+        <v>2.072220985586037e-27</v>
       </c>
       <c r="R12" t="n">
-        <v>1.152922767001487e-13</v>
+        <v>8.463142835146997e-14</v>
       </c>
       <c r="S12" t="n">
-        <v>1.040598404979138e-10</v>
+        <v>9.631948304845009e-11</v>
       </c>
       <c r="T12" t="n">
-        <v>6.526278398199494e-61</v>
+        <v>1.000454338427657e-60</v>
       </c>
       <c r="U12" t="n">
-        <v>3.229431082543301e-181</v>
+        <v>3.107697677767685e-184</v>
       </c>
       <c r="V12" t="n">
-        <v>1.127460521170777e-316</v>
+        <v>1.833431293062568e-315</v>
       </c>
     </row>
     <row r="13">
@@ -16168,67 +16168,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.531320788906373e-75</v>
+        <v>2.866831240041448e-71</v>
       </c>
       <c r="C13" t="n">
-        <v>8.7466419688934e-06</v>
+        <v>4.033913540630688e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06694274924802622</v>
+        <v>0.06587721613738949</v>
       </c>
       <c r="E13" t="n">
-        <v>7.956081411653797e-25</v>
+        <v>4.351049750807995e-25</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001021911740555802</v>
+        <v>0.0005077842163185852</v>
       </c>
       <c r="G13" t="n">
-        <v>3.039861640741604e-06</v>
+        <v>9.956793512988275e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>2.147254521399833e-05</v>
+        <v>1.167041032649252e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>2.030557974934362e-51</v>
+        <v>8.316278224097546e-59</v>
       </c>
       <c r="J13" t="n">
-        <v>1.060308248010187e-65</v>
+        <v>2.37123955811362e-70</v>
       </c>
       <c r="K13" t="n">
-        <v>1.050587044114164e-05</v>
+        <v>4.017376055434201e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03266270225067552</v>
+        <v>0.04750740006062549</v>
       </c>
       <c r="M13" t="n">
-        <v>8.362033058307639e-166</v>
+        <v>8.688687643656349e-165</v>
       </c>
       <c r="N13" t="n">
-        <v>0.000610578851590338</v>
+        <v>0.001291563560737306</v>
       </c>
       <c r="O13" t="n">
-        <v>1.233080577078078e-15</v>
+        <v>7.320190565869028e-15</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.06938538620307146</v>
+        <v>0.04600872725342938</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7067676890357756</v>
+        <v>0.7720926523322517</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01690301889901881</v>
+        <v>0.01377799673966237</v>
       </c>
       <c r="T13" t="n">
-        <v>9.27791518591044e-32</v>
+        <v>3.765193925160753e-31</v>
       </c>
       <c r="U13" t="n">
-        <v>8.694387588619405e-09</v>
+        <v>5.362152080531656e-09</v>
       </c>
       <c r="V13" t="n">
-        <v>0.09566117284826572</v>
+        <v>0.2273400240030324</v>
       </c>
     </row>
     <row r="14">
@@ -16241,58 +16241,58 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.654874410616284e-97</v>
+        <v>1.855851994746729e-96</v>
       </c>
       <c r="D14" t="n">
-        <v>3.044645424013263e-53</v>
+        <v>4.741170603440079e-52</v>
       </c>
       <c r="E14" t="n">
-        <v>2.427477411446022e-56</v>
+        <v>2.564401473880086e-54</v>
       </c>
       <c r="F14" t="n">
-        <v>1.312994992966211e-100</v>
+        <v>3.256925941530265e-99</v>
       </c>
       <c r="G14" t="n">
-        <v>1.141592741232434e-72</v>
+        <v>4.714556817405544e-71</v>
       </c>
       <c r="H14" t="n">
-        <v>2.883019824062086e-11</v>
+        <v>1.053477999592475e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>2.412706042490493e-278</v>
+        <v>9.455770084625257e-268</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>3.101239619072649e-25</v>
+        <v>9.458311035967816e-25</v>
       </c>
       <c r="L14" t="n">
-        <v>2.617249452241069e-30</v>
+        <v>5.390047002849346e-30</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>9.579550398849475e-127</v>
+        <v>1.896957759518764e-125</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.085398130886152e-55</v>
+        <v>1.085022413582706e-54</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.784017924523836e-47</v>
+        <v>3.6074572317734e-47</v>
       </c>
       <c r="R14" t="n">
         <v>9.982919115015652e-28</v>
       </c>
       <c r="S14" t="n">
-        <v>4.700217796411339e-30</v>
+        <v>5.428893461993334e-29</v>
       </c>
       <c r="T14" t="n">
-        <v>1.027236893783237e-159</v>
+        <v>1.859130716679865e-155</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -16311,58 +16311,58 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.363972704812335e-50</v>
+        <v>3.420230105275719e-52</v>
       </c>
       <c r="D15" t="n">
-        <v>1.079943421500126e-27</v>
+        <v>1.809536356430521e-28</v>
       </c>
       <c r="E15" t="n">
-        <v>4.64572107977953e-33</v>
+        <v>4.897338830773797e-34</v>
       </c>
       <c r="F15" t="n">
-        <v>5.115382749606175e-52</v>
+        <v>9.520751865658562e-54</v>
       </c>
       <c r="G15" t="n">
-        <v>2.195445659447862e-155</v>
+        <v>4.602827984014645e-159</v>
       </c>
       <c r="H15" t="n">
-        <v>5.913032642112736e-05</v>
+        <v>3.305418356429227e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>7.152594371432343e-141</v>
+        <v>2.021128361006837e-121</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.268335300472443e-19</v>
+        <v>1.131806851280094e-20</v>
       </c>
       <c r="L15" t="n">
-        <v>1.340245989608187e-18</v>
+        <v>3.797263902571597e-19</v>
       </c>
       <c r="M15" t="n">
-        <v>9.019032770414669e-149</v>
+        <v>5.779925194699972e-153</v>
       </c>
       <c r="N15" t="n">
-        <v>8.949913517179313e-69</v>
+        <v>1.990939268831647e-71</v>
       </c>
       <c r="O15" t="n">
-        <v>2.856233738526864e-208</v>
+        <v>1.291525508686231e-212</v>
       </c>
       <c r="P15" t="n">
-        <v>1.984431102915336e-29</v>
+        <v>4.05734887430106e-30</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.016057148203264e-34</v>
+        <v>3.260126663874579e-35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.612903361975269e-18</v>
+        <v>1.016044568950754e-19</v>
       </c>
       <c r="S15" t="n">
-        <v>4.331021848068554e-12</v>
+        <v>2.343316007734194e-12</v>
       </c>
       <c r="T15" t="n">
-        <v>2.819848663294446e-104</v>
+        <v>1.241744156713242e-107</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -16384,10 +16384,10 @@
         <v>5.25279737526659e-172</v>
       </c>
       <c r="D16" t="n">
-        <v>4.546979620712837e-149</v>
+        <v>5.771152922147488e-149</v>
       </c>
       <c r="E16" t="n">
-        <v>2.003936987168503e-51</v>
+        <v>3.404241198588375e-51</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -16399,40 +16399,40 @@
         <v>3.013266102762039e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>9.168519854955316e-143</v>
+        <v>3.895573959528169e-142</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>6.652654361282078e-28</v>
+        <v>3.316008407634659e-28</v>
       </c>
       <c r="L16" t="n">
         <v>8.43193103660275e-56</v>
       </c>
       <c r="M16" t="n">
-        <v>5.326382732153411e-312</v>
+        <v>1.07814458994819e-311</v>
       </c>
       <c r="N16" t="n">
-        <v>8.635018264137799e-215</v>
+        <v>3.554297835265974e-214</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.422267020151414e-117</v>
+        <v>1.908156512496813e-116</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.251237209488326e-99</v>
+        <v>1.422391266090573e-99</v>
       </c>
       <c r="R16" t="n">
         <v>1.766651489490487e-42</v>
       </c>
       <c r="S16" t="n">
-        <v>6.551072803483079e-28</v>
+        <v>1.144269751065348e-27</v>
       </c>
       <c r="T16" t="n">
-        <v>1.029313615694912e-172</v>
+        <v>5.206935675697749e-172</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -16448,67 +16448,67 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.150853808883708e-264</v>
+        <v>2.598398747809422e-266</v>
       </c>
       <c r="C17" t="n">
-        <v>0.343250308952174</v>
+        <v>0.423909287480893</v>
       </c>
       <c r="D17" t="n">
         <v>0.3171442442229303</v>
       </c>
       <c r="E17" t="n">
-        <v>5.223744793421795e-14</v>
+        <v>5.403873924229444e-14</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3826075653971815</v>
+        <v>0.4165619394594497</v>
       </c>
       <c r="G17" t="n">
-        <v>2.687547349859669e-09</v>
+        <v>1.512893614433692e-09</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8433915866925387</v>
+        <v>0.8324371244579716</v>
       </c>
       <c r="I17" t="n">
-        <v>0.004608810447403083</v>
+        <v>0.0064851193646713</v>
       </c>
       <c r="J17" t="n">
-        <v>4.841665288085559e-48</v>
+        <v>2.930917348070002e-48</v>
       </c>
       <c r="K17" t="n">
-        <v>1.856591198781659e-07</v>
+        <v>4.179974384041705e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0001278346990846743</v>
+        <v>9.115317407725122e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>1.228521413782868e-70</v>
+        <v>8.960623056752251e-71</v>
       </c>
       <c r="N17" t="n">
-        <v>2.040687170971147e-14</v>
+        <v>3.749077149930491e-15</v>
       </c>
       <c r="O17" t="n">
-        <v>2.168669678506487e-06</v>
+        <v>2.148483971237299e-06</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01755302727539235</v>
+        <v>0.01299322800835511</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.012866621911505e-09</v>
+        <v>1.11054183450385e-08</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0001691209162459554</v>
+        <v>0.0001769870053736742</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001091623835919936</v>
+        <v>0.001086794982589663</v>
       </c>
       <c r="T17" t="n">
-        <v>1.082898603334152e-13</v>
+        <v>3.099810590898253e-14</v>
       </c>
       <c r="U17" t="n">
-        <v>6.340472870056701e-32</v>
+        <v>3.940186712268526e-32</v>
       </c>
       <c r="V17" t="n">
-        <v>2.565900347375895e-37</v>
+        <v>4.245068871277508e-37</v>
       </c>
     </row>
     <row r="18">
@@ -16518,67 +16518,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.299375214846945e-59</v>
+        <v>1.01006557124593e-57</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0006706152190819975</v>
+        <v>0.001607664238041224</v>
       </c>
       <c r="D18" t="n">
-        <v>7.2758761827478e-25</v>
+        <v>1.119595390597465e-23</v>
       </c>
       <c r="E18" t="n">
-        <v>1.320356166103076e-05</v>
+        <v>1.016588063918768e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>3.467939133779461e-77</v>
+        <v>1.442205813014424e-76</v>
       </c>
       <c r="G18" t="n">
-        <v>8.163022157255031e-18</v>
+        <v>2.587251335056139e-18</v>
       </c>
       <c r="H18" t="n">
-        <v>4.718810252592413e-36</v>
+        <v>8.230432264751402e-36</v>
       </c>
       <c r="I18" t="n">
-        <v>5.89770878718695e-153</v>
+        <v>4.487105317184224e-152</v>
       </c>
       <c r="J18" t="n">
-        <v>9.729789276845334e-09</v>
+        <v>1.472671968575074e-08</v>
       </c>
       <c r="K18" t="n">
-        <v>1.400008611326979e-05</v>
+        <v>5.927556169918548e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>2.205680279823655e-18</v>
+        <v>1.845850551200065e-18</v>
       </c>
       <c r="M18" t="n">
-        <v>3.608552323620402e-37</v>
+        <v>4.724152521520092e-39</v>
       </c>
       <c r="N18" t="n">
-        <v>0.007390803987452517</v>
+        <v>0.005721019285241518</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01096336756551852</v>
+        <v>0.01352035157490513</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1067680770681233</v>
+        <v>0.07456819521587633</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1637232176097969</v>
+        <v>0.1285140679507185</v>
       </c>
       <c r="R18" t="n">
-        <v>1.459537242071281e-11</v>
+        <v>9.939020583339277e-12</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7313420388871176</v>
+        <v>0.7304052817655069</v>
       </c>
       <c r="T18" t="n">
-        <v>0.003406605393168528</v>
+        <v>0.003346947252381217</v>
       </c>
       <c r="U18" t="n">
-        <v>4.310888917982634e-114</v>
+        <v>1.565962171043455e-112</v>
       </c>
       <c r="V18" t="n">
-        <v>6.76337104014429e-33</v>
+        <v>2.263319572960285e-32</v>
       </c>
     </row>
     <row r="19">
@@ -16591,61 +16591,61 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>7.348610566796743e-103</v>
+        <v>7.822441330380338e-104</v>
       </c>
       <c r="D19" t="n">
-        <v>1.486053377963116e-63</v>
+        <v>8.916344039318373e-65</v>
       </c>
       <c r="E19" t="n">
-        <v>6.948817509964632e-76</v>
+        <v>4.570017409052258e-76</v>
       </c>
       <c r="F19" t="n">
-        <v>3.521649535083674e-167</v>
+        <v>1.156489591763554e-167</v>
       </c>
       <c r="G19" t="n">
-        <v>6.075279010086005e-240</v>
+        <v>2.073277214262465e-238</v>
       </c>
       <c r="H19" t="n">
-        <v>3.790622446859336e-17</v>
+        <v>6.073649710359638e-17</v>
       </c>
       <c r="I19" t="n">
-        <v>1.568763038092153e-21</v>
+        <v>2.21457286624748e-22</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2.971374385427513e-56</v>
+        <v>1.022749722380185e-56</v>
       </c>
       <c r="L19" t="n">
-        <v>1.034483475640022e-13</v>
+        <v>7.770523749957169e-14</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.004882071943415e-171</v>
+        <v>8.355399062369601e-171</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5.560698576085778e-105</v>
+        <v>3.034341265119929e-103</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.175660702557085e-101</v>
+        <v>1.489372955922454e-100</v>
       </c>
       <c r="R19" t="n">
-        <v>4.500834229743901e-05</v>
+        <v>5.525307861180257e-05</v>
       </c>
       <c r="S19" t="n">
-        <v>3.190819717093126e-18</v>
+        <v>3.036443436771267e-18</v>
       </c>
       <c r="T19" t="n">
-        <v>1.127769490626919e-150</v>
+        <v>3.416225911562772e-151</v>
       </c>
       <c r="U19" t="n">
-        <v>2.353078128918614e-226</v>
+        <v>2.105233955421234e-228</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -16661,7 +16661,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3.067415562325159e-29</v>
+        <v>3.286516673919813e-29</v>
       </c>
       <c r="D20" t="n">
         <v>4.171345371528256e-20</v>
@@ -16670,10 +16670,10 @@
         <v>7.969571200376706e-48</v>
       </c>
       <c r="F20" t="n">
-        <v>1.177531275532435e-29</v>
+        <v>1.118654711755813e-29</v>
       </c>
       <c r="G20" t="n">
-        <v>1.625907875190025e-41</v>
+        <v>1.699812778607754e-41</v>
       </c>
       <c r="H20" t="n">
         <v>0.004806417447233687</v>
@@ -16709,7 +16709,7 @@
         <v>1.232525950894506e-17</v>
       </c>
       <c r="S20" t="n">
-        <v>2.430230666439372e-12</v>
+        <v>2.343316007734194e-12</v>
       </c>
       <c r="T20" t="n">
         <v>4.204861527284118e-130</v>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.574443826175253e-31</v>
+        <v>2.678813170479656e-31</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -16737,7 +16737,7 @@
         <v>0.006865621115861267</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08272735713895375</v>
+        <v>0.08141422448595448</v>
       </c>
       <c r="F21" t="n">
         <v>0.0003731023329136949</v>
@@ -16749,22 +16749,22 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.151106512656095e-18</v>
+        <v>1.175598140584948e-18</v>
       </c>
       <c r="J21" t="n">
         <v>2.715824098298831e-07</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5161549682750485</v>
+        <v>0.5228582795513478</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1.926435582630805e-05</v>
+        <v>1.872923483113283e-05</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8608737897164513</v>
+        <v>0.8516170823001452</v>
       </c>
       <c r="O21" t="n">
         <v>8.528015270781189e-15</v>
@@ -16773,16 +16773,16 @@
         <v>0.004785972797783649</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.003161064471895681</v>
+        <v>0.003093807781004283</v>
       </c>
       <c r="R21" t="n">
         <v>0.04047930348577845</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1116575471792518</v>
+        <v>0.1094243962356668</v>
       </c>
       <c r="T21" t="n">
-        <v>0.74720079067013</v>
+        <v>0.7639918196739531</v>
       </c>
       <c r="U21" t="n">
         <v>1.221711485648667e-05</v>
@@ -16816,7 +16816,7 @@
         <v>0.0003975350428501904</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9013389313435529</v>
+        <v>0.9131986541243893</v>
       </c>
       <c r="I22" t="n">
         <v>3.846605124693801e-90</v>
@@ -16825,19 +16825,19 @@
         <v>9.920086567040363e-08</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5150817115202526</v>
+        <v>0.5219494676738559</v>
       </c>
       <c r="L22" t="n">
         <v>0.1072426988872058</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0001029451349190659</v>
+        <v>0.0001043553422467243</v>
       </c>
       <c r="N22" t="n">
-        <v>3.91765361280301e-05</v>
+        <v>3.846423547115682e-05</v>
       </c>
       <c r="O22" t="n">
-        <v>2.650573610375792e-08</v>
+        <v>2.607121583976189e-08</v>
       </c>
       <c r="P22" t="n">
         <v>0.004780154766431954</v>
@@ -16846,7 +16846,7 @@
         <v>0.0436445305208652</v>
       </c>
       <c r="R22" t="n">
-        <v>0.00031376145861832</v>
+        <v>0.0003274032611669427</v>
       </c>
       <c r="S22" t="n">
         <v>0.8441595061128788</v>
@@ -16855,7 +16855,7 @@
         <v>0.0001773147322537233</v>
       </c>
       <c r="U22" t="n">
-        <v>6.811266186398865e-08</v>
+        <v>6.917692220561348e-08</v>
       </c>
       <c r="V22" t="n">
         <v>5.753729459885882e-20</v>
@@ -16871,28 +16871,28 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.378672546377653e-23</v>
+        <v>2.658516375363259e-23</v>
       </c>
       <c r="D23" t="n">
         <v>1.02602633871465e-08</v>
       </c>
       <c r="E23" t="n">
-        <v>1.176749418905372e-13</v>
+        <v>1.215974399535551e-13</v>
       </c>
       <c r="F23" t="n">
         <v>3.367851789008176e-15</v>
       </c>
       <c r="G23" t="n">
-        <v>2.993681440670406e-35</v>
+        <v>3.118418167365006e-35</v>
       </c>
       <c r="H23" t="n">
-        <v>3.272065405294596e-05</v>
+        <v>3.234621355609319e-05</v>
       </c>
       <c r="I23" t="n">
         <v>0.008792958993910154</v>
       </c>
       <c r="J23" t="n">
-        <v>3.600553936359859e-31</v>
+        <v>3.72471096864813e-31</v>
       </c>
       <c r="K23" t="n">
         <v>1.725117273259786e-13</v>
@@ -16916,7 +16916,7 @@
         <v>2.385923036965226e-07</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0001224833461768825</v>
+        <v>0.0001255454298313046</v>
       </c>
       <c r="S23" t="n">
         <v>1.761150432232408e-08</v>
@@ -16953,10 +16953,10 @@
         <v>0.0003497275375828331</v>
       </c>
       <c r="G24" t="n">
-        <v>4.450204242467821e-05</v>
+        <v>4.52198173024956e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7435225304021311</v>
+        <v>0.7464690887468838</v>
       </c>
       <c r="I24" t="n">
         <v>0.2118692661599025</v>
@@ -16965,16 +16965,16 @@
         <v>4.412233915678295e-10</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02044121806604939</v>
+        <v>0.02080623981722884</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0001137868663910584</v>
+        <v>0.0001108692544323133</v>
       </c>
       <c r="M24" t="n">
         <v>3.587285448321868e-29</v>
       </c>
       <c r="N24" t="n">
-        <v>2.482230489812439e-18</v>
+        <v>2.378804219403587e-18</v>
       </c>
       <c r="O24" t="n">
         <v>6.137077999201169e-22</v>
@@ -16986,7 +16986,7 @@
         <v>0.0001293592790250558</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0002785664441630381</v>
+        <v>0.0002912285552613579</v>
       </c>
       <c r="S24" t="n">
         <v>0.3755359513052301</v>
@@ -17011,7 +17011,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.648131748117143e-20</v>
+        <v>2.787507103281203e-20</v>
       </c>
       <c r="D25" t="n">
         <v>1.571057763781508e-06</v>
@@ -17029,13 +17029,13 @@
         <v>0.01035286092950512</v>
       </c>
       <c r="I25" t="n">
-        <v>0.004922998616295441</v>
+        <v>0.00499233662497566</v>
       </c>
       <c r="J25" t="n">
         <v>1.828692734997559e-21</v>
       </c>
       <c r="K25" t="n">
-        <v>5.697919539501248e-10</v>
+        <v>5.507988888184539e-10</v>
       </c>
       <c r="L25" t="n">
         <v>3.700312611888644e-16</v>
@@ -17056,7 +17056,7 @@
         <v>1.744516534991869e-07</v>
       </c>
       <c r="R25" t="n">
-        <v>4.787581625747406e-08</v>
+        <v>5.129551741872221e-08</v>
       </c>
       <c r="S25" t="n">
         <v>0.01863925263481197</v>
@@ -17078,7 +17078,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.882858935094789e-42</v>
+        <v>6.98261051386428e-42</v>
       </c>
       <c r="C26" t="n">
         <v>0.007043350551015831</v>
@@ -17087,16 +17087,16 @@
         <v>0.001383821938337144</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2230568522215111</v>
+        <v>0.2199152064155743</v>
       </c>
       <c r="F26" t="n">
         <v>0.01303074857472805</v>
       </c>
       <c r="G26" t="n">
-        <v>0.003407426896433715</v>
+        <v>0.003360101522872136</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9363997966177117</v>
+        <v>0.9434049126122671</v>
       </c>
       <c r="I26" t="n">
         <v>0.004447437592665963</v>
@@ -17108,16 +17108,16 @@
         <v>0.9875612326293516</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5916660583947838</v>
+        <v>0.5853234184718809</v>
       </c>
       <c r="M26" t="n">
-        <v>1.087083222938692e-05</v>
+        <v>1.071553462610996e-05</v>
       </c>
       <c r="N26" t="n">
         <v>1.535365844378002e-07</v>
       </c>
       <c r="O26" t="n">
-        <v>2.059225440902461e-08</v>
+        <v>2.024905016887419e-08</v>
       </c>
       <c r="P26" t="n">
         <v>0.5545967276592317</v>
@@ -17132,13 +17132,13 @@
         <v>0.03543663622821214</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2608097647083509</v>
+        <v>0.2640296383467257</v>
       </c>
       <c r="U26" t="n">
         <v>0.0001794764991751929</v>
       </c>
       <c r="V26" t="n">
-        <v>1.954915201655995e-10</v>
+        <v>2.014155056251631e-10</v>
       </c>
     </row>
     <row r="27">
@@ -17151,16 +17151,16 @@
         <v>0.719742893408099</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3920774426725231</v>
+        <v>0.3975229627096414</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2083294713533245</v>
+        <v>0.2053102036525517</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8548439560048415</v>
+        <v>0.8645580918685329</v>
       </c>
       <c r="G27" t="n">
         <v>0.78463276156697</v>
@@ -17175,7 +17175,7 @@
         <v>0.1190431989503718</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1177947156658548</v>
+        <v>0.116087545873596</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -17184,7 +17184,7 @@
         <v>0.06006601384031054</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2505490447459138</v>
+        <v>0.2474171816865899</v>
       </c>
       <c r="O27" t="n">
         <v>0.04120192779443577</v>
@@ -17221,40 +17221,40 @@
         <v>3.220171072259151e-284</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0008182376399995494</v>
+        <v>0.0008546037573328628</v>
       </c>
       <c r="D28" t="n">
         <v>2.423330492124028e-08</v>
       </c>
       <c r="E28" t="n">
-        <v>0.05136570340894871</v>
+        <v>0.05052364269732661</v>
       </c>
       <c r="F28" t="n">
         <v>7.114368927373887e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>6.661117070981074e-10</v>
+        <v>6.970936469631356e-10</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7435225304021311</v>
+        <v>0.7485322446973427</v>
       </c>
       <c r="I28" t="n">
         <v>0.9667006139728425</v>
       </c>
       <c r="J28" t="n">
-        <v>1.00969120782109e-27</v>
+        <v>1.0412440580655e-27</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000418785362462767</v>
+        <v>0.000409875035601857</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04547240656880015</v>
+        <v>0.04631448817192607</v>
       </c>
       <c r="M28" t="n">
         <v>2.093667345483076e-41</v>
       </c>
       <c r="N28" t="n">
-        <v>2.248263160966183e-11</v>
+        <v>2.182137773878943e-11</v>
       </c>
       <c r="O28" t="n">
         <v>6.685234886588598e-49</v>
@@ -17266,7 +17266,7 @@
         <v>0.00731342700016741</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0003387223771237193</v>
+        <v>0.0003531360952991966</v>
       </c>
       <c r="S28" t="n">
         <v>0.002400276777128118</v>
@@ -17300,13 +17300,13 @@
         <v>0.3268954701706438</v>
       </c>
       <c r="F29" t="n">
-        <v>6.434609005997579e-08</v>
+        <v>6.250763034397648e-08</v>
       </c>
       <c r="G29" t="n">
         <v>0.6616255556556394</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7834111585425378</v>
+        <v>0.8064526632055535</v>
       </c>
       <c r="I29" t="n">
         <v>0.05875470387388701</v>
@@ -17342,7 +17342,7 @@
         <v>0.7435403751624357</v>
       </c>
       <c r="T29" t="n">
-        <v>5.637186547162393e-07</v>
+        <v>5.52665347761019e-07</v>
       </c>
       <c r="U29" t="n">
         <v>4.966800576210834e-14</v>
@@ -17361,25 +17361,25 @@
         <v>8.079715095633749e-99</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001108018817127534</v>
+        <v>0.0001135719287555722</v>
       </c>
       <c r="D30" t="n">
         <v>0.04644680263592103</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2230568522215111</v>
+        <v>0.2199152064155743</v>
       </c>
       <c r="F30" t="n">
         <v>9.412157190856696e-05</v>
       </c>
       <c r="G30" t="n">
-        <v>1.923028786486342e-05</v>
+        <v>1.956766133617681e-05</v>
       </c>
       <c r="H30" t="n">
         <v>0.06091369194054948</v>
       </c>
       <c r="I30" t="n">
-        <v>0.006426900589262369</v>
+        <v>0.0064851193646713</v>
       </c>
       <c r="J30" t="n">
         <v>7.300994312490727e-12</v>
@@ -17394,7 +17394,7 @@
         <v>1.038356223181797e-14</v>
       </c>
       <c r="N30" t="n">
-        <v>3.943979479984544e-05</v>
+        <v>3.87355127498482e-05</v>
       </c>
       <c r="O30" t="n">
         <v>3.622122506777146e-09</v>
@@ -17412,7 +17412,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>4.124291331292641e-07</v>
+        <v>4.041805504666788e-07</v>
       </c>
       <c r="U30" t="n">
         <v>2.722430240907056e-11</v>
@@ -17440,10 +17440,10 @@
         <v>6.830489914080896e-08</v>
       </c>
       <c r="F31" t="n">
-        <v>3.76217288422915e-13</v>
+        <v>3.640812468608855e-13</v>
       </c>
       <c r="G31" t="n">
-        <v>4.431855777904798e-05</v>
+        <v>4.504509151313073e-05</v>
       </c>
       <c r="H31" t="n">
         <v>3.583860347332936e-07</v>
@@ -17464,7 +17464,7 @@
         <v>1.048380093915946e-32</v>
       </c>
       <c r="N31" t="n">
-        <v>3.250834957826098e-10</v>
+        <v>3.160533986775373e-10</v>
       </c>
       <c r="O31" t="n">
         <v>1.087687513522243e-29</v>
@@ -17507,13 +17507,13 @@
         <v>0.0002061800463289976</v>
       </c>
       <c r="E32" t="n">
-        <v>1.995028530214234e-12</v>
+        <v>2.059384289253402e-12</v>
       </c>
       <c r="F32" t="n">
-        <v>5.87919809687345e-07</v>
+        <v>5.732218144451615e-07</v>
       </c>
       <c r="G32" t="n">
-        <v>3.931791166752429e-11</v>
+        <v>4.250585045137762e-11</v>
       </c>
       <c r="H32" t="n">
         <v>0.1988601799065851</v>
@@ -17534,10 +17534,10 @@
         <v>1.357388267770862e-30</v>
       </c>
       <c r="N32" t="n">
-        <v>4.817058820660656e-13</v>
+        <v>4.66652573251501e-13</v>
       </c>
       <c r="O32" t="n">
-        <v>3.016467165900647e-26</v>
+        <v>3.100257920508999e-26</v>
       </c>
       <c r="P32" t="n">
         <v>2.496151547698265e-10</v>
@@ -17546,16 +17546,16 @@
         <v>5.750161795761766e-06</v>
       </c>
       <c r="R32" t="n">
-        <v>7.873684145137634e-13</v>
+        <v>8.231578879007525e-13</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1116575471792518</v>
+        <v>0.1094243962356668</v>
       </c>
       <c r="T32" t="n">
         <v>3.086376737204336e-22</v>
       </c>
       <c r="U32" t="n">
-        <v>4.299540182740425e-19</v>
+        <v>4.397257005075435e-19</v>
       </c>
       <c r="V32" t="n">
         <v>1.43798433169236e-89</v>
@@ -17568,25 +17568,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.320372631855963e-55</v>
+        <v>1.341668964627834e-55</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6349114225272849</v>
+        <v>0.6505882477748722</v>
       </c>
       <c r="D33" t="n">
         <v>0.0003411518273677316</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5481249652065835</v>
+        <v>0.5550632559054011</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4124148460055651</v>
+        <v>0.4165619394594497</v>
       </c>
       <c r="G33" t="n">
-        <v>2.394261233426624e-05</v>
+        <v>2.435541599520186e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1133014442231576</v>
+        <v>0.110890775197133</v>
       </c>
       <c r="I33" t="n">
         <v>0.0001939717470497348</v>
@@ -17607,7 +17607,7 @@
         <v>0.0005734449627535299</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0005896817467727708</v>
+        <v>0.0005973399512763132</v>
       </c>
       <c r="P33" t="n">
         <v>0.8290932784793452</v>
@@ -17625,10 +17625,10 @@
         <v>0.01429803311709474</v>
       </c>
       <c r="U33" t="n">
-        <v>1.200085999330311e-17</v>
+        <v>1.175084207677596e-17</v>
       </c>
       <c r="V33" t="n">
-        <v>1.010427560915277e-11</v>
+        <v>1.026215491554578e-11</v>
       </c>
     </row>
     <row r="34">
@@ -17647,19 +17647,19 @@
         <v>3.382560471094592e-14</v>
       </c>
       <c r="E34" t="n">
-        <v>4.175023819494324e-10</v>
+        <v>4.297818637714745e-10</v>
       </c>
       <c r="F34" t="n">
-        <v>2.598493100038584e-12</v>
+        <v>2.517290190662378e-12</v>
       </c>
       <c r="G34" t="n">
-        <v>1.53809850352392e-17</v>
+        <v>1.640638403758847e-17</v>
       </c>
       <c r="H34" t="n">
         <v>0.007796220659403415</v>
       </c>
       <c r="I34" t="n">
-        <v>9.000642242765881e-50</v>
+        <v>8.667285122663441e-50</v>
       </c>
       <c r="J34" t="n">
         <v>3.18686269460833e-33</v>
@@ -17717,7 +17717,7 @@
         <v>0.2838361650978824</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8669432245887816</v>
+        <v>0.8868729538896732</v>
       </c>
       <c r="F35" t="n">
         <v>0.1337032015597848</v>
@@ -17735,7 +17735,7 @@
         <v>0.000112182562766529</v>
       </c>
       <c r="K35" t="n">
-        <v>0.593405124880339</v>
+        <v>0.6008226889413433</v>
       </c>
       <c r="L35" t="n">
         <v>0.0006273189461819289</v>
@@ -17753,22 +17753,22 @@
         <v>0.3163231910373501</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.872191444986386</v>
+        <v>0.8618082134984528</v>
       </c>
       <c r="R35" t="n">
-        <v>0.7120677131408075</v>
+        <v>0.7212452746150976</v>
       </c>
       <c r="S35" t="n">
         <v>0.4676050600474375</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3248861174403239</v>
+        <v>0.3288004080118941</v>
       </c>
       <c r="U35" t="n">
-        <v>1.391239841674815e-08</v>
+        <v>1.413679193959893e-08</v>
       </c>
       <c r="V35" t="n">
-        <v>0.1731468707827154</v>
+        <v>0.1749694694225335</v>
       </c>
     </row>
     <row r="36">
@@ -17787,16 +17787,16 @@
         <v>0.854205653857657</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3942801574925378</v>
+        <v>0.3994680543016502</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6070478603057503</v>
+        <v>0.6141065563558171</v>
       </c>
       <c r="G36" t="n">
         <v>0.7253908400247829</v>
       </c>
       <c r="H36" t="n">
-        <v>0.303605383884239</v>
+        <v>0.3090269085964575</v>
       </c>
       <c r="I36" t="n">
         <v>6.921500980411462e-08</v>
@@ -17805,7 +17805,7 @@
         <v>0.2891802093732612</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03734136750951466</v>
+        <v>0.03796372363467324</v>
       </c>
       <c r="L36" t="n">
         <v>0.7928472420785875</v>
@@ -17835,7 +17835,7 @@
         <v>0.4199159654734304</v>
       </c>
       <c r="U36" t="n">
-        <v>0.8213750975054611</v>
+        <v>0.8128191069064459</v>
       </c>
       <c r="V36" t="n">
         <v>0.0002056949949825402</v>
@@ -17851,13 +17851,13 @@
         <v>0.01666219420403727</v>
       </c>
       <c r="C37" t="n">
-        <v>0.608941939871162</v>
+        <v>0.6245558357652942</v>
       </c>
       <c r="D37" t="n">
         <v>0.05802826900128293</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5286410121760647</v>
+        <v>0.5354184610501168</v>
       </c>
       <c r="F37" t="n">
         <v>0.298439472669106</v>
@@ -17866,7 +17866,7 @@
         <v>0.423720909364687</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2731133641671344</v>
+        <v>0.2782664465099105</v>
       </c>
       <c r="I37" t="n">
         <v>0.0002326259127175788</v>
@@ -17884,7 +17884,7 @@
         <v>2.080522347500779e-07</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0009205871354758556</v>
+        <v>0.0009359302544004531</v>
       </c>
       <c r="O37" t="n">
         <v>0.213582392547089</v>
@@ -17896,13 +17896,13 @@
         <v>0.8941572615836049</v>
       </c>
       <c r="R37" t="n">
-        <v>0.7225095576839584</v>
+        <v>0.7399194265438129</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>0.0358262678476705</v>
+        <v>0.03630395141897277</v>
       </c>
       <c r="U37" t="n">
         <v>1.029109868010152e-06</v>
@@ -17921,19 +17921,19 @@
         <v>3.254229435645465e-110</v>
       </c>
       <c r="C38" t="n">
-        <v>4.790310762185372e-05</v>
+        <v>4.923374950023855e-05</v>
       </c>
       <c r="D38" t="n">
         <v>6.295336217989474e-09</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7129252540524718</v>
+        <v>0.7296999659125298</v>
       </c>
       <c r="F38" t="n">
         <v>5.239268081356518e-06</v>
       </c>
       <c r="G38" t="n">
-        <v>1.848912413628174e-14</v>
+        <v>1.906690926554054e-14</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -17948,13 +17948,13 @@
         <v>0.01004941720237082</v>
       </c>
       <c r="L38" t="n">
-        <v>0.7661167669726434</v>
+        <v>0.7754596543747487</v>
       </c>
       <c r="M38" t="n">
         <v>9.787256212577893e-19</v>
       </c>
       <c r="N38" t="n">
-        <v>0.000113750907437619</v>
+        <v>0.000111789684895591</v>
       </c>
       <c r="O38" t="n">
         <v>4.315193028016256e-10</v>
@@ -17969,7 +17969,7 @@
         <v>0.09969198027689352</v>
       </c>
       <c r="S38" t="n">
-        <v>0.1056296478627165</v>
+        <v>0.1034290301989099</v>
       </c>
       <c r="T38" t="n">
         <v>0.01139508046438769</v>
@@ -17988,7 +17988,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7.379064502977733e-50</v>
+        <v>7.49436238583676e-50</v>
       </c>
       <c r="C39" t="n">
         <v>0.945296997806068</v>
@@ -17997,13 +17997,13 @@
         <v>0.3400353145188795</v>
       </c>
       <c r="E39" t="n">
-        <v>9.723836515874701e-05</v>
+        <v>9.529359785557208e-05</v>
       </c>
       <c r="F39" t="n">
         <v>0.06305171277139161</v>
       </c>
       <c r="G39" t="n">
-        <v>3.576879724274865e-05</v>
+        <v>3.636494386346112e-05</v>
       </c>
       <c r="H39" t="n">
         <v>0.09051496056129399</v>
@@ -18015,7 +18015,7 @@
         <v>2.74479824863292e-08</v>
       </c>
       <c r="K39" t="n">
-        <v>0.02648140687314529</v>
+        <v>0.02693798285371676</v>
       </c>
       <c r="L39" t="n">
         <v>0.4099845939379552</v>
@@ -18027,7 +18027,7 @@
         <v>0.004424208675024415</v>
       </c>
       <c r="O39" t="n">
-        <v>1.725288447700776e-05</v>
+        <v>1.748922536025445e-05</v>
       </c>
       <c r="P39" t="n">
         <v>0.8290932784793452</v>
@@ -18042,13 +18042,13 @@
         <v>0.8441595061128788</v>
       </c>
       <c r="T39" t="n">
-        <v>3.169292061894069e-07</v>
+        <v>3.104612632059496e-07</v>
       </c>
       <c r="U39" t="n">
         <v>4.874323822947765e-14</v>
       </c>
       <c r="V39" t="n">
-        <v>1.773233886451324e-06</v>
+        <v>1.797196506538504e-06</v>
       </c>
     </row>
     <row r="40">
@@ -18070,13 +18070,13 @@
         <v>3.68157049723396e-18</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5051125082720879</v>
+        <v>0.5111257524181843</v>
       </c>
       <c r="G40" t="n">
-        <v>1.920986267362686e-14</v>
+        <v>1.979197972434282e-14</v>
       </c>
       <c r="H40" t="n">
-        <v>0.001087076085975732</v>
+        <v>0.001054134386400709</v>
       </c>
       <c r="I40" t="n">
         <v>7.735026218785585e-84</v>
@@ -18085,7 +18085,7 @@
         <v>0.05073403491512057</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5235564291446e-11</v>
+        <v>3.397715128103721e-11</v>
       </c>
       <c r="L40" t="n">
         <v>1.08429267352168e-05</v>
@@ -18100,7 +18100,7 @@
         <v>1.85438923454399e-22</v>
       </c>
       <c r="P40" t="n">
-        <v>2.960484016894606e-08</v>
+        <v>2.873410957574176e-08</v>
       </c>
       <c r="Q40" t="n">
         <v>7.416953071187682e-05</v>
@@ -18143,7 +18143,7 @@
         <v>0.0004508293640940462</v>
       </c>
       <c r="G41" t="n">
-        <v>3.880265487210989e-29</v>
+        <v>4.035476106699429e-29</v>
       </c>
       <c r="H41" t="n">
         <v>8.898872309106322e-05</v>
@@ -18164,7 +18164,7 @@
         <v>6.29642551023739e-108</v>
       </c>
       <c r="N41" t="n">
-        <v>3.059599386532885e-13</v>
+        <v>2.960902632128599e-13</v>
       </c>
       <c r="O41" t="n">
         <v>3.7860997561115e-47</v>
@@ -18176,7 +18176,7 @@
         <v>3.721275354477477e-09</v>
       </c>
       <c r="R41" t="n">
-        <v>3.105330962219822e-16</v>
+        <v>3.260597510330814e-16</v>
       </c>
       <c r="S41" t="n">
         <v>0.0008159022068372642</v>
@@ -18188,7 +18188,7 @@
         <v>1.055863277576682e-82</v>
       </c>
       <c r="V41" t="n">
-        <v>1.266073191674931e-111</v>
+        <v>1.308275631397429e-111</v>
       </c>
     </row>
     <row r="42">
@@ -18201,7 +18201,7 @@
         <v>7.856303940406604e-13</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1833887237249825</v>
+        <v>0.1861673407511186</v>
       </c>
       <c r="D42" t="n">
         <v>0.05105064787759433</v>
@@ -18210,10 +18210,10 @@
         <v>0.005787402812928381</v>
       </c>
       <c r="F42" t="n">
-        <v>4.231961836691268e-07</v>
+        <v>4.120594419936235e-07</v>
       </c>
       <c r="G42" t="n">
-        <v>0.003407426896433715</v>
+        <v>0.003360101522872136</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -18225,7 +18225,7 @@
         <v>2.028515867409564e-11</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5604168396726845</v>
+        <v>0.5675107237191742</v>
       </c>
       <c r="L42" t="n">
         <v>0.0118164479427599</v>
@@ -18234,7 +18234,7 @@
         <v>0.07324438912287638</v>
       </c>
       <c r="N42" t="n">
-        <v>9.374686113121718e-06</v>
+        <v>9.190868738354625e-06</v>
       </c>
       <c r="O42" t="n">
         <v>0.03953884095887696</v>
@@ -18268,43 +18268,43 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.298210547713041e-40</v>
+        <v>3.345327841251798e-40</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0005475110978693764</v>
+        <v>0.0005602439140988968</v>
       </c>
       <c r="D43" t="n">
         <v>0.0002737663731695707</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5502500909102486</v>
+        <v>0.5571282170466266</v>
       </c>
       <c r="F43" t="n">
         <v>2.954931687657508e-06</v>
       </c>
       <c r="G43" t="n">
-        <v>3.017234778366517e-09</v>
+        <v>3.078810998333181e-09</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>2.480914761176298e-20</v>
+        <v>2.536046200313549e-20</v>
       </c>
       <c r="J43" t="n">
         <v>1.401178818792867e-35</v>
       </c>
       <c r="K43" t="n">
-        <v>0.03190457522174056</v>
+        <v>0.03244533073397345</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7166788283376772</v>
+        <v>0.7258670184445704</v>
       </c>
       <c r="M43" t="n">
-        <v>0.000103638832149413</v>
+        <v>0.0001050393569081889</v>
       </c>
       <c r="N43" t="n">
-        <v>0.1003360918516951</v>
+        <v>0.09904973169975033</v>
       </c>
       <c r="O43" t="n">
         <v>0.001519896761069436</v>
@@ -18325,7 +18325,7 @@
         <v>0.004411950699311732</v>
       </c>
       <c r="U43" t="n">
-        <v>0.526979619969805</v>
+        <v>0.5213734537999135</v>
       </c>
       <c r="V43" t="n">
         <v>2.131776545602324e-16</v>
@@ -18341,7 +18341,7 @@
         <v>2.620366380515338e-117</v>
       </c>
       <c r="C44" t="n">
-        <v>0.156318044046792</v>
+        <v>0.1587992828411855</v>
       </c>
       <c r="D44" t="n">
         <v>0.0196468517371168</v>
@@ -18353,7 +18353,7 @@
         <v>0.0001703552525221243</v>
       </c>
       <c r="G44" t="n">
-        <v>1.838891757407342e-08</v>
+        <v>1.874948458532976e-08</v>
       </c>
       <c r="H44" t="n">
         <v>0.1946371918325802</v>
@@ -18377,7 +18377,7 @@
         <v>5.644742587731714e-08</v>
       </c>
       <c r="O44" t="n">
-        <v>3.062389101580045e-15</v>
+        <v>3.128962777701351e-15</v>
       </c>
       <c r="P44" t="n">
         <v>0.0002461165874600034</v>
@@ -18386,7 +18386,7 @@
         <v>0.5680109192039827</v>
       </c>
       <c r="R44" t="n">
-        <v>6.198892089050344e-10</v>
+        <v>6.675729942054217e-10</v>
       </c>
       <c r="S44" t="n">
         <v>0.1563224768860283</v>
@@ -18423,10 +18423,10 @@
         <v>0.004826436377593359</v>
       </c>
       <c r="G45" t="n">
-        <v>6.238746843729251e-11</v>
+        <v>6.731279489286824e-11</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9082238358827267</v>
+        <v>0.9200189506344504</v>
       </c>
       <c r="I45" t="n">
         <v>0.6316528933004432</v>
@@ -18438,13 +18438,13 @@
         <v>0.2607225034777895</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5698736476372533</v>
+        <v>0.5620671593134554</v>
       </c>
       <c r="M45" t="n">
         <v>1.559486218681194e-21</v>
       </c>
       <c r="N45" t="n">
-        <v>4.246025672632035e-05</v>
+        <v>4.171533994164808e-05</v>
       </c>
       <c r="O45" t="n">
         <v>1.012778952051313e-09</v>
@@ -18453,22 +18453,22 @@
         <v>0.002193258836150257</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0002615183472338914</v>
+        <v>0.0002682239458809142</v>
       </c>
       <c r="R45" t="n">
-        <v>6.836862462374749e-05</v>
+        <v>7.012166628076664e-05</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0581408923073754</v>
+        <v>0.05675658534767599</v>
       </c>
       <c r="T45" t="n">
-        <v>7.043970656750344e-11</v>
+        <v>7.133246558911363e-11</v>
       </c>
       <c r="U45" t="n">
         <v>1.540428678519975e-12</v>
       </c>
       <c r="V45" t="n">
-        <v>1.436752175634428e-27</v>
+        <v>1.466073648606559e-27</v>
       </c>
     </row>
     <row r="46">
@@ -18478,10 +18478,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.484235078844283e-24</v>
+        <v>1.522786639333745e-24</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3920774426725231</v>
+        <v>0.3975229627096414</v>
       </c>
       <c r="D46" t="n">
         <v>0.4182065620844901</v>
@@ -18496,7 +18496,7 @@
         <v>0.633897424484254</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9363997966177117</v>
+        <v>0.9434049126122671</v>
       </c>
       <c r="I46" t="n">
         <v>1.204685081357131e-14</v>
@@ -18514,7 +18514,7 @@
         <v>0.0001315265370228233</v>
       </c>
       <c r="N46" t="n">
-        <v>0.006497759732013386</v>
+        <v>0.006406241989308972</v>
       </c>
       <c r="O46" t="n">
         <v>0.06971166376971091</v>
@@ -18523,7 +18523,7 @@
         <v>0.1217120577837547</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8941572615836049</v>
+        <v>0.8886673005862733</v>
       </c>
       <c r="R46" t="n">
         <v>0.5294835656536786</v>
@@ -18535,7 +18535,7 @@
         <v>0.01140779565709416</v>
       </c>
       <c r="U46" t="n">
-        <v>0.0102173131917639</v>
+        <v>0.0104934567915413</v>
       </c>
       <c r="V46" t="n">
         <v>0.0001721662722351824</v>
@@ -18554,16 +18554,16 @@
         <v>0.9928332893117695</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09737894219345228</v>
+        <v>0.09875047659054316</v>
       </c>
       <c r="E47" t="n">
         <v>2.800882431905872e-07</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5522825376213859</v>
+        <v>0.5587799792404611</v>
       </c>
       <c r="G47" t="n">
-        <v>9.743618668954893e-14</v>
+        <v>1.031677270830518e-13</v>
       </c>
       <c r="H47" t="n">
         <v>0.4710199224793452</v>
@@ -18590,13 +18590,13 @@
         <v>0.01629407471512428</v>
       </c>
       <c r="P47" t="n">
-        <v>0.09514646207651363</v>
+        <v>0.09376752784352067</v>
       </c>
       <c r="Q47" t="n">
         <v>0.2591025523016081</v>
       </c>
       <c r="R47" t="n">
-        <v>0.02638296179437332</v>
+        <v>0.02595045422397376</v>
       </c>
       <c r="S47" t="n">
         <v>0.001909723576936872</v>
@@ -18608,7 +18608,7 @@
         <v>0.1402966253934137</v>
       </c>
       <c r="V47" t="n">
-        <v>0.1949573499759862</v>
+        <v>0.1969881557049027</v>
       </c>
     </row>
     <row r="48">
@@ -18618,7 +18618,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9.19522591042969e-75</v>
+        <v>9.353764288195721e-75</v>
       </c>
       <c r="C48" t="n">
         <v>0.2413927812021963</v>
@@ -18627,25 +18627,25 @@
         <v>8.033728198933589e-06</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4947502362166851</v>
+        <v>0.5011755639597589</v>
       </c>
       <c r="F48" t="n">
         <v>0.03148392297033729</v>
       </c>
       <c r="G48" t="n">
-        <v>0.06588606423667884</v>
+        <v>0.06673075736791829</v>
       </c>
       <c r="H48" t="n">
         <v>0.04938650860553085</v>
       </c>
       <c r="I48" t="n">
-        <v>1.490239029388194e-20</v>
+        <v>1.524108098237926e-20</v>
       </c>
       <c r="J48" t="n">
         <v>3.076209297600951e-17</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01875022282973022</v>
+        <v>0.01909744917842893</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -18654,10 +18654,10 @@
         <v>3.324688190332805e-07</v>
       </c>
       <c r="N48" t="n">
-        <v>5.653269441890538e-10</v>
+        <v>5.504499193419734e-10</v>
       </c>
       <c r="O48" t="n">
-        <v>9.673526853354086e-07</v>
+        <v>9.822350343405688e-07</v>
       </c>
       <c r="P48" t="n">
         <v>0.319843340715279</v>
@@ -18666,19 +18666,19 @@
         <v>0.9880892989921486</v>
       </c>
       <c r="R48" t="n">
-        <v>0.8558582033164943</v>
+        <v>0.8655838647178181</v>
       </c>
       <c r="S48" t="n">
         <v>0.3306242023811535</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07194273994722324</v>
+        <v>0.07287706124523911</v>
       </c>
       <c r="U48" t="n">
-        <v>0.004912197981589899</v>
+        <v>0.00497948836489935</v>
       </c>
       <c r="V48" t="n">
-        <v>5.781314788097901e-14</v>
+        <v>5.967808813520414e-14</v>
       </c>
     </row>
     <row r="49">
@@ -18688,16 +18688,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.585258979591496e-44</v>
+        <v>2.624429570191367e-44</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6290582413590413</v>
+        <v>0.6449837664567386</v>
       </c>
       <c r="D49" t="n">
-        <v>0.07808003487655436</v>
+        <v>0.07921162958491022</v>
       </c>
       <c r="E49" t="n">
-        <v>6.509816446196729e-15</v>
+        <v>6.750920759018831e-15</v>
       </c>
       <c r="F49" t="n">
         <v>0.02857829073317857</v>
@@ -18706,7 +18706,7 @@
         <v>2.954256542424911e-06</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8433915866925387</v>
+        <v>0.8635017342770506</v>
       </c>
       <c r="I49" t="n">
         <v>0.2201206721113559</v>
@@ -18724,10 +18724,10 @@
         <v>1.743049647343656e-11</v>
       </c>
       <c r="N49" t="n">
-        <v>0.08873063607510014</v>
+        <v>0.08757829015204686</v>
       </c>
       <c r="O49" t="n">
-        <v>2.263723647836826e-05</v>
+        <v>2.294314507942729e-05</v>
       </c>
       <c r="P49" t="n">
         <v>0.005514046599887986</v>
@@ -18736,7 +18736,7 @@
         <v>0.0436445305208652</v>
       </c>
       <c r="R49" t="n">
-        <v>0.02439886353473512</v>
+        <v>0.0239922158091562</v>
       </c>
       <c r="S49" t="n">
         <v>0.000295626576579414</v>
@@ -18761,25 +18761,25 @@
         <v>3.758003563719396e-23</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4883771669527758</v>
+        <v>0.4996595846955251</v>
       </c>
       <c r="D50" t="n">
         <v>0.3878561227158902</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6968144575638958</v>
+        <v>0.713405277982084</v>
       </c>
       <c r="F50" t="n">
-        <v>6.739601869529414e-08</v>
+        <v>6.552390706486931e-08</v>
       </c>
       <c r="G50" t="n">
         <v>0.633897424484254</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8433915866925387</v>
+        <v>0.8574676204057174</v>
       </c>
       <c r="I50" t="n">
-        <v>1.701455013877114e-43</v>
+        <v>1.642784151329628e-43</v>
       </c>
       <c r="J50" t="n">
         <v>6.419376030146945e-07</v>
@@ -18788,13 +18788,13 @@
         <v>0.4542149831497106</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5916660583947838</v>
+        <v>0.5845806496275577</v>
       </c>
       <c r="M50" t="n">
         <v>1.044597655224821e-12</v>
       </c>
       <c r="N50" t="n">
-        <v>0.006497759732013386</v>
+        <v>0.006406241989308972</v>
       </c>
       <c r="O50" t="n">
         <v>0.9588404303766915</v>
@@ -18843,19 +18843,19 @@
         <v>1.539297196511216e-16</v>
       </c>
       <c r="G51" t="n">
-        <v>0.004001589279664547</v>
+        <v>0.003946772988162294</v>
       </c>
       <c r="H51" t="n">
-        <v>3.190748323370509e-11</v>
+        <v>3.456644016984718e-11</v>
       </c>
       <c r="I51" t="n">
         <v>1.127777130597663e-175</v>
       </c>
       <c r="J51" t="n">
-        <v>4.559854766762383e-31</v>
+        <v>4.711849925654462e-31</v>
       </c>
       <c r="K51" t="n">
-        <v>1.528415799893711e-31</v>
+        <v>1.681257379883083e-31</v>
       </c>
       <c r="L51" t="n">
         <v>7.557242717512217e-06</v>
@@ -18864,7 +18864,7 @@
         <v>3.634457722988193e-39</v>
       </c>
       <c r="N51" t="n">
-        <v>8.886875087880806e-14</v>
+        <v>8.590645918284779e-14</v>
       </c>
       <c r="O51" t="n">
         <v>1.245419664821402e-68</v>
@@ -18876,7 +18876,7 @@
         <v>0.001552553489140758</v>
       </c>
       <c r="R51" t="n">
-        <v>2.244941521795569e-23</v>
+        <v>2.084588555953028e-23</v>
       </c>
       <c r="S51" t="n">
         <v>0.001320175742482094</v>
@@ -18885,7 +18885,7 @@
         <v>2.783410022704314e-81</v>
       </c>
       <c r="U51" t="n">
-        <v>3.280410681113462e-18</v>
+        <v>3.210614709174877e-18</v>
       </c>
       <c r="V51" t="n">
         <v>3.167933417885553e-175</v>
@@ -18907,19 +18907,19 @@
         <v>0.002383332432676919</v>
       </c>
       <c r="E52" t="n">
-        <v>0.257888519321346</v>
+        <v>0.2543067343307718</v>
       </c>
       <c r="F52" t="n">
         <v>6.779057010495845e-05</v>
       </c>
       <c r="G52" t="n">
-        <v>7.776376422735744e-10</v>
+        <v>8.129848078314641e-10</v>
       </c>
       <c r="H52" t="n">
         <v>0.04794728889036966</v>
       </c>
       <c r="I52" t="n">
-        <v>7.223103550362014e-12</v>
+        <v>7.089342373503458e-12</v>
       </c>
       <c r="J52" t="n">
         <v>6.208160737416253e-25</v>
@@ -18934,10 +18934,10 @@
         <v>0.1285859807158184</v>
       </c>
       <c r="N52" t="n">
-        <v>4.718230688698351e-10</v>
+        <v>4.590710940355152e-10</v>
       </c>
       <c r="O52" t="n">
-        <v>3.048936729108179e-05</v>
+        <v>3.089589218829622e-05</v>
       </c>
       <c r="P52" t="n">
         <v>0.05196090481244512</v>
@@ -18952,10 +18952,10 @@
         <v>0.6877474427112125</v>
       </c>
       <c r="T52" t="n">
-        <v>0.3181791868867102</v>
+        <v>0.3220594208731334</v>
       </c>
       <c r="U52" t="n">
-        <v>1.54613664811242e-08</v>
+        <v>1.57067849966976e-08</v>
       </c>
       <c r="V52" t="n">
         <v>9.849919642762564e-06</v>
@@ -18971,13 +18971,13 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>6.451215002988734e-05</v>
+        <v>6.620983818856859e-05</v>
       </c>
       <c r="D53" t="n">
         <v>0.0004081605549141149</v>
       </c>
       <c r="E53" t="n">
-        <v>1.799387560631655e-14</v>
+        <v>1.863651402082785e-14</v>
       </c>
       <c r="F53" t="n">
         <v>0.003201224117832145</v>
@@ -18992,7 +18992,7 @@
         <v>3.673649119688088e-149</v>
       </c>
       <c r="J53" t="n">
-        <v>0.001667549173383387</v>
+        <v>0.001691035781459209</v>
       </c>
       <c r="K53" t="n">
         <v>4.484740614677186e-08</v>
@@ -19016,7 +19016,7 @@
         <v>0.16882125918009</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0001383825358352316</v>
+        <v>0.0001416773581170229</v>
       </c>
       <c r="S53" t="n">
         <v>0.0003195910509350183</v>
@@ -19041,16 +19041,16 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0001579066702268027</v>
+        <v>0.0001616663528512504</v>
       </c>
       <c r="D54" t="n">
         <v>0.001383821938337144</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0002203054267108037</v>
+        <v>0.0002159857124615723</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5051125082720879</v>
+        <v>0.5111257524181843</v>
       </c>
       <c r="G54" t="n">
         <v>0.0005099930918539114</v>
@@ -19062,19 +19062,19 @@
         <v>1.792780101232089e-228</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9046592112844072</v>
+        <v>0.9090535952939878</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0004347808315246862</v>
+        <v>0.0004257228975345886</v>
       </c>
       <c r="L54" t="n">
         <v>0.0003280510301892825</v>
       </c>
       <c r="M54" t="n">
-        <v>3.00002758089384e-23</v>
+        <v>2.926856176481795e-23</v>
       </c>
       <c r="N54" t="n">
-        <v>0.006497759732013386</v>
+        <v>0.006406241989308972</v>
       </c>
       <c r="O54" t="n">
         <v>1.445332769226214e-07</v>
@@ -19111,13 +19111,13 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>4.125920735792001e-05</v>
+        <v>4.243804185386059e-05</v>
       </c>
       <c r="D55" t="n">
         <v>0.05802826900128293</v>
       </c>
       <c r="E55" t="n">
-        <v>4.280470582501441e-12</v>
+        <v>4.414235288204612e-12</v>
       </c>
       <c r="F55" t="n">
         <v>0.01839972564396996</v>
@@ -19126,25 +19126,25 @@
         <v>0.0001310603053014082</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1420892274492039</v>
+        <v>0.1391290352106788</v>
       </c>
       <c r="I55" t="n">
         <v>1.709794863634244e-98</v>
       </c>
       <c r="J55" t="n">
-        <v>7.956973795472518e-06</v>
+        <v>8.075734598390018e-06</v>
       </c>
       <c r="K55" t="n">
-        <v>8.059526046639155e-11</v>
+        <v>7.781611355375736e-11</v>
       </c>
       <c r="L55" t="n">
-        <v>0.493031531527318</v>
+        <v>0.4859882239340707</v>
       </c>
       <c r="M55" t="n">
         <v>1.8806819910994e-14</v>
       </c>
       <c r="N55" t="n">
-        <v>1.035827479015479e-05</v>
+        <v>1.015907719803643e-05</v>
       </c>
       <c r="O55" t="n">
         <v>4.708151723058609e-21</v>
@@ -19156,7 +19156,7 @@
         <v>0.1001456012293997</v>
       </c>
       <c r="R55" t="n">
-        <v>2.149601910133116e-08</v>
+        <v>2.308831681254087e-08</v>
       </c>
       <c r="S55" t="n">
         <v>0.4726279933543308</v>
@@ -19181,7 +19181,7 @@
         <v>4.203651715675259e-126</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6349114225272849</v>
+        <v>0.6505882477748722</v>
       </c>
       <c r="D56" t="n">
         <v>0.01973685725608071</v>
@@ -19196,7 +19196,7 @@
         <v>0.8372627938671661</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7834111585425378</v>
+        <v>0.8064526632055535</v>
       </c>
       <c r="I56" t="n">
         <v>9.69974479528825e-296</v>
@@ -19205,7 +19205,7 @@
         <v>8.8514924007292e-07</v>
       </c>
       <c r="K56" t="n">
-        <v>0.02044121806604939</v>
+        <v>0.02080623981722884</v>
       </c>
       <c r="L56" t="n">
         <v>0.625296232019107</v>
@@ -19217,7 +19217,7 @@
         <v>0.460200973125905</v>
       </c>
       <c r="O56" t="n">
-        <v>4.291972493600556e-06</v>
+        <v>4.35417499350781e-06</v>
       </c>
       <c r="P56" t="n">
         <v>0.3232989681550383</v>
@@ -19226,10 +19226,10 @@
         <v>0.6118951330855397</v>
       </c>
       <c r="R56" t="n">
-        <v>1.77225778961566e-05</v>
+        <v>1.876508247828346e-05</v>
       </c>
       <c r="S56" t="n">
-        <v>0.1230191634105834</v>
+        <v>0.1206070229515523</v>
       </c>
       <c r="T56" t="n">
         <v>9.767212808312604e-23</v>
@@ -19238,7 +19238,7 @@
         <v>1.591201722024917e-11</v>
       </c>
       <c r="V56" t="n">
-        <v>5.461445352246319e-11</v>
+        <v>5.545467588434724e-11</v>
       </c>
     </row>
     <row r="57">
@@ -19263,7 +19263,7 @@
         <v>1.117681319119686e-25</v>
       </c>
       <c r="G57" t="n">
-        <v>6.947610092216673e-13</v>
+        <v>7.333588430673154e-13</v>
       </c>
       <c r="H57" t="n">
         <v>0.0002326602922056203</v>
@@ -19272,7 +19272,7 @@
         <v>0.7532014152005895</v>
       </c>
       <c r="J57" t="n">
-        <v>3.98136773130207e-81</v>
+        <v>3.791778791716257e-81</v>
       </c>
       <c r="K57" t="n">
         <v>1.328540614477976e-07</v>
@@ -19296,7 +19296,7 @@
         <v>2.196235363822142e-07</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0002928420607124426</v>
+        <v>0.0003058572634107734</v>
       </c>
       <c r="S57" t="n">
         <v>0.000542843973219924</v>
@@ -19327,13 +19327,13 @@
         <v>8.058584547602639e-09</v>
       </c>
       <c r="E58" t="n">
-        <v>6.739991248311509e-12</v>
+        <v>6.944233407351252e-12</v>
       </c>
       <c r="F58" t="n">
         <v>4.459086914233833e-10</v>
       </c>
       <c r="G58" t="n">
-        <v>6.588440640143158e-11</v>
+        <v>7.095243766308016e-11</v>
       </c>
       <c r="H58" t="n">
         <v>0.004719211689712817</v>
@@ -19354,7 +19354,7 @@
         <v>1.110332708846797e-12</v>
       </c>
       <c r="N58" t="n">
-        <v>2.672502201709306e-05</v>
+        <v>2.622077631865734e-05</v>
       </c>
       <c r="O58" t="n">
         <v>1.705401036074304e-32</v>
@@ -19366,7 +19366,7 @@
         <v>0.001179657510866882</v>
       </c>
       <c r="R58" t="n">
-        <v>1.145094280426633e-07</v>
+        <v>1.2240662997664e-07</v>
       </c>
       <c r="S58" t="n">
         <v>0.000343799548223</v>
@@ -19391,7 +19391,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.3864649622779691</v>
+        <v>0.3919858903105115</v>
       </c>
       <c r="D59" t="n">
         <v>0.007995038651203027</v>
@@ -19403,7 +19403,7 @@
         <v>0.001076689308604651</v>
       </c>
       <c r="G59" t="n">
-        <v>3.389826621553397e-09</v>
+        <v>3.457623153984465e-09</v>
       </c>
       <c r="H59" t="n">
         <v>1.633122483008546e-07</v>
@@ -19436,7 +19436,7 @@
         <v>5.636106323817813e-10</v>
       </c>
       <c r="R59" t="n">
-        <v>1.435923112565118e-06</v>
+        <v>1.528563313375771e-06</v>
       </c>
       <c r="S59" t="n">
         <v>0.007689280893754145</v>
@@ -19458,13 +19458,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.182958291442757e-28</v>
+        <v>3.266720351743883e-28</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7396975337141173</v>
+        <v>0.7485034567345236</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2233979747945473</v>
+        <v>0.2264582210246096</v>
       </c>
       <c r="E60" t="n">
         <v>1.013883893071195e-52</v>
@@ -19473,13 +19473,13 @@
         <v>0.1383382713754171</v>
       </c>
       <c r="G60" t="n">
-        <v>2.239932074283271e-18</v>
+        <v>2.399927222446361e-18</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>2.077829350247216e-25</v>
+        <v>2.023149630503868e-25</v>
       </c>
       <c r="J60" t="n">
         <v>0.1100399102441618</v>
@@ -19494,19 +19494,19 @@
         <v>1.552666631391674e-08</v>
       </c>
       <c r="N60" t="n">
-        <v>0.9796015004958213</v>
+        <v>0.9693973181989899</v>
       </c>
       <c r="O60" t="n">
-        <v>9.51506255574796e-06</v>
+        <v>9.649077521321877e-06</v>
       </c>
       <c r="P60" t="n">
         <v>0.007008669085123127</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.003635782741728188</v>
+        <v>0.003598250038461274</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0004215724564781537</v>
+        <v>0.0004301759759981159</v>
       </c>
       <c r="S60" t="n">
         <v>2.468883067164447e-05</v>
@@ -19534,7 +19534,7 @@
         <v>5.996443539470161e-08</v>
       </c>
       <c r="D61" t="n">
-        <v>0.08669806192864279</v>
+        <v>0.08793660567048055</v>
       </c>
       <c r="E61" t="n">
         <v>9.284950420372532e-42</v>
@@ -19564,7 +19564,7 @@
         <v>3.049305235782119e-82</v>
       </c>
       <c r="N61" t="n">
-        <v>0.05160472100464221</v>
+        <v>0.05091665805791364</v>
       </c>
       <c r="O61" t="n">
         <v>7.522210066852002e-40</v>
@@ -19601,61 +19601,61 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1.28131269205314e-30</v>
+        <v>1.171291972470647e-31</v>
       </c>
       <c r="D62" t="n">
-        <v>2.192189028325097e-30</v>
+        <v>4.763754422863546e-34</v>
       </c>
       <c r="E62" t="n">
-        <v>1.501877539431384e-63</v>
+        <v>4.16510099937206e-64</v>
       </c>
       <c r="F62" t="n">
-        <v>6.338586433636175e-29</v>
+        <v>1.724158685530776e-30</v>
       </c>
       <c r="G62" t="n">
-        <v>1.413750097627189e-95</v>
+        <v>1.277002665740362e-101</v>
       </c>
       <c r="H62" t="n">
-        <v>1.193057001006756e-12</v>
+        <v>2.480945305858199e-12</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1.468977392916034e-80</v>
+        <v>1.519500727725117e-89</v>
       </c>
       <c r="K62" t="n">
-        <v>1.736713682161009e-61</v>
+        <v>7.084095351872126e-64</v>
       </c>
       <c r="L62" t="n">
-        <v>1.475255402904295e-20</v>
+        <v>5.352783703813157e-22</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.201119083935472e-87</v>
+        <v>1.323462199897513e-94</v>
       </c>
       <c r="O62" t="n">
-        <v>7.966091514702447e-180</v>
+        <v>1.660400940003845e-202</v>
       </c>
       <c r="P62" t="n">
-        <v>3.976684650663944e-27</v>
+        <v>3.116617423129128e-28</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.305683249707737e-16</v>
+        <v>3.893961761434116e-20</v>
       </c>
       <c r="R62" t="n">
-        <v>5.70955548417493e-32</v>
+        <v>1.33983915660242e-32</v>
       </c>
       <c r="S62" t="n">
-        <v>1.84161774647313e-18</v>
+        <v>1.475471965703856e-20</v>
       </c>
       <c r="T62" t="n">
-        <v>1.719142789267179e-205</v>
+        <v>1.283400497478451e-216</v>
       </c>
       <c r="U62" t="n">
-        <v>1.935111663912493e-240</v>
+        <v>6.837114590297185e-262</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -19668,67 +19668,67 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.184311451912072e-38</v>
+        <v>7.74843213818668e-24</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1008689470160526</v>
+        <v>0.1403709459700757</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0714541102399783</v>
+        <v>0.2524666523555015</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0003484030933363383</v>
+        <v>0.0003599003913765015</v>
       </c>
       <c r="F63" t="n">
-        <v>1.045599695620737e-05</v>
+        <v>4.020633146753118e-05</v>
       </c>
       <c r="G63" t="n">
-        <v>0.006421307341714468</v>
+        <v>0.001027853719089054</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1484868988566538</v>
+        <v>0.1088906081723443</v>
       </c>
       <c r="I63" t="n">
-        <v>3.401367772551162e-13</v>
+        <v>7.292986510429395e-14</v>
       </c>
       <c r="J63" t="n">
-        <v>1.315501111162752e-31</v>
+        <v>4.317034671085963e-27</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0001181152463439165</v>
+        <v>0.0003389481579060573</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5916660583947838</v>
+        <v>0.4391595307857605</v>
       </c>
       <c r="M63" t="n">
-        <v>9.453455160535995e-05</v>
+        <v>6.690543032917373e-07</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>0.6662981750770669</v>
       </c>
       <c r="O63" t="n">
-        <v>2.273833998463059e-06</v>
+        <v>0.001294964752609436</v>
       </c>
       <c r="P63" t="n">
-        <v>0.01409202457434674</v>
+        <v>0.02475164254434495</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.8941572615836049</v>
+        <v>0.8356654698832023</v>
       </c>
       <c r="R63" t="n">
-        <v>4.62458613227193e-07</v>
+        <v>5.619612114040568e-07</v>
       </c>
       <c r="S63" t="n">
-        <v>0.1300310799888169</v>
+        <v>0.05516597363656736</v>
       </c>
       <c r="T63" t="n">
-        <v>0.0248884839798317</v>
+        <v>0.1073497162438626</v>
       </c>
       <c r="U63" t="n">
-        <v>0.8971788056695666</v>
+        <v>0.3731357589114339</v>
       </c>
       <c r="V63" t="n">
-        <v>1.719453341099187e-14</v>
+        <v>2.079500010848527e-10</v>
       </c>
     </row>
     <row r="64">
@@ -19741,7 +19741,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>9.095619455733294e-27</v>
+        <v>1.023257188769996e-26</v>
       </c>
       <c r="D64" t="n">
         <v>6.008417585098032e-35</v>
@@ -19753,13 +19753,13 @@
         <v>1.159131499271846e-30</v>
       </c>
       <c r="G64" t="n">
-        <v>8.279876955794305e-67</v>
+        <v>8.7398701200051e-67</v>
       </c>
       <c r="H64" t="n">
-        <v>3.580869886131663e-05</v>
+        <v>3.305418356429227e-05</v>
       </c>
       <c r="I64" t="n">
-        <v>2.689015950938498e-138</v>
+        <v>2.857079447872154e-138</v>
       </c>
       <c r="J64" t="n">
         <v>2.436835725238744e-122</v>
@@ -19820,10 +19820,10 @@
         <v>1.953386154048485e-84</v>
       </c>
       <c r="F65" t="n">
-        <v>1.896787038893165e-30</v>
+        <v>1.796956142109314e-30</v>
       </c>
       <c r="G65" t="n">
-        <v>6.131411639085458e-13</v>
+        <v>6.481778018461771e-13</v>
       </c>
       <c r="H65" t="n">
         <v>1.800953230063211e-19</v>
@@ -19835,7 +19835,7 @@
         <v>4.490088187712634e-91</v>
       </c>
       <c r="K65" t="n">
-        <v>2.673404403774461e-62</v>
+        <v>1.782269602516307e-62</v>
       </c>
       <c r="L65" t="n">
         <v>2.885843189204632e-07</v>
@@ -19899,7 +19899,7 @@
         <v>2.159988627873655e-24</v>
       </c>
       <c r="I66" t="n">
-        <v>1.124814082652878e-20</v>
+        <v>1.150972549691317e-20</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -19957,7 +19957,7 @@
         <v>1.330898569078903e-19</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3826301297107614</v>
+        <v>0.3877318647735715</v>
       </c>
       <c r="F67" t="n">
         <v>1.768746613523796e-22</v>
@@ -19966,10 +19966,10 @@
         <v>4.297830876432982e-85</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2309699547350617</v>
+        <v>0.2332180736769475</v>
       </c>
       <c r="I67" t="n">
-        <v>2.587203079056711e-20</v>
+        <v>2.643446624253596e-20</v>
       </c>
       <c r="J67" t="n">
         <v>1.385695023495388e-94</v>
@@ -19996,7 +19996,7 @@
         <v>2.385923036965226e-07</v>
       </c>
       <c r="R67" t="n">
-        <v>5.163233288454575e-05</v>
+        <v>5.44232697972239e-05</v>
       </c>
       <c r="S67" t="n">
         <v>0.0001728129970659434</v>
@@ -20021,7 +20021,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1725685443483753</v>
+        <v>0.175223445030658</v>
       </c>
       <c r="D68" t="n">
         <v>0.01973685725608071</v>
@@ -20054,7 +20054,7 @@
         <v>4.281714531388889e-53</v>
       </c>
       <c r="N68" t="n">
-        <v>2.297036316063922e-11</v>
+        <v>2.231406707033524e-11</v>
       </c>
       <c r="O68" t="n">
         <v>2.040813249187114e-122</v>
@@ -20069,7 +20069,7 @@
         <v>1.373724038085617e-49</v>
       </c>
       <c r="S68" t="n">
-        <v>0.06980915704327331</v>
+        <v>0.06825784244231169</v>
       </c>
       <c r="T68" t="n">
         <v>3.474720978072489e-199</v>
@@ -20109,7 +20109,7 @@
         <v>3.045439478797938e-21</v>
       </c>
       <c r="I69" t="n">
-        <v>1.100578512090898e-24</v>
+        <v>1.073064049288626e-24</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -20158,13 +20158,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6.159191168886935e-84</v>
+        <v>6.269176725474202e-84</v>
       </c>
       <c r="C70" t="n">
         <v>0.4507527132687596</v>
       </c>
       <c r="D70" t="n">
-        <v>0.07808003487655436</v>
+        <v>0.07921162958491022</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -20173,7 +20173,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.02463913329518415</v>
+        <v>0.02495912203927745</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
@@ -20243,7 +20243,7 @@
         <v>1.117681319119686e-25</v>
       </c>
       <c r="G71" t="n">
-        <v>5.962007368157789e-20</v>
+        <v>6.649931295252918e-20</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
@@ -20276,7 +20276,7 @@
         <v>0.004522092034086658</v>
       </c>
       <c r="R71" t="n">
-        <v>1.050212420963423e-05</v>
+        <v>1.148669835428743e-05</v>
       </c>
       <c r="S71" t="n">
         <v>4.263316728021519e-09</v>
@@ -20298,10 +20298,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.506289506644169e-62</v>
+        <v>1.531394331754905e-62</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1725685443483753</v>
+        <v>0.175223445030658</v>
       </c>
       <c r="D72" t="n">
         <v>0.4660064171666479</v>
@@ -20337,7 +20337,7 @@
         <v>6.655845907410632e-09</v>
       </c>
       <c r="O72" t="n">
-        <v>9.271570265087984e-11</v>
+        <v>9.449869693262754e-11</v>
       </c>
       <c r="P72" t="n">
         <v>0.0008625402100019909</v>
@@ -20346,16 +20346,16 @@
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>1.3870810289915e-19</v>
+        <v>1.305488027286118e-19</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>0.0251937294264822</v>
+        <v>0.02553418522954277</v>
       </c>
       <c r="U72" t="n">
-        <v>0.08880554870858641</v>
+        <v>0.08986275762178389</v>
       </c>
       <c r="V72" t="n">
         <v>0.0001056837681711115</v>
@@ -20364,14 +20364,14 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Function:DNA binding region</t>
+          <t>Function:DNA binding</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>6.36414922971888e-05</v>
+        <v>6.536153262954523e-05</v>
       </c>
       <c r="D73" t="n">
         <v>0.4254475944753193</v>
@@ -20438,7 +20438,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.63365452800615e-42</v>
+        <v>1.658037431409227e-42</v>
       </c>
       <c r="C74" t="n">
         <v>6.063129291207971e-10</v>
@@ -20477,10 +20477,10 @@
         <v>0.7035457888586958</v>
       </c>
       <c r="O74" t="n">
-        <v>4.805898050652993e-27</v>
+        <v>4.943209423528793e-27</v>
       </c>
       <c r="P74" t="n">
-        <v>0.09514646207651363</v>
+        <v>0.09376752784352067</v>
       </c>
       <c r="Q74" t="n">
         <v>0.7175658996576265</v>
@@ -20514,10 +20514,10 @@
         <v>9.45732528258914e-71</v>
       </c>
       <c r="D75" t="n">
-        <v>3.158263853649566e-64</v>
+        <v>2.807345647688503e-64</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2958481230585297</v>
+        <v>0.2917954090440293</v>
       </c>
       <c r="F75" t="n">
         <v>1.414731485180472e-201</v>
@@ -20535,7 +20535,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>2.230536727445512e-11</v>
+        <v>2.147924256058641e-11</v>
       </c>
       <c r="L75" t="n">
         <v>2.122927376327227e-29</v>
@@ -20556,10 +20556,10 @@
         <v>5.322878537149543e-23</v>
       </c>
       <c r="R75" t="n">
-        <v>1.115580153528476e-10</v>
+        <v>1.160203359669615e-10</v>
       </c>
       <c r="S75" t="n">
-        <v>3.745594201490628e-20</v>
+        <v>3.210509315563395e-20</v>
       </c>
       <c r="T75" t="n">
         <v>8.883523689223717e-85</v>
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.656931850368087e-42</v>
+        <v>1.681298495226441e-42</v>
       </c>
       <c r="C76" t="n">
         <v>0.03444732204977169</v>
@@ -20587,13 +20587,13 @@
         <v>3.891683942064935e-60</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1269042244637489</v>
+        <v>0.1249213459565029</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0008020676135909703</v>
+        <v>0.0007877449776339886</v>
       </c>
       <c r="G76" t="n">
-        <v>3.240396448430905e-05</v>
+        <v>3.295318422133124e-05</v>
       </c>
       <c r="H76" t="n">
         <v>6.389553611027512e-06</v>
@@ -20614,7 +20614,7 @@
         <v>2.461706769348749e-07</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8675461395951212</v>
+        <v>0.8583169253441093</v>
       </c>
       <c r="O76" t="n">
         <v>0.174812694965532</v>
@@ -20638,7 +20638,7 @@
         <v>1.78406318096834e-45</v>
       </c>
       <c r="V76" t="n">
-        <v>1.689057896911411e-26</v>
+        <v>1.756620212787867e-26</v>
       </c>
     </row>
     <row r="77">
@@ -20651,19 +20651,19 @@
         <v>3.226075757941117e-268</v>
       </c>
       <c r="C77" t="n">
-        <v>7.684849426827123e-05</v>
+        <v>7.881896848027818e-05</v>
       </c>
       <c r="D77" t="n">
         <v>0.0001428786428503215</v>
       </c>
       <c r="E77" t="n">
-        <v>4.136256787304575e-15</v>
+        <v>4.295343586816289e-15</v>
       </c>
       <c r="F77" t="n">
         <v>0.002527767634794461</v>
       </c>
       <c r="G77" t="n">
-        <v>1.655614595957926e-05</v>
+        <v>1.685179142314317e-05</v>
       </c>
       <c r="H77" t="n">
         <v>1.222170718238465e-28</v>
@@ -20675,7 +20675,7 @@
         <v>7.844830449332123e-25</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03873531497091458</v>
+        <v>0.03894986754935127</v>
       </c>
       <c r="L77" t="n">
         <v>4.971764291442755e-18</v>
@@ -20687,7 +20687,7 @@
         <v>2.674501753608332e-08</v>
       </c>
       <c r="O77" t="n">
-        <v>8.322888294299248e-06</v>
+        <v>8.441786698503522e-06</v>
       </c>
       <c r="P77" t="n">
         <v>0.00461712793539258</v>
@@ -20696,7 +20696,7 @@
         <v>3.922495809006033e-65</v>
       </c>
       <c r="R77" t="n">
-        <v>0.001693755172854286</v>
+        <v>0.001725712817625121</v>
       </c>
       <c r="S77" t="n">
         <v>0.1311438805223523</v>
@@ -20718,7 +20718,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.371969414061902e-53</v>
+        <v>2.409619722221615e-53</v>
       </c>
       <c r="C78" t="n">
         <v>2.732937812781895e-09</v>
@@ -20727,7 +20727,7 @@
         <v>2.141042408670931e-07</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0806239455289265</v>
+        <v>0.07932355931071801</v>
       </c>
       <c r="F78" t="n">
         <v>0.005620578364977508</v>
@@ -20757,7 +20757,7 @@
         <v>0.002084920917983612</v>
       </c>
       <c r="O78" t="n">
-        <v>1.029915000498784e-05</v>
+        <v>1.044219375505711e-05</v>
       </c>
       <c r="P78" t="n">
         <v>0.2176273630473285</v>
@@ -20791,7 +20791,7 @@
         <v>4.902673513697265e-112</v>
       </c>
       <c r="C79" t="n">
-        <v>0.394094136466216</v>
+        <v>0.3994926862808217</v>
       </c>
       <c r="D79" t="n">
         <v>0.006806681729049926</v>
@@ -20800,22 +20800,22 @@
         <v>0.001830467298431405</v>
       </c>
       <c r="F79" t="n">
-        <v>4.325085498986012e-07</v>
+        <v>4.214185870806883e-07</v>
       </c>
       <c r="G79" t="n">
         <v>0.347915675655587</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8433915866925387</v>
+        <v>0.8661859539004451</v>
       </c>
       <c r="I79" t="n">
-        <v>7.339566962419467e-25</v>
+        <v>7.151372937742044e-25</v>
       </c>
       <c r="J79" t="n">
         <v>3.282126325995603e-11</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1013291207339948</v>
+        <v>0.09983898660555368</v>
       </c>
       <c r="L79" t="n">
         <v>1.919106945465559e-06</v>
@@ -20824,7 +20824,7 @@
         <v>2.568672354594623e-08</v>
       </c>
       <c r="N79" t="n">
-        <v>3.564751927286301e-05</v>
+        <v>3.498738002706925e-05</v>
       </c>
       <c r="O79" t="n">
         <v>8.442077020908253e-17</v>
@@ -20842,7 +20842,7 @@
         <v>0.6389132284901318</v>
       </c>
       <c r="T79" t="n">
-        <v>0.6452870233927234</v>
+        <v>0.6526198304767317</v>
       </c>
       <c r="U79" t="n">
         <v>0.02342966312265216</v>
@@ -20861,7 +20861,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>1.561955031710722e-27</v>
+        <v>1.770215702605485e-27</v>
       </c>
       <c r="D80" t="n">
         <v>1.436787213600484e-13</v>
@@ -20873,7 +20873,7 @@
         <v>1.099655648879658e-74</v>
       </c>
       <c r="G80" t="n">
-        <v>3.115904081079893e-99</v>
+        <v>2.876219151766055e-99</v>
       </c>
       <c r="H80" t="n">
         <v>0.01008027620851285</v>
@@ -20885,7 +20885,7 @@
         <v>9.181632842710579e-128</v>
       </c>
       <c r="K80" t="n">
-        <v>0.007388040745421429</v>
+        <v>0.007243177201393557</v>
       </c>
       <c r="L80" t="n">
         <v>1.178250683195375e-07</v>
@@ -20906,7 +20906,7 @@
         <v>1.056412196023978e-10</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001714413413237382</v>
+        <v>0.001746161809778815</v>
       </c>
       <c r="S80" t="n">
         <v>7.105574075871103e-10</v>
@@ -20928,22 +20928,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4.84961032373863e-36</v>
+        <v>5.051677420561074e-36</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2233525697315598</v>
+        <v>0.2266861901753144</v>
       </c>
       <c r="D81" t="n">
-        <v>0.1846175859551353</v>
+        <v>0.1871817190934011</v>
       </c>
       <c r="E81" t="n">
         <v>2.370251979068832e-32</v>
       </c>
       <c r="F81" t="n">
-        <v>7.20672755107825e-14</v>
+        <v>6.96650329937564e-14</v>
       </c>
       <c r="G81" t="n">
-        <v>6.876468408834713e-67</v>
+        <v>7.280966550530871e-67</v>
       </c>
       <c r="H81" t="n">
         <v>0.0001204367326139664</v>
@@ -20955,7 +20955,7 @@
         <v>1.179326947150521e-11</v>
       </c>
       <c r="K81" t="n">
-        <v>0.02120040133891104</v>
+        <v>0.02157233820450597</v>
       </c>
       <c r="L81" t="n">
         <v>1</v>
@@ -20964,7 +20964,7 @@
         <v>4.006905193459758e-10</v>
       </c>
       <c r="N81" t="n">
-        <v>6.647243039633814e-17</v>
+        <v>6.391579845801744e-17</v>
       </c>
       <c r="O81" t="n">
         <v>2.880821179312545e-17</v>
@@ -20979,7 +20979,7 @@
         <v>2.434545556992259e-34</v>
       </c>
       <c r="S81" t="n">
-        <v>0.09971963734568701</v>
+        <v>0.09759794293407663</v>
       </c>
       <c r="T81" t="n">
         <v>2.804685922238165e-13</v>
@@ -20988,7 +20988,7 @@
         <v>2.708596965948574e-267</v>
       </c>
       <c r="V81" t="n">
-        <v>2.364579651039637e-10</v>
+        <v>2.399352881201985e-10</v>
       </c>
     </row>
     <row r="82">
@@ -21001,7 +21001,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>4.858206002872601e-46</v>
+        <v>4.372385402585341e-46</v>
       </c>
       <c r="D82" t="n">
         <v>8.77660192464051e-85</v>
@@ -21019,7 +21019,7 @@
         <v>2.226858210183539e-31</v>
       </c>
       <c r="I82" t="n">
-        <v>2.608390684504659e-14</v>
+        <v>2.660558498194752e-14</v>
       </c>
       <c r="J82" t="n">
         <v>9.740028886007595e-250</v>
@@ -21034,7 +21034,7 @@
         <v>2.350067236116786e-147</v>
       </c>
       <c r="N82" t="n">
-        <v>3.058087886352494e-12</v>
+        <v>2.965418556463024e-12</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -21068,7 +21068,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3.449772049337242e-84</v>
+        <v>3.51249517750701e-84</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -21080,7 +21080,7 @@
         <v>0.01515765157847841</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4160720418656768</v>
+        <v>0.4211460911567216</v>
       </c>
       <c r="G83" t="n">
         <v>3.485874452728023e-94</v>
@@ -21153,7 +21153,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>2.282635668313303e-10</v>
+        <v>2.391332604899651e-10</v>
       </c>
       <c r="H84" t="n">
         <v>0.4928391281738051</v>
@@ -21174,7 +21174,7 @@
         <v>1.849690627096071e-07</v>
       </c>
       <c r="N84" t="n">
-        <v>0.001060986673209532</v>
+        <v>0.001078379897360508</v>
       </c>
       <c r="O84" t="n">
         <v>2.451518120980388e-29</v>
@@ -21262,7 +21262,7 @@
         <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>4.157152175050772e-06</v>
+        <v>4.078715341559248e-06</v>
       </c>
       <c r="U85" t="n">
         <v>8.578339559829139e-83</v>
@@ -21284,7 +21284,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3170141301039043</v>
+        <v>0.3171442442229303</v>
       </c>
       <c r="E86" t="n">
         <v>0.1401469381090643</v>
@@ -21311,7 +21311,7 @@
         <v>0.8662414774633862</v>
       </c>
       <c r="M86" t="n">
-        <v>3.26295343685457e-06</v>
+        <v>3.214968827489062e-06</v>
       </c>
       <c r="N86" t="n">
         <v>0.7451446943140205</v>
@@ -21326,7 +21326,7 @@
         <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001905779206014274</v>
+        <v>0.001940429737032715</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -21335,7 +21335,7 @@
         <v>0.01976817338129612</v>
       </c>
       <c r="U86" t="n">
-        <v>7.614866288486995e-09</v>
+        <v>7.490032414905242e-09</v>
       </c>
       <c r="V86" t="n">
         <v>0.0004460806646098046</v>
@@ -21396,7 +21396,7 @@
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0.8376939972496905</v>
+        <v>0.8474346251246868</v>
       </c>
       <c r="S87" t="n">
         <v>0.0001728129970659434</v>
@@ -21418,7 +21418,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7.75825786970443e-33</v>
+        <v>8.077090384897763e-33</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -21427,7 +21427,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>3.351176517415247e-05</v>
+        <v>3.278324853993177e-05</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -21436,7 +21436,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2970312282989027</v>
+        <v>0.3024317960861556</v>
       </c>
       <c r="I88" t="n">
         <v>3.560338286319762e-40</v>
@@ -21448,13 +21448,13 @@
         <v>2.261016769269951e-21</v>
       </c>
       <c r="L88" t="n">
-        <v>0.5287892424758246</v>
+        <v>0.5214449474414381</v>
       </c>
       <c r="M88" t="n">
         <v>3.667494204067273e-13</v>
       </c>
       <c r="N88" t="n">
-        <v>7.469965174872075e-07</v>
+        <v>7.320565871374634e-07</v>
       </c>
       <c r="O88" t="n">
         <v>1.385035768709707e-13</v>
@@ -21463,22 +21463,22 @@
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.505150760514223e-17</v>
+        <v>4.254864607152323e-17</v>
       </c>
       <c r="R88" t="n">
-        <v>0.7225095576839584</v>
+        <v>0.7399194265438129</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>0.07194273994722324</v>
+        <v>0.07287706124523911</v>
       </c>
       <c r="U88" t="n">
-        <v>0.3911218778862935</v>
+        <v>0.38687055312666</v>
       </c>
       <c r="V88" t="n">
-        <v>1.758820238265657e-06</v>
+        <v>1.782913666187105e-06</v>
       </c>
     </row>
     <row r="89">
@@ -21506,7 +21506,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.8433915866925387</v>
+        <v>0.8635017342770506</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -21536,7 +21536,7 @@
         <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0001334706908927154</v>
+        <v>0.0001367260735974158</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -21548,7 +21548,7 @@
         <v>1</v>
       </c>
       <c r="V89" t="n">
-        <v>0.270813334260555</v>
+        <v>0.268077846035701</v>
       </c>
     </row>
     <row r="90">
@@ -21567,13 +21567,13 @@
         <v>0.9904183207824132</v>
       </c>
       <c r="E90" t="n">
-        <v>6.67058474774e-05</v>
+        <v>6.534450365133061e-05</v>
       </c>
       <c r="F90" t="n">
         <v>0.002184128107061422</v>
       </c>
       <c r="G90" t="n">
-        <v>0.001404270926175184</v>
+        <v>0.00138420991294411</v>
       </c>
       <c r="H90" t="n">
         <v>0.05923790213748835</v>
@@ -21588,7 +21588,7 @@
         <v>0.0001385109061643857</v>
       </c>
       <c r="L90" t="n">
-        <v>0.7193972031487129</v>
+        <v>0.7283896681880718</v>
       </c>
       <c r="M90" t="n">
         <v>8.90873958339161e-20</v>
@@ -21603,7 +21603,7 @@
         <v>0.3833005192594703</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.00253680849767194</v>
+        <v>0.002481660486852985</v>
       </c>
       <c r="R90" t="n">
         <v>0.03277870408862692</v>
@@ -21643,7 +21643,7 @@
         <v>0.2927177870889919</v>
       </c>
       <c r="G91" t="n">
-        <v>9.704766659601438e-11</v>
+        <v>1.017816991128931e-10</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
@@ -21664,10 +21664,10 @@
         <v>0.000276457992088326</v>
       </c>
       <c r="N91" t="n">
-        <v>0.04409565836307185</v>
+        <v>0.0434997710878952</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0004065614605446916</v>
+        <v>0.0004119109534465956</v>
       </c>
       <c r="P91" t="n">
         <v>0.1624701592402025</v>
@@ -21676,16 +21676,16 @@
         <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>2.227940997185418e-05</v>
+        <v>2.355251911310299e-05</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>0.6383621496788946</v>
+        <v>0.6457849653728351</v>
       </c>
       <c r="U91" t="n">
-        <v>0.8218272731109074</v>
+        <v>0.813354826996362</v>
       </c>
       <c r="V91" t="n">
         <v>0.006444725486380705</v>
@@ -21707,13 +21707,13 @@
         <v>5.023072162913633e-10</v>
       </c>
       <c r="E92" t="n">
-        <v>0.6968144575638958</v>
+        <v>0.713405277982084</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8027760386287913</v>
+        <v>0.8120033494176281</v>
       </c>
       <c r="G92" t="n">
-        <v>7.912323388615098e-06</v>
+        <v>8.056183813862645e-06</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
@@ -21749,7 +21749,7 @@
         <v>1</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0593957367409611</v>
+        <v>0.05804583363321199</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
@@ -21771,19 +21771,19 @@
         <v>3.92173945349764e-07</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0006611674467388873</v>
+        <v>0.0006761939796193165</v>
       </c>
       <c r="D93" t="n">
         <v>0.243675714725167</v>
       </c>
       <c r="E93" t="n">
-        <v>0.5986519766321574</v>
+        <v>0.6060427417757643</v>
       </c>
       <c r="F93" t="n">
         <v>9.169995504874738e-05</v>
       </c>
       <c r="G93" t="n">
-        <v>7.991051426161743e-10</v>
+        <v>8.346209267324486e-10</v>
       </c>
       <c r="H93" t="n">
         <v>0.4992426150771688</v>
@@ -21792,10 +21792,10 @@
         <v>2.613671010528508e-10</v>
       </c>
       <c r="J93" t="n">
-        <v>0.9006490945313239</v>
+        <v>0.9090535952939878</v>
       </c>
       <c r="K93" t="n">
-        <v>0.5152357929811812</v>
+        <v>0.522015211309881</v>
       </c>
       <c r="L93" t="n">
         <v>1</v>
@@ -21804,7 +21804,7 @@
         <v>0.8530236279589689</v>
       </c>
       <c r="N93" t="n">
-        <v>0.07044218812192041</v>
+        <v>0.06951531722557935</v>
       </c>
       <c r="O93" t="n">
         <v>0.1027869350398009</v>
@@ -21853,7 +21853,7 @@
         <v>0.02857829073317857</v>
       </c>
       <c r="G94" t="n">
-        <v>2.32683577964494e-07</v>
+        <v>2.371582621561189e-07</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -21874,7 +21874,7 @@
         <v>0.09995150864154836</v>
       </c>
       <c r="N94" t="n">
-        <v>0.6536316797632893</v>
+        <v>0.6613214642310926</v>
       </c>
       <c r="O94" t="n">
         <v>0.7826199051669964</v>
@@ -21911,7 +21911,7 @@
         <v>5.755092005811856e-06</v>
       </c>
       <c r="C95" t="n">
-        <v>0.6594116760920949</v>
+        <v>0.6673563950811564</v>
       </c>
       <c r="D95" t="n">
         <v>0.01351863439156888</v>
@@ -21923,7 +21923,7 @@
         <v>0.009378190483402471</v>
       </c>
       <c r="G95" t="n">
-        <v>1.327003401654896e-09</v>
+        <v>1.384699201726848e-09</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
@@ -21938,7 +21938,7 @@
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0.5287892424758246</v>
+        <v>0.5214449474414381</v>
       </c>
       <c r="M95" t="n">
         <v>0.00596020019308755</v>
@@ -21987,7 +21987,7 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0.8058747702598105</v>
+        <v>0.8246160439867828</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -22014,7 +22014,7 @@
         <v>0.1836628407098301</v>
       </c>
       <c r="N96" t="n">
-        <v>0.6584523681758917</v>
+        <v>0.6661087910616578</v>
       </c>
       <c r="O96" t="n">
         <v>0.3406748811475743</v>
@@ -22032,7 +22032,7 @@
         <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>0.6452870233927234</v>
+        <v>0.6526198304767317</v>
       </c>
       <c r="U96" t="n">
         <v>0.218389782566792</v>
@@ -22075,7 +22075,7 @@
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0.5499350860110355</v>
+        <v>0.5569855358316897</v>
       </c>
       <c r="L97" t="n">
         <v>1</v>
@@ -22084,7 +22084,7 @@
         <v>0.7957452289206935</v>
       </c>
       <c r="N97" t="n">
-        <v>0.1652600467185839</v>
+        <v>0.1631681473930323</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -22108,7 +22108,7 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.1547764056211615</v>
+        <v>0.1564229631277696</v>
       </c>
     </row>
     <row r="98">
@@ -22127,7 +22127,7 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1841890611272501</v>
+        <v>0.1815333616446312</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
@@ -22148,13 +22148,13 @@
         <v>0.04759741341260426</v>
       </c>
       <c r="L98" t="n">
-        <v>0.7276024461306754</v>
+        <v>0.7365851923792023</v>
       </c>
       <c r="M98" t="n">
         <v>0.8530236279589689</v>
       </c>
       <c r="N98" t="n">
-        <v>0.56606066587881</v>
+        <v>0.5728806739014463</v>
       </c>
       <c r="O98" t="n">
         <v>0.6063943025412368</v>
@@ -22200,10 +22200,10 @@
         <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1956925004412862</v>
+        <v>0.1930832671020691</v>
       </c>
       <c r="G99" t="n">
-        <v>0.009221709287688142</v>
+        <v>0.009343047567789304</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -22212,7 +22212,7 @@
         <v>0.4671866233632822</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9046592112844072</v>
+        <v>0.9090535952939878</v>
       </c>
       <c r="K99" t="n">
         <v>1</v>
@@ -22224,7 +22224,7 @@
         <v>0.1709279419763337</v>
       </c>
       <c r="N99" t="n">
-        <v>0.6536316797632893</v>
+        <v>0.6613214642310926</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
@@ -22270,13 +22270,13 @@
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2330793648682078</v>
+        <v>0.230012531119942</v>
       </c>
       <c r="G100" t="n">
-        <v>0.006150877537628768</v>
+        <v>0.006067757570904054</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2309699547350617</v>
+        <v>0.2332180736769475</v>
       </c>
       <c r="I100" t="n">
         <v>2.799132613881654e-05</v>
@@ -22288,7 +22288,7 @@
         <v>0.7611418613035594</v>
       </c>
       <c r="L100" t="n">
-        <v>0.7193972031487129</v>
+        <v>0.7283896681880718</v>
       </c>
       <c r="M100" t="n">
         <v>0.1446730202768181</v>
@@ -22303,10 +22303,10 @@
         <v>0.05641774217877538</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.0515701567035805</v>
+        <v>0.04985115148012781</v>
       </c>
       <c r="R100" t="n">
-        <v>0.02439886353473512</v>
+        <v>0.0239922158091562</v>
       </c>
       <c r="S100" t="n">
         <v>0.3755359513052301</v>
@@ -22315,7 +22315,7 @@
         <v>0.0008877726183719859</v>
       </c>
       <c r="U100" t="n">
-        <v>0.4583557609945644</v>
+        <v>0.4534272044247303</v>
       </c>
       <c r="V100" t="n">
         <v>0.0001716111837181965</v>
@@ -22331,13 +22331,13 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.000112625619367188</v>
+        <v>0.000115372585693217</v>
       </c>
       <c r="D101" t="n">
         <v>2.104371350256244e-63</v>
       </c>
       <c r="E101" t="n">
-        <v>3.443141060424674e-05</v>
+        <v>3.369882739990106e-05</v>
       </c>
       <c r="F101" t="n">
         <v>1.310396649472876e-17</v>
@@ -22346,13 +22346,13 @@
         <v>1.065836160619804e-111</v>
       </c>
       <c r="H101" t="n">
-        <v>4.582522154319956e-05</v>
+        <v>4.243076068814774e-05</v>
       </c>
       <c r="I101" t="n">
         <v>0.05328341763280907</v>
       </c>
       <c r="J101" t="n">
-        <v>2.002539754797487e-28</v>
+        <v>2.067137811403858e-28</v>
       </c>
       <c r="K101" t="n">
         <v>1.008755498593212e-43</v>
@@ -22379,7 +22379,7 @@
         <v>1.589352503481029e-26</v>
       </c>
       <c r="S101" t="n">
-        <v>0.0593957367409611</v>
+        <v>0.05804583363321199</v>
       </c>
       <c r="T101" t="n">
         <v>6.345879980905119e-23</v>
@@ -22413,7 +22413,7 @@
         <v>8.238132020998759e-05</v>
       </c>
       <c r="G102" t="n">
-        <v>1.226160375595731e-40</v>
+        <v>1.279471696273806e-40</v>
       </c>
       <c r="H102" t="n">
         <v>0.5212774663159446</v>
@@ -22425,7 +22425,7 @@
         <v>3.415728260563464e-07</v>
       </c>
       <c r="K102" t="n">
-        <v>1.201220153418792e-11</v>
+        <v>1.1550193782873e-11</v>
       </c>
       <c r="L102" t="n">
         <v>1.52125896301192e-05</v>
@@ -22434,7 +22434,7 @@
         <v>3.470291513617395e-09</v>
       </c>
       <c r="N102" t="n">
-        <v>3.245466216567481e-17</v>
+        <v>3.115647567904782e-17</v>
       </c>
       <c r="O102" t="n">
         <v>1.407330791910127e-09</v>
@@ -22446,7 +22446,7 @@
         <v>0.07735738007096883</v>
       </c>
       <c r="R102" t="n">
-        <v>2.562122854236262e-11</v>
+        <v>2.668877973162773e-11</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
@@ -22507,7 +22507,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>2.168895203794468e-06</v>
+        <v>2.201266774000355e-06</v>
       </c>
       <c r="P103" t="n">
         <v>1</v>
@@ -22525,7 +22525,7 @@
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>0.5572738975267895</v>
+        <v>0.5514078565001918</v>
       </c>
       <c r="V103" t="n">
         <v>0.0002242611939838352</v>
@@ -22547,13 +22547,13 @@
         <v>9.368309427565465e-69</v>
       </c>
       <c r="E104" t="n">
-        <v>4.636052059950057e-05</v>
+        <v>4.539467642034431e-05</v>
       </c>
       <c r="F104" t="n">
         <v>7.937915669408315e-33</v>
       </c>
       <c r="G104" t="n">
-        <v>9.010614457169956e-209</v>
+        <v>1.029784509390852e-208</v>
       </c>
       <c r="H104" t="n">
         <v>2.745699187434313e-05</v>
@@ -22574,7 +22574,7 @@
         <v>2.735068784159555e-96</v>
       </c>
       <c r="N104" t="n">
-        <v>2.465412528809702e-83</v>
+        <v>2.739347254233002e-83</v>
       </c>
       <c r="O104" t="n">
         <v>1.994679988488731e-152</v>
@@ -22583,13 +22583,13 @@
         <v>3.768520213298832e-18</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.01006505985151172</v>
+        <v>0.01019862025097673</v>
       </c>
       <c r="R104" t="n">
         <v>5.936446403828532e-43</v>
       </c>
       <c r="S104" t="n">
-        <v>0.07439751348953778</v>
+        <v>0.07278017623976524</v>
       </c>
       <c r="T104" t="n">
         <v>8.933230434693058e-72</v>
@@ -23364,22 +23364,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27444</v>
+        <v>27416</v>
       </c>
       <c r="C11" t="n">
         <v>688</v>
       </c>
       <c r="D11" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E11" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F11" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G11" t="n">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="H11" t="n">
         <v>146</v>
@@ -23391,19 +23391,19 @@
         <v>1504</v>
       </c>
       <c r="K11" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L11" t="n">
         <v>202</v>
       </c>
       <c r="M11" t="n">
-        <v>7355</v>
+        <v>7349</v>
       </c>
       <c r="N11" t="n">
         <v>953</v>
       </c>
       <c r="O11" t="n">
-        <v>2534</v>
+        <v>2528</v>
       </c>
       <c r="P11" t="n">
         <v>322</v>
@@ -23412,19 +23412,19 @@
         <v>240</v>
       </c>
       <c r="R11" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S11" t="n">
         <v>263</v>
       </c>
       <c r="T11" t="n">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="U11" t="n">
-        <v>4384</v>
+        <v>4378</v>
       </c>
       <c r="V11" t="n">
-        <v>3861</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="12">
@@ -23434,16 +23434,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20988</v>
+        <v>20906</v>
       </c>
       <c r="C12" t="n">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D12" t="n">
         <v>315</v>
       </c>
       <c r="E12" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F12" t="n">
         <v>349</v>
@@ -23455,46 +23455,46 @@
         <v>107</v>
       </c>
       <c r="I12" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J12" t="n">
-        <v>1740</v>
+        <v>1716</v>
       </c>
       <c r="K12" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="L12" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M12" t="n">
-        <v>4265</v>
+        <v>4259</v>
       </c>
       <c r="N12" t="n">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="O12" t="n">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="P12" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q12" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R12" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="S12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="T12" t="n">
-        <v>1447</v>
+        <v>1438</v>
       </c>
       <c r="U12" t="n">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="V12" t="n">
-        <v>2832</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="13">
@@ -23504,67 +23504,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14844</v>
+        <v>14784</v>
       </c>
       <c r="C13" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D13" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E13" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F13" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G13" t="n">
-        <v>1314</v>
+        <v>1304</v>
       </c>
       <c r="H13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I13" t="n">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="J13" t="n">
-        <v>1590</v>
+        <v>1603</v>
       </c>
       <c r="K13" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L13" t="n">
         <v>137</v>
       </c>
       <c r="M13" t="n">
-        <v>2118</v>
+        <v>2105</v>
       </c>
       <c r="N13" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O13" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="P13" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q13" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R13" t="n">
         <v>356</v>
       </c>
       <c r="S13" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="T13" t="n">
         <v>879</v>
       </c>
       <c r="U13" t="n">
-        <v>2651</v>
+        <v>2626</v>
       </c>
       <c r="V13" t="n">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="14">
@@ -23574,49 +23574,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11800</v>
+        <v>11853</v>
       </c>
       <c r="C14" t="n">
         <v>151</v>
       </c>
       <c r="D14" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F14" t="n">
+        <v>224</v>
+      </c>
+      <c r="G14" t="n">
+        <v>927</v>
+      </c>
+      <c r="H14" t="n">
+        <v>58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3066</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1135</v>
+      </c>
+      <c r="K14" t="n">
+        <v>224</v>
+      </c>
+      <c r="L14" t="n">
+        <v>87</v>
+      </c>
+      <c r="M14" t="n">
+        <v>909</v>
+      </c>
+      <c r="N14" t="n">
         <v>225</v>
       </c>
-      <c r="G14" t="n">
-        <v>918</v>
-      </c>
-      <c r="H14" t="n">
-        <v>56</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3109</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1130</v>
-      </c>
-      <c r="K14" t="n">
-        <v>221</v>
-      </c>
-      <c r="L14" t="n">
-        <v>86</v>
-      </c>
-      <c r="M14" t="n">
-        <v>887</v>
-      </c>
-      <c r="N14" t="n">
-        <v>223</v>
-      </c>
       <c r="O14" t="n">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="n">
         <v>82</v>
@@ -23625,16 +23625,16 @@
         <v>130</v>
       </c>
       <c r="S14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T14" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="U14" t="n">
-        <v>1080</v>
+        <v>1108</v>
       </c>
       <c r="V14" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="15">
@@ -23644,7 +23644,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4429</v>
+        <v>4546</v>
       </c>
       <c r="C15" t="n">
         <v>91</v>
@@ -23656,19 +23656,19 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G15" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
       </c>
       <c r="I15" t="n">
-        <v>402</v>
+        <v>472</v>
       </c>
       <c r="J15" t="n">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="K15" t="n">
         <v>114</v>
@@ -23677,13 +23677,13 @@
         <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="N15" t="n">
         <v>152</v>
       </c>
       <c r="O15" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="P15" t="n">
         <v>90</v>
@@ -23695,16 +23695,16 @@
         <v>35</v>
       </c>
       <c r="S15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T15" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U15" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="V15" t="n">
-        <v>916</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16">
@@ -23714,7 +23714,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8241</v>
+        <v>8229</v>
       </c>
       <c r="C16" t="n">
         <v>104</v>
@@ -23735,13 +23735,13 @@
         <v>27</v>
       </c>
       <c r="I16" t="n">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="J16" t="n">
         <v>645</v>
       </c>
       <c r="K16" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L16" t="n">
         <v>43</v>
@@ -23759,7 +23759,7 @@
         <v>99</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R16" t="n">
         <v>34</v>
@@ -23774,7 +23774,7 @@
         <v>405</v>
       </c>
       <c r="V16" t="n">
-        <v>1477</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="17">
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4687</v>
+        <v>4677</v>
       </c>
       <c r="C17" t="n">
         <v>109</v>
@@ -23799,37 +23799,37 @@
         <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H17" t="n">
         <v>51</v>
       </c>
       <c r="I17" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J17" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K17" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N17" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O17" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P17" t="n">
         <v>72</v>
       </c>
       <c r="Q17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R17" t="n">
         <v>72</v>
@@ -23838,13 +23838,13 @@
         <v>28</v>
       </c>
       <c r="T17" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="U17" t="n">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="V17" t="n">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="18">
@@ -23854,67 +23854,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19076</v>
+        <v>18949</v>
       </c>
       <c r="C18" t="n">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="D18" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E18" t="n">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F18" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G18" t="n">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="H18" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I18" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J18" t="n">
-        <v>1169</v>
+        <v>1159</v>
       </c>
       <c r="K18" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L18" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M18" t="n">
-        <v>1364</v>
+        <v>1339</v>
       </c>
       <c r="N18" t="n">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="O18" t="n">
-        <v>1325</v>
+        <v>1314</v>
       </c>
       <c r="P18" t="n">
         <v>256</v>
       </c>
       <c r="Q18" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R18" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="S18" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T18" t="n">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="U18" t="n">
-        <v>5300</v>
+        <v>5266</v>
       </c>
       <c r="V18" t="n">
-        <v>3016</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="19">
@@ -23924,67 +23924,67 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>47501</v>
+        <v>47650</v>
       </c>
       <c r="C19" t="n">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="D19" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E19" t="n">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F19" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G19" t="n">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="H19" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I19" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J19" t="n">
-        <v>4349</v>
+        <v>4360</v>
       </c>
       <c r="K19" t="n">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="L19" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M19" t="n">
-        <v>13051</v>
+        <v>13077</v>
       </c>
       <c r="N19" t="n">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="O19" t="n">
-        <v>4124</v>
+        <v>4136</v>
       </c>
       <c r="P19" t="n">
         <v>609</v>
       </c>
       <c r="Q19" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="R19" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="S19" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="T19" t="n">
-        <v>2867</v>
+        <v>2877</v>
       </c>
       <c r="U19" t="n">
-        <v>5785</v>
+        <v>5822</v>
       </c>
       <c r="V19" t="n">
-        <v>6494</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="20">
@@ -26934,67 +26934,67 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>18189</v>
+        <v>17413</v>
       </c>
       <c r="C62" t="n">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="D62" t="n">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="E62" t="n">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F62" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G62" t="n">
-        <v>1230</v>
+        <v>1195</v>
       </c>
       <c r="H62" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I62" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="J62" t="n">
-        <v>1583</v>
+        <v>1523</v>
       </c>
       <c r="K62" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="L62" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="M62" t="n">
-        <v>3371</v>
+        <v>3224</v>
       </c>
       <c r="N62" t="n">
-        <v>602</v>
+        <v>573</v>
       </c>
       <c r="O62" t="n">
-        <v>1468</v>
+        <v>1380</v>
       </c>
       <c r="P62" t="n">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="Q62" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="R62" t="n">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="S62" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="T62" t="n">
-        <v>984</v>
+        <v>939</v>
       </c>
       <c r="U62" t="n">
-        <v>2885</v>
+        <v>2746</v>
       </c>
       <c r="V62" t="n">
-        <v>2945</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="63">
@@ -27004,67 +27004,67 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>33437</v>
+        <v>34213</v>
       </c>
       <c r="C63" t="n">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="D63" t="n">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="E63" t="n">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F63" t="n">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="G63" t="n">
-        <v>2062</v>
+        <v>2097</v>
       </c>
       <c r="H63" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I63" t="n">
-        <v>2684</v>
+        <v>2694</v>
       </c>
       <c r="J63" t="n">
-        <v>2364</v>
+        <v>2424</v>
       </c>
       <c r="K63" t="n">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="L63" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="M63" t="n">
-        <v>6085</v>
+        <v>6232</v>
       </c>
       <c r="N63" t="n">
-        <v>1126</v>
+        <v>1155</v>
       </c>
       <c r="O63" t="n">
-        <v>2483</v>
+        <v>2571</v>
       </c>
       <c r="P63" t="n">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="Q63" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="R63" t="n">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="S63" t="n">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="T63" t="n">
-        <v>1794</v>
+        <v>1839</v>
       </c>
       <c r="U63" t="n">
-        <v>4867</v>
+        <v>5006</v>
       </c>
       <c r="V63" t="n">
-        <v>5310</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="64">
@@ -27700,7 +27700,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Function:DNA binding region</t>
+          <t>Function:DNA binding</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -30700,7 +30700,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9214</v>
+        <v>9202</v>
       </c>
       <c r="C11" t="n">
         <v>246</v>
@@ -30733,13 +30733,13 @@
         <v>154</v>
       </c>
       <c r="M11" t="n">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="N11" t="n">
         <v>438</v>
       </c>
       <c r="O11" t="n">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="P11" t="n">
         <v>307</v>
@@ -30748,7 +30748,7 @@
         <v>64</v>
       </c>
       <c r="R11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S11" t="n">
         <v>104</v>
@@ -30757,10 +30757,10 @@
         <v>833</v>
       </c>
       <c r="U11" t="n">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="V11" t="n">
-        <v>2162</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="12">
@@ -30770,67 +30770,67 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14872</v>
+        <v>14735</v>
       </c>
       <c r="C12" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D12" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E12" t="n">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F12" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G12" t="n">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H12" t="n">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="I12" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="J12" t="n">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="K12" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="L12" t="n">
         <v>229</v>
       </c>
       <c r="M12" t="n">
-        <v>1931</v>
+        <v>1917</v>
       </c>
       <c r="N12" t="n">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="O12" t="n">
-        <v>1413</v>
+        <v>1401</v>
       </c>
       <c r="P12" t="n">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R12" t="n">
         <v>102</v>
       </c>
       <c r="S12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T12" t="n">
-        <v>1468</v>
+        <v>1457</v>
       </c>
       <c r="U12" t="n">
-        <v>1343</v>
+        <v>1331</v>
       </c>
       <c r="V12" t="n">
-        <v>3515</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="13">
@@ -30840,67 +30840,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28030</v>
+        <v>27806</v>
       </c>
       <c r="C13" t="n">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D13" t="n">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="E13" t="n">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="F13" t="n">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G13" t="n">
-        <v>1288</v>
+        <v>1267</v>
       </c>
       <c r="H13" t="n">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="I13" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J13" t="n">
-        <v>1355</v>
+        <v>1337</v>
       </c>
       <c r="K13" t="n">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="L13" t="n">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="M13" t="n">
-        <v>2895</v>
+        <v>2878</v>
       </c>
       <c r="N13" t="n">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="O13" t="n">
-        <v>2411</v>
+        <v>2393</v>
       </c>
       <c r="P13" t="n">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="Q13" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="R13" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="S13" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T13" t="n">
-        <v>2287</v>
+        <v>2279</v>
       </c>
       <c r="U13" t="n">
-        <v>2304</v>
+        <v>2289</v>
       </c>
       <c r="V13" t="n">
-        <v>7334</v>
+        <v>7256</v>
       </c>
     </row>
     <row r="14">
@@ -30910,67 +30910,67 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46106</v>
+        <v>46061</v>
       </c>
       <c r="C14" t="n">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="D14" t="n">
         <v>1723</v>
       </c>
       <c r="E14" t="n">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F14" t="n">
-        <v>2028</v>
+        <v>2014</v>
       </c>
       <c r="G14" t="n">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="H14" t="n">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="I14" t="n">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="J14" t="n">
-        <v>4574</v>
+        <v>4547</v>
       </c>
       <c r="K14" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="L14" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M14" t="n">
-        <v>2694</v>
+        <v>2707</v>
       </c>
       <c r="N14" t="n">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="O14" t="n">
-        <v>3873</v>
+        <v>3869</v>
       </c>
       <c r="P14" t="n">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="Q14" t="n">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R14" t="n">
         <v>204</v>
       </c>
       <c r="S14" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="T14" t="n">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="U14" t="n">
-        <v>3003</v>
+        <v>3012</v>
       </c>
       <c r="V14" t="n">
-        <v>14414</v>
+        <v>14404</v>
       </c>
     </row>
     <row r="15">
@@ -30980,67 +30980,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29043</v>
+        <v>29461</v>
       </c>
       <c r="C15" t="n">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="D15" t="n">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="E15" t="n">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="F15" t="n">
-        <v>1184</v>
+        <v>1205</v>
       </c>
       <c r="G15" t="n">
-        <v>1130</v>
+        <v>1151</v>
       </c>
       <c r="H15" t="n">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="I15" t="n">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="J15" t="n">
-        <v>3343</v>
+        <v>3396</v>
       </c>
       <c r="K15" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="L15" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="M15" t="n">
-        <v>1306</v>
+        <v>1326</v>
       </c>
       <c r="N15" t="n">
-        <v>1074</v>
+        <v>1093</v>
       </c>
       <c r="O15" t="n">
-        <v>2340</v>
+        <v>2375</v>
       </c>
       <c r="P15" t="n">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="Q15" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="R15" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="S15" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="T15" t="n">
-        <v>1215</v>
+        <v>1238</v>
       </c>
       <c r="U15" t="n">
-        <v>1786</v>
+        <v>1806</v>
       </c>
       <c r="V15" t="n">
-        <v>9511</v>
+        <v>9637</v>
       </c>
     </row>
     <row r="16">
@@ -31050,22 +31050,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52635</v>
+        <v>52595</v>
       </c>
       <c r="C16" t="n">
         <v>1234</v>
       </c>
       <c r="D16" t="n">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="E16" t="n">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F16" t="n">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="G16" t="n">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="H16" t="n">
         <v>464</v>
@@ -31074,7 +31074,7 @@
         <v>1168</v>
       </c>
       <c r="J16" t="n">
-        <v>6514</v>
+        <v>6511</v>
       </c>
       <c r="K16" t="n">
         <v>415</v>
@@ -31083,16 +31083,16 @@
         <v>774</v>
       </c>
       <c r="M16" t="n">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="N16" t="n">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="O16" t="n">
-        <v>4434</v>
+        <v>4432</v>
       </c>
       <c r="P16" t="n">
-        <v>2178</v>
+        <v>2173</v>
       </c>
       <c r="Q16" t="n">
         <v>608</v>
@@ -31101,16 +31101,16 @@
         <v>149</v>
       </c>
       <c r="S16" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T16" t="n">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="U16" t="n">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="V16" t="n">
-        <v>17392</v>
+        <v>17380</v>
       </c>
     </row>
     <row r="17">
@@ -31120,10 +31120,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12965</v>
+        <v>12964</v>
       </c>
       <c r="C17" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D17" t="n">
         <v>396</v>
@@ -31132,37 +31132,37 @@
         <v>266</v>
       </c>
       <c r="F17" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G17" t="n">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H17" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I17" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J17" t="n">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="K17" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L17" t="n">
         <v>265</v>
       </c>
       <c r="M17" t="n">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="N17" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O17" t="n">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="P17" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="Q17" t="n">
         <v>160</v>
@@ -31171,16 +31171,16 @@
         <v>71</v>
       </c>
       <c r="S17" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T17" t="n">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="U17" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="V17" t="n">
-        <v>4349</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="18">
@@ -31190,67 +31190,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26627</v>
+        <v>26495</v>
       </c>
       <c r="C18" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D18" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E18" t="n">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="F18" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G18" t="n">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="H18" t="n">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="I18" t="n">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="J18" t="n">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="K18" t="n">
         <v>426</v>
       </c>
       <c r="L18" t="n">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="M18" t="n">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="N18" t="n">
-        <v>1103</v>
+        <v>1094</v>
       </c>
       <c r="O18" t="n">
-        <v>2166</v>
+        <v>2152</v>
       </c>
       <c r="P18" t="n">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="Q18" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="R18" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S18" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T18" t="n">
-        <v>2540</v>
+        <v>2527</v>
       </c>
       <c r="U18" t="n">
-        <v>2594</v>
+        <v>2580</v>
       </c>
       <c r="V18" t="n">
-        <v>7413</v>
+        <v>7389</v>
       </c>
     </row>
     <row r="19">
@@ -31260,67 +31260,67 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35038</v>
+        <v>35211</v>
       </c>
       <c r="C19" t="n">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D19" t="n">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E19" t="n">
-        <v>1244</v>
+        <v>1254</v>
       </c>
       <c r="F19" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G19" t="n">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="I19" t="n">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="J19" t="n">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="K19" t="n">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="L19" t="n">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="M19" t="n">
-        <v>6474</v>
+        <v>6482</v>
       </c>
       <c r="N19" t="n">
-        <v>1490</v>
+        <v>1501</v>
       </c>
       <c r="O19" t="n">
-        <v>3556</v>
+        <v>3573</v>
       </c>
       <c r="P19" t="n">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="Q19" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="R19" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="S19" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T19" t="n">
-        <v>3036</v>
+        <v>3050</v>
       </c>
       <c r="U19" t="n">
-        <v>2380</v>
+        <v>2396</v>
       </c>
       <c r="V19" t="n">
-        <v>7782</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="20">
@@ -34270,67 +34270,67 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62395</v>
+        <v>61983</v>
       </c>
       <c r="C62" t="n">
-        <v>1448</v>
+        <v>1427</v>
       </c>
       <c r="D62" t="n">
-        <v>1964</v>
+        <v>1958</v>
       </c>
       <c r="E62" t="n">
-        <v>1907</v>
+        <v>1890</v>
       </c>
       <c r="F62" t="n">
-        <v>1904</v>
+        <v>1894</v>
       </c>
       <c r="G62" t="n">
-        <v>3588</v>
+        <v>3570</v>
       </c>
       <c r="H62" t="n">
-        <v>1248</v>
+        <v>1230</v>
       </c>
       <c r="I62" t="n">
-        <v>1803</v>
+        <v>1788</v>
       </c>
       <c r="J62" t="n">
-        <v>3888</v>
+        <v>3866</v>
       </c>
       <c r="K62" t="n">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L62" t="n">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="M62" t="n">
-        <v>4901</v>
+        <v>4870</v>
       </c>
       <c r="N62" t="n">
-        <v>2270</v>
+        <v>2256</v>
       </c>
       <c r="O62" t="n">
-        <v>5131</v>
+        <v>5107</v>
       </c>
       <c r="P62" t="n">
-        <v>2172</v>
+        <v>2156</v>
       </c>
       <c r="Q62" t="n">
+        <v>498</v>
+      </c>
+      <c r="R62" t="n">
+        <v>415</v>
+      </c>
+      <c r="S62" t="n">
         <v>499</v>
       </c>
-      <c r="R62" t="n">
-        <v>424</v>
-      </c>
-      <c r="S62" t="n">
-        <v>502</v>
-      </c>
       <c r="T62" t="n">
-        <v>4016</v>
+        <v>3984</v>
       </c>
       <c r="U62" t="n">
-        <v>4231</v>
+        <v>4199</v>
       </c>
       <c r="V62" t="n">
-        <v>18691</v>
+        <v>18578</v>
       </c>
     </row>
     <row r="63">
@@ -34340,67 +34340,67 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>60376</v>
+        <v>60788</v>
       </c>
       <c r="C63" t="n">
-        <v>1522</v>
+        <v>1543</v>
       </c>
       <c r="D63" t="n">
-        <v>1871</v>
+        <v>1877</v>
       </c>
       <c r="E63" t="n">
-        <v>1787</v>
+        <v>1804</v>
       </c>
       <c r="F63" t="n">
-        <v>2104</v>
+        <v>2114</v>
       </c>
       <c r="G63" t="n">
-        <v>3305</v>
+        <v>3323</v>
       </c>
       <c r="H63" t="n">
-        <v>1172</v>
+        <v>1190</v>
       </c>
       <c r="I63" t="n">
-        <v>2031</v>
+        <v>2046</v>
       </c>
       <c r="J63" t="n">
-        <v>4610</v>
+        <v>4632</v>
       </c>
       <c r="K63" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L63" t="n">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="M63" t="n">
-        <v>3919</v>
+        <v>3950</v>
       </c>
       <c r="N63" t="n">
-        <v>2108</v>
+        <v>2122</v>
       </c>
       <c r="O63" t="n">
-        <v>4936</v>
+        <v>4960</v>
       </c>
       <c r="P63" t="n">
-        <v>2233</v>
+        <v>2249</v>
       </c>
       <c r="Q63" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="R63" t="n">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="S63" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="T63" t="n">
-        <v>3372</v>
+        <v>3404</v>
       </c>
       <c r="U63" t="n">
-        <v>3751</v>
+        <v>3783</v>
       </c>
       <c r="V63" t="n">
-        <v>18664</v>
+        <v>18777</v>
       </c>
     </row>
     <row r="64">
@@ -35036,7 +35036,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Function:DNA binding region</t>
+          <t>Function:DNA binding</t>
         </is>
       </c>
       <c r="B73" t="n">
